--- a/inst/extdata/uncnewsletter.xlsx
+++ b/inst/extdata/uncnewsletter.xlsx
@@ -351,13 +351,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA174"/>
+  <dimension ref="A1:AB174"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>paper_id</t>
+          <t>paperid</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -407,7 +407,7 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>supp_link</t>
+          <t>supp_url</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
@@ -427,7 +427,7 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>first_author_affiliation_region</t>
+          <t>first_author_affiliation_country</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
@@ -452,7 +452,7 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>correspondence_author_affiliation_region</t>
+          <t>correspondence_author_affiliation_country</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
@@ -482,10 +482,15 @@
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
+          <t>das_repo_url</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
           <t>citations</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>keywords</t>
         </is>
@@ -552,11 +557,6 @@
           <t>North Carolina State University</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q2" t="inlineStr">
         <is>
           <t>0000-0002-5778-354X</t>
@@ -565,12 +565,12 @@
       <c r="W2" t="b">
         <v>0</v>
       </c>
-      <c r="Z2">
+      <c r="AA2">
         <v>2</v>
       </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>["drinking water", "environmental policy", "health and safety"]</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>c("drinkingwater", "environmentalpolicy", "healthandsafety")</t>
         </is>
       </c>
     </row>
@@ -635,15 +635,10 @@
           <t>North Carolina State University</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W3" t="b">
         <v>0</v>
       </c>
-      <c r="Z3">
+      <c r="AA3">
         <v>3</v>
       </c>
     </row>
@@ -708,11 +703,6 @@
           <t>University of North Carolina</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
           <t>0000-0002-1906-8692</t>
@@ -731,7 +721,12 @@
           <t>available in online repository</t>
         </is>
       </c>
-      <c r="Z4">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>https://github.com/tedlanghorst/OpenOBS</t>
+        </is>
+      </c>
+      <c r="AA4">
         <v>4</v>
       </c>
     </row>
@@ -770,6 +765,9 @@
       <c r="H5" t="b">
         <v>0</v>
       </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
       <c r="L5">
         <v>5</v>
       </c>
@@ -783,15 +781,10 @@
           <t>Shenyang Ligong University</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
       <c r="W5" t="b">
         <v>0</v>
       </c>
-      <c r="Z5">
+      <c r="AA5">
         <v>0</v>
       </c>
     </row>
@@ -830,6 +823,9 @@
       <c r="H6" t="b">
         <v>0</v>
       </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
       <c r="L6">
         <v>7</v>
       </c>
@@ -843,20 +839,15 @@
           <t>Longwood University</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W6" t="b">
         <v>0</v>
       </c>
-      <c r="Z6">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>["Container breeding", "Mosquito", "Mosquito larvae", "Rainwater harvesting"]</t>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>c("Containerbreeding", "Mosquito", "Mosquitolarvae", "Rainwaterharvesting")</t>
         </is>
       </c>
     </row>
@@ -895,6 +886,9 @@
       <c r="H7" t="b">
         <v>0</v>
       </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
       <c r="L7">
         <v>7</v>
       </c>
@@ -908,11 +902,6 @@
           <t>North Carolina State University</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>0000-0002-2365-6200</t>
@@ -931,9 +920,14 @@
           <t>available in online repository</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>["compensatory mitigation", "decision science", "knowledge coproduction", "natural resources management", "research-management partnerships", "watershed planning"]</t>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>c("https://deq.nc.gov/about/divisions/mitigation-services/dms-planning/dms-web-map", "https://www.nconemap.gov/", "https://doi.org/10.5066/P96HHBIE", "https://doi.org/10.5066/P9UUT74V", "https://websoilsurvey.nrcs.usda.gov/", "https://doi.org/10.5066/P95PTP5G")</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>c("compensatorymitigation", "decisionscience", "knowledgecoproduction", "naturalresourcesmanagement", "research-managementpartnerships", "watershedplanning")</t>
         </is>
       </c>
     </row>
@@ -972,6 +966,9 @@
       <c r="H8" t="b">
         <v>0</v>
       </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
       <c r="L8">
         <v>3</v>
       </c>
@@ -985,17 +982,12 @@
           <t>University of South Carolina</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W8" t="b">
         <v>0</v>
       </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>["Drought", "Communications/decision-making", "Decision support", "Local effects", "Societal impacts", "Community"]</t>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>c("Drought", "Communications/decision-making", "Decisionsupport", "Localeffects", "Societalimpacts", "Community")</t>
         </is>
       </c>
     </row>
@@ -1034,6 +1026,9 @@
       <c r="H9" t="b">
         <v>0</v>
       </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
       <c r="L9">
         <v>4</v>
       </c>
@@ -1049,29 +1044,29 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0000-0001-5895-5318</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Rebecca C. Fry</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>University of North Carolina at Chapel Hill</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0000-0001-5895-5318</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>Rebecca C. Fry</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>University of North Carolina at Chapel Hill</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W9" t="b">
         <v>1</v>
       </c>
@@ -1085,12 +1080,17 @@
           <t>available in online repository</t>
         </is>
       </c>
-      <c r="Z9">
-        <v>1</v>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>["environmental justice", "private wells", "toxic metals"]</t>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.15139/S3/BDQG9O</t>
+        </is>
+      </c>
+      <c r="AA9">
+        <v>1</v>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>c("environmentaljustice", "privatewells", "toxicmetals")</t>
         </is>
       </c>
     </row>
@@ -1129,6 +1129,9 @@
       <c r="H10" t="b">
         <v>0</v>
       </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
       <c r="L10">
         <v>6</v>
       </c>
@@ -1142,11 +1145,6 @@
           <t>North Carolina State University</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>0000-0003-4213-6929</t>
@@ -1165,12 +1163,12 @@
           <t>on request</t>
         </is>
       </c>
-      <c r="Z10">
+      <c r="AA10">
         <v>2</v>
       </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>["Escherichia coli", "Plasmid-mediated quinolone resistance", "Plasmid-mediated colistin resistance", "Poultry workers", "Chicken", "Poultry Environments", "Nigeria"]</t>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>c("Escherichiacoli", "Plasmid-mediatedquinoloneresistance", "Plasmid-mediatedcolistinresistance", "Poultryworkers", "Chicken", "PoultryEnvironments", "Nigeria")</t>
         </is>
       </c>
     </row>
@@ -1209,6 +1207,9 @@
       <c r="H11" t="b">
         <v>0</v>
       </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
       <c r="L11">
         <v>13</v>
       </c>
@@ -1222,11 +1223,6 @@
           <t>University of Nebraska-Lincoln</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q11" t="inlineStr">
         <is>
           <t>0000-0002-0371-7125</t>
@@ -1235,12 +1231,12 @@
       <c r="W11" t="b">
         <v>0</v>
       </c>
-      <c r="Z11">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>["Stakeholder analysis", "FEWS", "Environmental sustainability", "Transdisciplinary research", "Stakeholder engagement", "Livestock production"]</t>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>c("Stakeholderanalysis", "FEWS", "Environmentalsustainability", "Transdisciplinaryresearch", "Stakeholderengagement", "Livestockproduction")</t>
         </is>
       </c>
     </row>
@@ -1305,15 +1301,10 @@
           <t>University of North Carolina Wilmington</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W12" t="b">
         <v>0</v>
       </c>
-      <c r="Z12">
+      <c r="AA12">
         <v>2</v>
       </c>
     </row>
@@ -1352,6 +1343,9 @@
       <c r="H13" t="b">
         <v>0</v>
       </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
       <c r="L13">
         <v>4</v>
       </c>
@@ -1363,11 +1357,6 @@
       <c r="N13" t="inlineStr">
         <is>
           <t>National Renewable Energy Lab NREL</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>USA</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1414,6 +1403,9 @@
       <c r="H14" t="b">
         <v>0</v>
       </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
       <c r="L14">
         <v>8</v>
       </c>
@@ -1427,11 +1419,6 @@
           <t>Universidade Regional do Noroeste do Estado do Rio Grande do Sul</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
       <c r="Q14" t="inlineStr">
         <is>
           <t>0000-0003-1591-3622</t>
@@ -1440,9 +1427,9 @@
       <c r="W14" t="b">
         <v>0</v>
       </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>["Water Resources", "Life", "Environmental Education", "Development", "UN 2030 Agenda"]</t>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>c("WaterResources", "Life", "EnvironmentalEducation", "Development", "UN2030Agenda")</t>
         </is>
       </c>
     </row>
@@ -1481,6 +1468,9 @@
       <c r="H15" t="b">
         <v>0</v>
       </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
       <c r="L15">
         <v>2</v>
       </c>
@@ -1494,17 +1484,12 @@
           <t>Duke Law School</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W15" t="b">
         <v>0</v>
       </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>["water", "safe drinking water act", "environmental law", "law", "policy", "public health", "North Carolina"]</t>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>c("water", "safedrinkingwateract", "environmentallaw", "law", "policy", "publichealth", "NorthCarolina")</t>
         </is>
       </c>
     </row>
@@ -1543,6 +1528,9 @@
       <c r="H16" t="b">
         <v>0</v>
       </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
       <c r="L16">
         <v>6</v>
       </c>
@@ -1556,11 +1544,6 @@
           <t>University of North Carolina at Chapel Hill</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>0000-0001-6999-8268</t>
@@ -1569,7 +1552,7 @@
       <c r="W16" t="b">
         <v>0</v>
       </c>
-      <c r="Z16">
+      <c r="AA16">
         <v>0</v>
       </c>
     </row>
@@ -1608,6 +1591,9 @@
       <c r="H17" t="b">
         <v>0</v>
       </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
       <c r="L17">
         <v>4</v>
       </c>
@@ -1623,30 +1609,30 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Emek Kose</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>St. Mary's College of Maryland</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>Emek Kose</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>St. Mary's College of Maryland</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="Z17">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>["Algal blooms", "dynamical systems", "math modelling", "nutrient treshold for resolvable blooms"]</t>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>c("Algalblooms", "dynamicalsystems", "mathmodelling", "nutrienttresholdforresolvableblooms")</t>
         </is>
       </c>
     </row>
@@ -1685,6 +1671,9 @@
       <c r="H18" t="b">
         <v>0</v>
       </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
       <c r="L18">
         <v>6</v>
       </c>
@@ -1698,12 +1687,7 @@
           <t>University of North Carolina</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="Z18">
+      <c r="AA18">
         <v>0</v>
       </c>
     </row>
@@ -1747,7 +1731,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>xlsx &amp; docx</t>
+          <t>c("xlsx", "docx")</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1770,24 +1754,24 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Scott M. Belcher</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>North Carolina State University</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>Scott M. Belcher</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>North Carolina State University</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="V19" t="inlineStr">
         <is>
           <t>0000-0002-1196-3705</t>
@@ -1806,12 +1790,17 @@
           <t>available in online repository</t>
         </is>
       </c>
-      <c r="Z19">
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>https://www.frontiersin.org/articles/10.3389/ftox.2022.1010185/full#supplementary-material</t>
+        </is>
+      </c>
+      <c r="AA19">
         <v>7</v>
       </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>["autoantibodies", "autoimmune", "crocodilian", "immune toxicity", "lupus", "one health", PFAS"]</t>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>c("autoantibodies", "autoimmune", "crocodilian", "immunetoxicity", "lupus", "onehealth")</t>
         </is>
       </c>
     </row>
@@ -1850,6 +1839,9 @@
       <c r="H20" t="b">
         <v>0</v>
       </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
       <c r="L20">
         <v>8</v>
       </c>
@@ -1861,11 +1853,6 @@
       <c r="N20" t="inlineStr">
         <is>
           <t>University of North Carolina</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>USA</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -1938,11 +1925,6 @@
           <t>North Carolina State University</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W21" t="b">
         <v>1</v>
       </c>
@@ -1956,7 +1938,7 @@
           <t>on request</t>
         </is>
       </c>
-      <c r="Z21">
+      <c r="AA21">
         <v>2</v>
       </c>
     </row>
@@ -1995,6 +1977,9 @@
       <c r="H22" t="b">
         <v>0</v>
       </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
       <c r="L22">
         <v>9</v>
       </c>
@@ -2008,11 +1993,6 @@
           <t>University of North Carolina</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q22" t="inlineStr">
         <is>
           <t>0000-0002-5347-1370</t>
@@ -2021,9 +2001,9 @@
       <c r="W22" t="b">
         <v>0</v>
       </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>["private wells", "environmental justice", "drinking water", "testing", "metal contamination"]</t>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>c("privatewells", "environmentaljustice", "drinkingwater", "testing", "metalcontamination")</t>
         </is>
       </c>
     </row>
@@ -2062,6 +2042,9 @@
       <c r="H23" t="b">
         <v>0</v>
       </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
       <c r="L23">
         <v>8</v>
       </c>
@@ -2075,11 +2058,6 @@
           <t>University of North Carolina</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q23" t="inlineStr">
         <is>
           <t>0000-0002-3078-6716</t>
@@ -2098,7 +2076,12 @@
           <t>available in online repository</t>
         </is>
       </c>
-      <c r="Z23">
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>https://github.com/davidfgold/TampaBayWater</t>
+        </is>
+      </c>
+      <c r="AA23">
         <v>4</v>
       </c>
     </row>
@@ -2163,11 +2146,6 @@
           <t>University of Georgia</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q24" t="inlineStr">
         <is>
           <t>0000-0003-2112-3846</t>
@@ -2186,7 +2164,7 @@
           <t>on request</t>
         </is>
       </c>
-      <c r="Z24">
+      <c r="AA24">
         <v>2</v>
       </c>
     </row>
@@ -2225,6 +2203,9 @@
       <c r="H25" t="b">
         <v>0</v>
       </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
       <c r="L25">
         <v>4</v>
       </c>
@@ -2238,17 +2219,12 @@
           <t>Duke University</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W25" t="b">
         <v>0</v>
       </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>["Infrastructure", "North Carolina", "Hurricanes", "Natural Disasters", "Public Opinion", "Water Systems"]</t>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>c("Infrastructure", "NorthCarolina", "Hurricanes", "NaturalDisasters", "PublicOpinion", "WaterSystems")</t>
         </is>
       </c>
     </row>
@@ -2287,6 +2263,9 @@
       <c r="H26" t="b">
         <v>0</v>
       </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
       <c r="L26">
         <v>3</v>
       </c>
@@ -2300,17 +2279,12 @@
           <t>North Carolina State University</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W26" t="b">
         <v>0</v>
       </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>["Utilities", "Financial Assistance", "Durham", "North Carolina"]</t>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>c("Utilities", "FinancialAssistance", "Durham", "NorthCarolina")</t>
         </is>
       </c>
     </row>
@@ -2375,11 +2349,6 @@
           <t>US EPA</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q27" t="inlineStr">
         <is>
           <t>0000-0002-6322-4349</t>
@@ -2388,12 +2357,12 @@
       <c r="W27" t="b">
         <v>0</v>
       </c>
-      <c r="Z27">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>["PFAS", "Multimorbidity", "Electronic Health Records", "PFOA", "PFHpA", "Chronic disease"]</t>
+      <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>c("PFAS", "Multimorbidity", "ElectronicHealthRecords", "PFOA", "PFHpA", "Chronicdisease")</t>
         </is>
       </c>
     </row>
@@ -2432,6 +2401,9 @@
       <c r="H28" t="b">
         <v>0</v>
       </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
       <c r="L28">
         <v>10</v>
       </c>
@@ -2447,24 +2419,24 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Mary H. Ward</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>National Institutes of Health, Bethesday, Maryland</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>Mary H. Ward</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>National Institutes of Health, Bethesday, Maryland</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="V28" t="inlineStr">
         <is>
           <t>0000-0001-7584-8856</t>
@@ -2473,12 +2445,12 @@
       <c r="W28" t="b">
         <v>0</v>
       </c>
-      <c r="Z28">
-        <v>0</v>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>["Drinking Water", "Nitrate", "Disinfection byproducts", "Trihalomethanes", "Exposure assessment", "Agriculture", "Cohort"]</t>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>c("DrinkingWater", "Nitrate", "Disinfectionbyproducts", "Trihalomethanes", "Exposureassessment", "Agriculture", "Cohort")</t>
         </is>
       </c>
     </row>
@@ -2545,29 +2517,29 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>0000-0002-1157-5120</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Mohamed A. Youssef</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>North Carolina State University</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>0000-0002-1157-5120</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>Mohamed A. Youssef</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>North Carolina State University</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W29" t="b">
         <v>1</v>
       </c>
@@ -2581,7 +2553,7 @@
           <t>on request</t>
         </is>
       </c>
-      <c r="Z29">
+      <c r="AA29">
         <v>1</v>
       </c>
     </row>
@@ -2617,6 +2589,9 @@
       <c r="G30">
         <v>2022</v>
       </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -2679,11 +2654,6 @@
           <t>University of California</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q31" t="inlineStr">
         <is>
           <t>0000-0002-1050-6721</t>
@@ -2743,7 +2713,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>pdf &amp; xlsx</t>
+          <t>c("pdf", "xlsx")</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2764,11 +2734,6 @@
           <t>WHO</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>Switzerland</t>
-        </is>
-      </c>
       <c r="W32" t="b">
         <v>1</v>
       </c>
@@ -2782,7 +2747,7 @@
           <t>on request</t>
         </is>
       </c>
-      <c r="Z32">
+      <c r="AA32">
         <v>46</v>
       </c>
     </row>
@@ -2826,7 +2791,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>pdf &amp; code</t>
+          <t>c("pdf", "code")</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2849,29 +2814,29 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>0000-0003-3065-3515</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Ariel Christensen</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>University of North Carolina</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>0000-0003-3065-3515</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>Ariel Christensen</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>University of North Carolina</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="V33" t="inlineStr">
         <is>
           <t>0000-0003-3925-1475</t>
@@ -2880,12 +2845,12 @@
       <c r="W33" t="b">
         <v>0</v>
       </c>
-      <c r="Z33">
-        <v>0</v>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>["COVID 19", "Viral load", "SARS CoV 2", "Epidemiology", "Public and occupational health", "North Carolina", "Disease surveillance", "Virus testing"]</t>
+      <c r="AA33">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>c("COVID19", "Viralload", "SARSCoV2", "Epidemiology", "Publicandoccupationalhealth", "NorthCarolina", "Diseasesurveillance", "Virustesting")</t>
         </is>
       </c>
     </row>
@@ -2929,7 +2894,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>xlsx &amp; docx</t>
+          <t>c("xlsx", "docx")</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2950,11 +2915,6 @@
           <t>North Carolina State University</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q34" t="inlineStr">
         <is>
           <t>0000-0001-7975-7476</t>
@@ -2963,7 +2923,7 @@
       <c r="W34" t="b">
         <v>0</v>
       </c>
-      <c r="Z34">
+      <c r="AA34">
         <v>15</v>
       </c>
     </row>
@@ -3030,29 +2990,29 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>0000-0003-0960-7565</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Jane A. Hoppin</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>North Carolina State University</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>0000-0003-0960-7565</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>Jane A. Hoppin</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>North Carolina State University</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="V35" t="inlineStr">
         <is>
           <t>0000-0001-8456-0969</t>
@@ -3061,7 +3021,7 @@
       <c r="W35" t="b">
         <v>0</v>
       </c>
-      <c r="Z35">
+      <c r="AA35">
         <v>8</v>
       </c>
     </row>
@@ -3094,6 +3054,9 @@
           <t>Drinking Water–Associated PFAS and Fluoroethers and Lipid Outcomes in the GenX Exposure Study</t>
         </is>
       </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37">
@@ -3130,6 +3093,9 @@
       <c r="H37" t="b">
         <v>0</v>
       </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
       <c r="L37">
         <v>1</v>
       </c>
@@ -3143,12 +3109,7 @@
           <t>independent</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="Z37">
+      <c r="AA37">
         <v>0</v>
       </c>
     </row>
@@ -3187,6 +3148,9 @@
       <c r="H38" t="b">
         <v>0</v>
       </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
       <c r="L38">
         <v>3</v>
       </c>
@@ -3238,12 +3202,12 @@
           <t>on request</t>
         </is>
       </c>
-      <c r="Z38">
-        <v>0</v>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>["Tropical Cyclones", "Spectral wave modelling", "Coastal hydrodynamics", "Ocean currents", "Storm surge", "Barrier islands"]</t>
+      <c r="AA38">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>c("TropicalCyclones", "Spectralwavemodelling", "Coastalhydrodynamics", "Oceancurrents", "Stormsurge", "Barrierislands")</t>
         </is>
       </c>
     </row>
@@ -3282,6 +3246,9 @@
       <c r="H39" t="b">
         <v>0</v>
       </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
       <c r="L39">
         <v>9</v>
       </c>
@@ -3297,24 +3264,24 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Marcelo Ardón</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>North Carolina State University</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>Marcelo Ardón</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>North Carolina State University</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="V39" t="inlineStr">
         <is>
           <t>0000-0001-7275-2672</t>
@@ -3333,12 +3300,12 @@
           <t>on request</t>
         </is>
       </c>
-      <c r="Z39">
+      <c r="AA39">
         <v>2</v>
       </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>["Pocosin", "Greenhouse gases", "Restoration", "Mitigation"]</t>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>c("Pocosin", "Greenhousegases", "Restoration", "Mitigation")</t>
         </is>
       </c>
     </row>
@@ -3403,11 +3370,6 @@
           <t>North Carolina State University</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W40" t="b">
         <v>1</v>
       </c>
@@ -3421,12 +3383,17 @@
           <t>available in online repository</t>
         </is>
       </c>
-      <c r="Z40">
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>c("https://ameriflux.lbl.gov/sites/siteinfo/US-Cwt", "https://earthengine.google.com", "https://lpdaac.usgs.gov/products/mod16a2gfv006", "https://www.usgs.gov/core-science-systems/nli/landsat/landsat-provisional-actual-evapotranspiration", "https://www.fs.usda.gov/rds/archive/Catalog/RDS-2019-0026", "https://www.fs.usda.gov/rds/archive/catalog/RDS-2013-0013")</t>
+        </is>
+      </c>
+      <c r="AA40">
         <v>2</v>
       </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>["Evapotranspiration", "Remote sensing", "Topography", "Forest composition", "Landsat", "MODIS"]</t>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>c("Evapotranspiration", "Remotesensing", "Topography", "Forestcomposition", "Landsat", "MODIS")</t>
         </is>
       </c>
     </row>
@@ -3491,11 +3458,6 @@
           <t>Mathematice Inc.</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q41" t="inlineStr">
         <is>
           <t>0000-0002-4324-6807</t>
@@ -3514,12 +3476,17 @@
           <t>available in online repository</t>
         </is>
       </c>
-      <c r="Z41">
-        <v>0</v>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>["Wastewater Monitoring", "Sars-Covid-2", "Covid-19 Surge", "Early Warning", "Alert Algorithm"]</t>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>c("https://wastewater.covidsurge.mathematica.org", "https://covid19.ncdhhs.gov/dashboard/data-behind-dashboards")</t>
+        </is>
+      </c>
+      <c r="AA41">
+        <v>0</v>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>c("WastewaterMonitoring", "Sars-Covid-2", "Covid-19Surge", "EarlyWarning", "AlertAlgorithm")</t>
         </is>
       </c>
     </row>
@@ -3584,11 +3551,6 @@
           <t>North Carolina State University</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q42" t="inlineStr">
         <is>
           <t>0000-0002-5604-8754</t>
@@ -3607,12 +3569,17 @@
           <t>available in online repository</t>
         </is>
       </c>
-      <c r="Z42">
-        <v>1</v>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>["Nonmarket Evaluation", "Water quality", "Urban streams", "Stated preference"]</t>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.7910/DVN/XT3RZ8</t>
+        </is>
+      </c>
+      <c r="AA42">
+        <v>1</v>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>c("NonmarketEvaluation", "Waterquality", "Urbanstreams", "Statedpreference")</t>
         </is>
       </c>
     </row>
@@ -3677,11 +3644,6 @@
           <t>Indiana University</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q43" t="inlineStr">
         <is>
           <t>0000-0002-5468-0713</t>
@@ -3700,12 +3662,17 @@
           <t>available in online repository</t>
         </is>
       </c>
-      <c r="Z43">
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>c("https://scholarworks.iu.edu/dspace/handle/2022/27027", "https://scholarworks.iu.edu/dspace/handle/2022/25638")</t>
+        </is>
+      </c>
+      <c r="AA43">
         <v>5</v>
       </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>["Drinking water", "Children", "Lead exposure", "</t>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>c("Drinkingwater", "Children", "Leadexposure")</t>
         </is>
       </c>
     </row>
@@ -3770,11 +3737,6 @@
           <t>University of North Carolina</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q44" t="inlineStr">
         <is>
           <t>0000-0002-3317-7318</t>
@@ -3783,12 +3745,12 @@
       <c r="W44" t="b">
         <v>0</v>
       </c>
-      <c r="Z44">
+      <c r="AA44">
         <v>2</v>
       </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>["Faecal Sludge Treatment", "Composting", "Temperature-time critera", "pathogen inactivation mechanism", "compost sanitation"]</t>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>c("FaecalSludgeTreatment", "Composting", "Temperature-timecritera", "pathogeninactivationmechanism", "compostsanitation")</t>
         </is>
       </c>
     </row>
@@ -3853,11 +3815,6 @@
           <t>East Carolina University</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q45" t="inlineStr">
         <is>
           <t>0000-0003-2315-7062</t>
@@ -3866,12 +3823,12 @@
       <c r="W45" t="b">
         <v>0</v>
       </c>
-      <c r="Z45">
-        <v>0</v>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>["Hazard mitigation", "compound event", "flooding", "rural resilience", "climate change"]</t>
+      <c r="AA45">
+        <v>0</v>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>c("Hazardmitigation", "compoundevent", "flooding", "ruralresilience", "climatechange")</t>
         </is>
       </c>
     </row>
@@ -3936,11 +3893,6 @@
           <t>North Carolina State University</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q46" t="inlineStr">
         <is>
           <t>0000-0003-3160-5363</t>
@@ -3949,12 +3901,12 @@
       <c r="W46" t="b">
         <v>0</v>
       </c>
-      <c r="Z46">
+      <c r="AA46">
         <v>3</v>
       </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>["Environmental justive", "Ambient water quality", "Interfaces with society"]</t>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>c("Environmentaljustive", "Ambientwaterquality", "Interfaceswithsociety")</t>
         </is>
       </c>
     </row>
@@ -4019,11 +3971,6 @@
           <t>University of North Carolina</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q47" t="inlineStr">
         <is>
           <t>0000-0002-6982-8768</t>
@@ -4042,12 +3989,17 @@
           <t>available in online repository</t>
         </is>
       </c>
-      <c r="Z47">
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>https://www.hydroshare.org/resource/b9fb89d2539c4e43b51889770f7a81f7</t>
+        </is>
+      </c>
+      <c r="AA47">
         <v>9</v>
       </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>["urban", "nonpoint source", "watershed", "nitrogen", "hydrology", "management"]</t>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>c("urban", "nonpointsource", "watershed", "nitrogen", "hydrology", "management")</t>
         </is>
       </c>
     </row>
@@ -4112,11 +4064,6 @@
           <t>University of Utah</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q48" t="inlineStr">
         <is>
           <t>0000-0002-1174-8458</t>
@@ -4135,12 +4082,17 @@
           <t>available in online repository</t>
         </is>
       </c>
-      <c r="Z48">
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.4211/hs.c169de42e6174baf842a319efe28a75e</t>
+        </is>
+      </c>
+      <c r="AA48">
         <v>2</v>
       </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>["sand hills", "seepage flux", "groundwater", "surface water", "spatial variability", "hydrology"]</t>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>c("sandhills", "seepageflux", "groundwater", "surfacewater", "spatialvariability", "hydrology")</t>
         </is>
       </c>
     </row>
@@ -4205,11 +4157,6 @@
           <t>University of North Carolina</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q49" t="inlineStr">
         <is>
           <t>0000-0002-3078-6716</t>
@@ -4228,12 +4175,17 @@
           <t>available in online repository</t>
         </is>
       </c>
-      <c r="Z49">
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>c("https://github.com/bernardoct/WaterPaths/tree/JLWTPAgreementsModel", "https://www.hydroshare.org/resource/3fc8e01960d948a2bd38189dd4e7fa69")</t>
+        </is>
+      </c>
+      <c r="AA49">
         <v>5</v>
       </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>["water utility", "cooperation", "demand", "deep uncertainty", "optimization", "financial risk"]</t>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>c("waterutility", "cooperation", "demand", "deepuncertainty", "optimization", "financialrisk")</t>
         </is>
       </c>
     </row>
@@ -4298,11 +4250,6 @@
           <t>University of North Carolina</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q50" t="inlineStr">
         <is>
           <t>0000-0002-0921-0384</t>
@@ -4321,12 +4268,17 @@
           <t>available in online repository</t>
         </is>
       </c>
-      <c r="Z50">
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>c("https://github.com/acgold/HTF-on-roads", "https://doi.org/10.5281/zenodo.5562568")</t>
+        </is>
+      </c>
+      <c r="AA50">
         <v>6</v>
       </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>["coastal development", "stormwater management", "infrastructure", "inundation modeling", "high-tide flooding"]</t>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>c("coastaldevelopment", "stormwatermanagement", "infrastructure", "inundationmodeling", "high-tideflooding")</t>
         </is>
       </c>
     </row>
@@ -4391,11 +4343,6 @@
           <t>North Carolina State University</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q51" t="inlineStr">
         <is>
           <t>0000-0001-6115-6322</t>
@@ -4411,15 +4358,15 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>available in online repository</t>
-        </is>
-      </c>
-      <c r="Z51">
+          <t>in paper or supp</t>
+        </is>
+      </c>
+      <c r="AA51">
         <v>6</v>
       </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>["erosion", "land-use change", "legacy sediment", "slope-area treshold". "soil nutrients", "stream channel initiation"]</t>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>c("erosion", "land-usechange", "legacysediment", "slope-areatreshold", ".", "soilnutrients", "streamchannelinitiation")</t>
         </is>
       </c>
     </row>
@@ -4458,6 +4405,9 @@
       <c r="H52" t="b">
         <v>0</v>
       </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
       <c r="L52">
         <v>3</v>
       </c>
@@ -4471,11 +4421,6 @@
           <t>University of Georgia</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q52" t="inlineStr">
         <is>
           <t>0000-0003-2112-3846</t>
@@ -4484,13 +4429,12 @@
       <c r="W52" t="b">
         <v>0</v>
       </c>
-      <c r="Z52">
+      <c r="AA52">
         <v>4</v>
       </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">["collaborative governance", "policy beliefs", "regional water planning", "Gobernanza colaborativa", "creencias políticas", "planificación regional del agua", "协作治理", " 政策信念", "区域水资源规划"]
-</t>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>c("collaborativegovernance", "policybeliefs", "regionalwaterplanning", "Gobernanzacolaborativa", "creenciaspolíticas", "planificaciónregionaldelagua", "协作治理", "政策信念", "区域水资源规划")</t>
         </is>
       </c>
     </row>
@@ -4557,29 +4501,29 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>0000-0001-7369-0709</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Frank A. Leibfarth</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>University of North Carolina</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>0000-0001-7369-0709</t>
-        </is>
-      </c>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>Frank A. Leibfarth</t>
-        </is>
-      </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>University of North Carolina</t>
-        </is>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="V53" t="inlineStr">
         <is>
           <t>0000-0001-7737-0331</t>
@@ -4588,7 +4532,7 @@
       <c r="W53" t="b">
         <v>0</v>
       </c>
-      <c r="Z53">
+      <c r="AA53">
         <v>3</v>
       </c>
     </row>
@@ -4627,6 +4571,9 @@
       <c r="H54" t="b">
         <v>0</v>
       </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
       <c r="L54">
         <v>5</v>
       </c>
@@ -4640,11 +4587,6 @@
           <t>Davidson College</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q54" t="inlineStr">
         <is>
           <t>0000-0002-3799-5019</t>
@@ -4663,9 +4605,14 @@
           <t>available in online repository</t>
         </is>
       </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>["biology-geology feebacks", "DMQ99", "evapotranspiration", "headwater streams", "land use change", "seasonal flashiness", "specific conductance", "stream gauges"]</t>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>https://www.hydroshare.org/resource/957475e1101346a6a1cbbb62f17e747d</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>c("biology-geologyfeebacks", "DMQ99", "evapotranspiration", "headwaterstreams", "landusechange", "seasonalflashiness", "specificconductance", "streamgauges")</t>
         </is>
       </c>
     </row>
@@ -4730,11 +4677,6 @@
           <t>Research Triangle Institute</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q55" t="inlineStr">
         <is>
           <t>0000-0003-3641-737X</t>
@@ -4743,7 +4685,7 @@
       <c r="W55" t="b">
         <v>0</v>
       </c>
-      <c r="Z55">
+      <c r="AA55">
         <v>4</v>
       </c>
     </row>
@@ -4808,11 +4750,6 @@
           <t>Center for Environmental Measurement &amp; Modeling</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q56" t="inlineStr">
         <is>
           <t>0000-0001-6231-9437</t>
@@ -4821,12 +4758,12 @@
       <c r="W56" t="b">
         <v>0</v>
       </c>
-      <c r="Z56">
-        <v>1</v>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>["WASP", "environmental modeling", "nanocopper", "nanomaterials", "freswater"]</t>
+      <c r="AA56">
+        <v>1</v>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>c("WASP", "environmentalmodeling", "nanocopper", "nanomaterials", "freswater")</t>
         </is>
       </c>
     </row>
@@ -4865,6 +4802,9 @@
       <c r="H57" t="b">
         <v>0</v>
       </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
       <c r="L57">
         <v>4</v>
       </c>
@@ -4878,11 +4818,6 @@
           <t>North Carolina State University</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q57" t="inlineStr">
         <is>
           <t>0000-0001-7360-0021</t>
@@ -4891,12 +4826,12 @@
       <c r="W57" t="b">
         <v>0</v>
       </c>
-      <c r="Z57">
-        <v>0</v>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>["health education", "health information needs", "health professionals", "information dissemination", "information literacy", "information seeking behavior", "patient education", "research", "qualitative"]</t>
+      <c r="AA57">
+        <v>0</v>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>c("healtheducation", "healthinformationneeds", "healthprofessionals", "informationdissemination", "informationliteracy", "informationseekingbehavior", "patienteducation", "research", "qualitative")</t>
         </is>
       </c>
     </row>
@@ -4935,6 +4870,9 @@
       <c r="H58" t="b">
         <v>0</v>
       </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
       <c r="L58">
         <v>8</v>
       </c>
@@ -4948,11 +4886,6 @@
           <t>University of California</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q58" t="inlineStr">
         <is>
           <t>0000-0002-3039-9927</t>
@@ -4961,7 +4894,7 @@
       <c r="W58" t="b">
         <v>0</v>
       </c>
-      <c r="Z58">
+      <c r="AA58">
         <v>9</v>
       </c>
     </row>
@@ -5028,24 +4961,24 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Marirosa Molina</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>US EPA</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>Marirosa Molina</t>
-        </is>
-      </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>US EPA</t>
-        </is>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="V59" t="inlineStr">
         <is>
           <t>0000-0002-6373-8374</t>
@@ -5064,12 +4997,12 @@
           <t>on request</t>
         </is>
       </c>
-      <c r="Z59">
+      <c r="AA59">
         <v>2</v>
       </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>["crAssphage", "Municipal untreated wastewater", "Temporal variations", "Spatial variations", "Enteric pathogens correlations", "Bacteria", "And viruses"; "qPCR", "rt-qPCR"]</t>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>c("crAssphage", "Municipaluntreatedwastewater", "Temporalvariations", "Spatialvariations", "Entericpathogenscorrelations", "Bacteria", "Andviruses", ";", "qPCR", "rt-qPCR")</t>
         </is>
       </c>
     </row>
@@ -5108,6 +5041,9 @@
       <c r="H60" t="b">
         <v>0</v>
       </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
       <c r="L60">
         <v>3</v>
       </c>
@@ -5123,24 +5059,24 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Lifeng Zhang</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>North Carolina State University</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>Lifeng Zhang</t>
-        </is>
-      </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>North Carolina State University</t>
-        </is>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="V60" t="inlineStr">
         <is>
           <t>no</t>
@@ -5149,7 +5085,7 @@
       <c r="W60" t="b">
         <v>0</v>
       </c>
-      <c r="Z60">
+      <c r="AA60">
         <v>4</v>
       </c>
     </row>
@@ -5188,6 +5124,9 @@
       <c r="H61" t="b">
         <v>0</v>
       </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
       <c r="L61">
         <v>2</v>
       </c>
@@ -5203,24 +5142,24 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Zhiqiang Deng</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>Louisiana State University</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr">
-        <is>
-          <t>Zhiqiang Deng</t>
-        </is>
-      </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>Louisiana State University</t>
-        </is>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="V61" t="inlineStr">
         <is>
           <t>0000-0002-9245-2826</t>
@@ -5239,12 +5178,12 @@
           <t>on request</t>
         </is>
       </c>
-      <c r="Z61">
-        <v>0</v>
-      </c>
-      <c r="AA61" t="inlineStr">
-        <is>
-          <t>["Artificial Neural Networks", "Genetic programming", "Antedcedent environmental conditions", "Temperature", "Salinity", "Oysters"]</t>
+      <c r="AA61">
+        <v>0</v>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>c("ArtificialNeuralNetworks", "Geneticprogramming", "Antedcedentenvironmentalconditions", "Temperature", "Salinity", "Oysters")</t>
         </is>
       </c>
     </row>
@@ -5309,15 +5248,10 @@
           <t>North Carolina State University</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W62" t="b">
         <v>0</v>
       </c>
-      <c r="Z62">
+      <c r="AA62">
         <v>3</v>
       </c>
     </row>
@@ -5382,11 +5316,6 @@
           <t>Technical University of Denmark</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>Denmark</t>
-        </is>
-      </c>
       <c r="Q63" t="inlineStr">
         <is>
           <t>0000-0001-8813-4019</t>
@@ -5405,12 +5334,18 @@
           <t>available in online repository</t>
         </is>
       </c>
-      <c r="Z63">
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>c("https://www.ebi.ac.uk/ena/browser/view/PRJEB40798", "https://www.ebi.ac.uk/ena/browser/view/PRJEB40816", "https://www.ebi.ac.uk/ena/browser/view/PRJEB40815", "https://www.ebi.ac.uk/ena/browser/view/PRJEB27621", "https://www.ebi.ac.uk/ena/browser/view/PRJEB51229", "https://www.ebi.ac.uk/ena/browser/view/ERP015409", "https://bitbucket.org/genomicepidemiology/resfinder_db", "https://ccb-microbe.cs.uni-saarland.de/plsdb/plasmids/download/", "https://www.arb-silva.de/download/arb-files/", "https://benlangmead.github.io/aws-indexes/k2"
+)</t>
+        </is>
+      </c>
+      <c r="AA63">
         <v>4</v>
       </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>["Antimicrobial resistance", "Metagenomics", "Microbial ecology", "Policy and public health in microbiology"]</t>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>c("Antimicrobialresistance", "Metagenomics", "Microbialecology", "Policyandpublichealthinmicrobiology")</t>
         </is>
       </c>
     </row>
@@ -5475,11 +5410,6 @@
           <t>University of North Carolina</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q64" t="inlineStr">
         <is>
           <t>0000-0002-3445-6589</t>
@@ -5498,12 +5428,12 @@
           <t>on request</t>
         </is>
       </c>
-      <c r="Z64">
+      <c r="AA64">
         <v>2</v>
       </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>["Preterm birth", "Low birth weight", "Adverse birth outcome", "Polluted sites", "Superfund", "Industrial sites"]</t>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>c("Pretermbirth", "Lowbirthweight", "Adversebirthoutcome", "Pollutedsites", "Superfund", "Industrialsites")</t>
         </is>
       </c>
     </row>
@@ -5570,29 +5500,29 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>0000-0002-8185-2082</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>Antonio B. Rodriguez</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>University of North Carolina</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>0000-0002-8185-2082</t>
-        </is>
-      </c>
-      <c r="R65" t="inlineStr">
-        <is>
-          <t>Antonio B. Rodriguez</t>
-        </is>
-      </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>University of North Carolina</t>
-        </is>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="V65" t="inlineStr">
         <is>
           <t>0000-0001-6578-5118</t>
@@ -5611,12 +5541,17 @@
           <t>available in online repository</t>
         </is>
       </c>
-      <c r="Z65">
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.6084/m9.figshare.20137649.v265</t>
+        </is>
+      </c>
+      <c r="AA65">
         <v>2</v>
       </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>["Carbon cycle", "Climate-change mitigation", "Environmental impact"]</t>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>c("Carboncycle", "Climate-changemitigation", "Environmentalimpact")</t>
         </is>
       </c>
     </row>
@@ -5683,24 +5618,24 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>Eric M. V. Hoek</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>University of California</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr">
-        <is>
-          <t>Eric M. V. Hoek</t>
-        </is>
-      </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>University of California</t>
-        </is>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="V66" t="inlineStr">
         <is>
           <t>0000-0002-9674-1916</t>
@@ -5716,15 +5651,15 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>no datasets were generated during the study</t>
-        </is>
-      </c>
-      <c r="Z66">
+          <t>no data generated</t>
+        </is>
+      </c>
+      <c r="AA66">
         <v>40</v>
       </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>["Chemical Engineering", "Water resources"]</t>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>c("ChemicalEngineering", "Waterresources")</t>
         </is>
       </c>
     </row>
@@ -5789,11 +5724,6 @@
           <t>USDA-ARS</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q67" t="inlineStr">
         <is>
           <t>0000-0002-0176-7815</t>
@@ -5813,12 +5743,17 @@
           <t>available in online repository</t>
         </is>
       </c>
-      <c r="Z67">
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>c("https://github.com/TransformingDrainageProject/Drain-Flow-Gap-Filling", "https://github.com/isudatateam/datateam")</t>
+        </is>
+      </c>
+      <c r="AA67">
         <v>2</v>
       </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>["Agriculture", "Environmental impact", "Hydrology", "Water resources"]</t>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>c("Agriculture", "Environmentalimpact", "Hydrology", "Waterresources")</t>
         </is>
       </c>
     </row>
@@ -5885,7 +5820,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -5906,7 +5841,7 @@
       <c r="W68" t="b">
         <v>0</v>
       </c>
-      <c r="Z68">
+      <c r="AA68">
         <v>0</v>
       </c>
     </row>
@@ -5973,24 +5908,24 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>Megan Mullin</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>Nicholas School of the Environment, Duke University, Durham, NC, United States of America</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="R69" t="inlineStr">
-        <is>
-          <t>Megan Mullin</t>
-        </is>
-      </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>Nicholas School of the Environment, Duke University, Durham, NC, United States of America</t>
-        </is>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="V69" t="inlineStr">
         <is>
           <t>0000-0002-1936-802X</t>
@@ -5999,7 +5934,7 @@
       <c r="W69" t="b">
         <v>0</v>
       </c>
-      <c r="Z69">
+      <c r="AA69">
         <v>5</v>
       </c>
     </row>
@@ -6043,7 +5978,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>docx &amp; tif</t>
+          <t>c("docx", "tif")</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -6064,11 +5999,6 @@
           <t>Department of Biological &amp; Agricultural Engineering, NC State University, Raleigh, NC, United States of America</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q70" t="inlineStr">
         <is>
           <t>0000-0002-5366-1166</t>
@@ -6087,7 +6017,12 @@
           <t>available in online repository</t>
         </is>
       </c>
-      <c r="Z70">
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>https://datadryad.org/stash/dataset/doi:10.5061/dryad.2v6wwpzqk</t>
+        </is>
+      </c>
+      <c r="AA70">
         <v>5</v>
       </c>
     </row>
@@ -6152,11 +6087,6 @@
           <t>Nelson Mandela African Institution of Science and Technology, Arusha, Tanzania</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>Tanzania</t>
-        </is>
-      </c>
       <c r="Q71" t="inlineStr">
         <is>
           <t>0000-0003-1693-8098</t>
@@ -6175,7 +6105,12 @@
           <t>available in online repository</t>
         </is>
       </c>
-      <c r="Z71">
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>https://datadryad.org/stash/share/cBZAwC2jJmpnJR1evI7aa98YECL7xm6gN4rL-X6_LXk</t>
+        </is>
+      </c>
+      <c r="AA71">
         <v>0</v>
       </c>
     </row>
@@ -6242,33 +6177,33 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>0000-0002-9648-4948</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>Rachel T. Noble</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>Department of Earth, Marine, and Environmental Sciences, Institute of Marine Science, University of North Carolina at Chapel Hill, Morehead City, North Carolina, United States of America</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>0000-0002-9648-4948</t>
-        </is>
-      </c>
-      <c r="R72" t="inlineStr">
-        <is>
-          <t>Rachel T. Noble</t>
-        </is>
-      </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>Department of Earth, Marine, and Environmental Sciences, Institute of Marine Science, University of North Carolina at Chapel Hill, Morehead City, North Carolina, United States of America</t>
-        </is>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W72" t="b">
         <v>0</v>
       </c>
-      <c r="Z72">
+      <c r="AA72">
         <v>17</v>
       </c>
     </row>
@@ -6333,11 +6268,6 @@
           <t>Environmental Intervention Unit, Infectious Disease Division, icddr,b, Dhaka, Bangladesh</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>Bangladesh</t>
-        </is>
-      </c>
       <c r="Q73" t="inlineStr">
         <is>
           <t>0000-0003-0520-2683</t>
@@ -6346,7 +6276,7 @@
       <c r="W73" t="b">
         <v>0</v>
       </c>
-      <c r="Z73">
+      <c r="AA73">
         <v>1</v>
       </c>
     </row>
@@ -6413,38 +6343,38 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>0000-0002-1358-5138</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>Mark D. Sobsey</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>Department of Environmental Sciences and Engineering, Gillings School of Global Public Health, The University of North Carolina at Chapel Hill, 135 Dauer Drive, CB#7431, Chapel Hill, North Carolina 27599, United States</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>0000-0002-1358-5138</t>
-        </is>
-      </c>
-      <c r="R74" t="inlineStr">
-        <is>
-          <t>Mark D. Sobsey</t>
-        </is>
-      </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>Department of Environmental Sciences and Engineering, Gillings School of Global Public Health, The University of North Carolina at Chapel Hill, 135 Dauer Drive, CB#7431, Chapel Hill, North Carolina 27599, United States</t>
-        </is>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W74" t="b">
         <v>0</v>
       </c>
-      <c r="Z74">
-        <v>0</v>
-      </c>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>["Cryptosporidium", "Bacillus spores", "MS2 coliphage", "bromine", "chlorine", "disinfection", "water treatment"]</t>
+      <c r="AA74">
+        <v>0</v>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>c("Cryptosporidium", "Bacillusspores", "MS2coliphage", "bromine", "chlorine", "disinfection", "watertreatment")</t>
         </is>
       </c>
     </row>
@@ -6511,29 +6441,29 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>0000-0001-9686-0416</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>Detlef R.U. Knappe</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>Department of Civil, Construction, and Environmental Engineering, North Carolina State University, Raleigh, North Carolina 27695, United States</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>0000-0001-9686-0416</t>
-        </is>
-      </c>
-      <c r="R75" t="inlineStr">
-        <is>
-          <t>Detlef R.U. Knappe</t>
-        </is>
-      </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>Department of Civil, Construction, and Environmental Engineering, North Carolina State University, Raleigh, North Carolina 27695, United States</t>
-        </is>
-      </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="V75" t="inlineStr">
         <is>
           <t>0000-0003-1315-1791</t>
@@ -6542,12 +6472,12 @@
       <c r="W75" t="b">
         <v>0</v>
       </c>
-      <c r="Z75">
-        <v>0</v>
-      </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>["PFAS destruction", "fluoroethers", "GenX", "Nafion byproduct 2", "photolysis"]</t>
+      <c r="AA75">
+        <v>0</v>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>c("PFASdestruction", "fluoroethers", "GenX", "Nafionbyproduct2", "photolysis")</t>
         </is>
       </c>
     </row>
@@ -6614,29 +6544,29 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>0000-0002-0921-0384</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>Katherine Anarde</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>Department of Civil, Construction, and Environmental Engineering, North Carolina State University, Raleigh, NC, USA</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>0000-0002-0921-0384</t>
-        </is>
-      </c>
-      <c r="R76" t="inlineStr">
-        <is>
-          <t>Katherine Anarde</t>
-        </is>
-      </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>Department of Civil, Construction, and Environmental Engineering, North Carolina State University, Raleigh, NC, USA</t>
-        </is>
-      </c>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="V76" t="inlineStr">
         <is>
           <t>0000-0003-2586-0587</t>
@@ -6655,12 +6585,17 @@
           <t>available in online repository</t>
         </is>
       </c>
-      <c r="Z76">
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>c("https://doi.org/10.5281/zenodo.7135955", "https://sunnydayflood.apps.cloudapps.unc.edu", "https://github.com/sunny-day-flooding-project", "https://doi.org/10.5281/zenodo.7017187")</t>
+        </is>
+      </c>
+      <c r="AA76">
         <v>2</v>
       </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>["coastal flooding", "low-cost sensors", "high tide flooding", "stormwater management", "coastal infrastructure", "sea level rise"]</t>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>c("coastalflooding", "low-costsensors", "hightideflooding", "stormwatermanagement", "coastalinfrastructure", "sealevelrise")</t>
         </is>
       </c>
     </row>
@@ -6704,7 +6639,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>docx &amp; csv</t>
+          <t>c("docx", "csv")</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -6725,11 +6660,6 @@
           <t>Nicholas Institute for Energy, Environment and Sustainability, Duke University, Durham, North Carolina, United States of America</t>
         </is>
       </c>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q77" t="inlineStr">
         <is>
           <t>0000-0002-7512-7845</t>
@@ -6738,7 +6668,7 @@
       <c r="W77" t="b">
         <v>0</v>
       </c>
-      <c r="Z77">
+      <c r="AA77">
         <v>0</v>
       </c>
     </row>
@@ -6782,7 +6712,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>xlsx &amp; docx</t>
+          <t>c("xlsx", "docx")</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -6803,11 +6733,6 @@
           <t>Natural Resources Defense Council, 111 Sutter St. Floor 20, San Francisco, CA 94104, USA</t>
         </is>
       </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="R78" t="inlineStr">
         <is>
           <t>Anna Reade</t>
@@ -6831,12 +6756,12 @@
           <t>on request</t>
         </is>
       </c>
-      <c r="Z78">
+      <c r="AA78">
         <v>8</v>
       </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>["PFAS", "Drinking water", "US EPA", "PFPrA", "Ultra-short chain"]</t>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>c("PFAS", "Drinkingwater", "USEPA", "PFPrA", "Ultra-shortchain")</t>
         </is>
       </c>
     </row>
@@ -6901,11 +6826,6 @@
           <t>Department of Health Education and Promotion, East Carolina University, Greenville, NC 27858, USA</t>
         </is>
       </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q79" t="inlineStr">
         <is>
           <t>0000-0003-2664-4763</t>
@@ -6924,12 +6844,12 @@
           <t>on request</t>
         </is>
       </c>
-      <c r="Z79">
-        <v>0</v>
-      </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>["coastal", "fecal bacteria", "runoff", "stormwater"]</t>
+      <c r="AA79">
+        <v>0</v>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>c("coastal", "fecalbacteria", "runoff", "stormwater")</t>
         </is>
       </c>
     </row>
@@ -6994,11 +6914,6 @@
           <t>Center for Marine Sciences, University of North Carolina Wilmington, 5600 Marvin K. Moss Ln., Wilmington, NC 28409, USA</t>
         </is>
       </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q80" t="inlineStr">
         <is>
           <t>0000-0001-8701-7654</t>
@@ -7017,12 +6932,12 @@
           <t>on request</t>
         </is>
       </c>
-      <c r="Z80">
-        <v>0</v>
-      </c>
-      <c r="AA80" t="inlineStr">
-        <is>
-          <t>["cyanobacteria", "cyanotoxin", "microcystin", "stormwater pollution", "eutrophication"]</t>
+      <c r="AA80">
+        <v>0</v>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>c("cyanobacteria", "cyanotoxin", "microcystin", "stormwaterpollution", "eutrophication")</t>
         </is>
       </c>
     </row>
@@ -7061,6 +6976,9 @@
       <c r="H81" t="b">
         <v>0</v>
       </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
       <c r="L81">
         <v>4</v>
       </c>
@@ -7074,11 +6992,6 @@
           <t>CIEPQPF, Department of Chemical Engineering, University of Coimbra, 3030-790 Coimbra, Portugal</t>
         </is>
       </c>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
       <c r="Q81" t="inlineStr">
         <is>
           <t>0000-0002-0944-8632</t>
@@ -7087,12 +7000,12 @@
       <c r="W81" t="b">
         <v>0</v>
       </c>
-      <c r="Z81">
+      <c r="AA81">
         <v>8</v>
       </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>["water scarcity", "water recycling", "wastewater treatment plants", "nutrients", "phosphorus"]</t>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>c("waterscarcity", "waterrecycling", "wastewatertreatmentplants", "nutrients", "phosphorus")</t>
         </is>
       </c>
     </row>
@@ -7159,29 +7072,29 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>0000-0002-8025-3731</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>Emily S. Bailey</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>Department of Public Health, College of Pharmacy &amp; Health Sciences, Campbell University, Buies Creek, NC 27506, USA</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>0000-0002-8025-3731</t>
-        </is>
-      </c>
-      <c r="R82" t="inlineStr">
-        <is>
-          <t>Emily S. Bailey</t>
-        </is>
-      </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>Department of Public Health, College of Pharmacy &amp; Health Sciences, Campbell University, Buies Creek, NC 27506, USA</t>
-        </is>
-      </c>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="V82" t="inlineStr">
         <is>
           <t>0000-0003-1292-0771</t>
@@ -7200,12 +7113,12 @@
           <t>on request</t>
         </is>
       </c>
-      <c r="Z82">
+      <c r="AA82">
         <v>3</v>
       </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>["HWTS", "POU", "chitosan", "coagulation", "sand filtration", "bacterial reduction", "virus reduction"]</t>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>c("HWTS", "POU", "chitosan", "coagulation", "sandfiltration", "bacterialreduction", "virusreduction")</t>
         </is>
       </c>
     </row>
@@ -7244,6 +7157,9 @@
       <c r="H83" t="b">
         <v>0</v>
       </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
       <c r="L83">
         <v>4</v>
       </c>
@@ -7259,29 +7175,29 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>0000-0001-5895-5318</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>Rebecca C. Fry</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>Department of Environmental Health Sciences and Engineering, Gillings School of Global Public Health, University of North Carolina at Chapel Hill, Chapel Hill, NC 27599, USA</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="Q83" t="inlineStr">
-        <is>
-          <t>0000-0001-5895-5318</t>
-        </is>
-      </c>
-      <c r="R83" t="inlineStr">
-        <is>
-          <t>Rebecca C. Fry</t>
-        </is>
-      </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>Department of Environmental Health Sciences and Engineering, Gillings School of Global Public Health, University of North Carolina at Chapel Hill, Chapel Hill, NC 27599, USA</t>
-        </is>
-      </c>
-      <c r="T83" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W83" t="b">
         <v>1</v>
       </c>
@@ -7295,12 +7211,17 @@
           <t>available in online repository</t>
         </is>
       </c>
-      <c r="Z83">
-        <v>1</v>
-      </c>
-      <c r="AA83" t="inlineStr">
-        <is>
-          <t>["environmental justice", "private wells", "toxic metals"]</t>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.15139/S3/BDQG9O</t>
+        </is>
+      </c>
+      <c r="AA83">
+        <v>1</v>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>c("environmentaljustice", "privatewells", "toxicmetals")</t>
         </is>
       </c>
     </row>
@@ -7339,6 +7260,9 @@
       <c r="H84" t="b">
         <v>0</v>
       </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
       <c r="L84">
         <v>2</v>
       </c>
@@ -7352,20 +7276,15 @@
           <t>Department of Computer Science, San Francisco State University, 1600 Holloway Ave, San Francisco, CA 94132, USA</t>
         </is>
       </c>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W84" t="b">
         <v>0</v>
       </c>
-      <c r="Z84">
-        <v>1</v>
-      </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>["explainability", "LSP method", "water quality", "decision-making"]</t>
+      <c r="AA84">
+        <v>1</v>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>c("explainability", "LSPmethod", "waterquality", "decision-making")</t>
         </is>
       </c>
     </row>
@@ -7430,11 +7349,6 @@
           <t>Department of Earth and Ocean Sciences, University of North Carolina Wilmington, 601 S College Rd., Wilmington, NC 28403, USA</t>
         </is>
       </c>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q85" t="inlineStr">
         <is>
           <t>0000-0002-6591-7237</t>
@@ -7453,12 +7367,17 @@
           <t>available in online repository</t>
         </is>
       </c>
-      <c r="Z85">
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>c("https://coast.noaa.gov/slrdata/", "https://coast.noaa.gov/slrdata/", "https://fris.nc.gov/fris/Home.aspx?ST=NC", "https://earthexplorer.usgs.gov/", "https://deq.nc.gov/about/divisions/coastal", "https://www.nconemap.gov/pages/parcels")</t>
+        </is>
+      </c>
+      <c r="AA85">
         <v>2</v>
       </c>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>["wetlands", "nature-based solutions", "flood mitigation", "coastal flooding", "tidal watersheds"]</t>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>c("wetlands", "nature-basedsolutions", "floodmitigation", "coastalflooding", "tidalwatersheds")</t>
         </is>
       </c>
     </row>
@@ -7523,11 +7442,6 @@
           <t>Department of Environmental Sciences and Engineering, Gillings School of Global Public Health, The University of North Carolina at Chapel Hill, Chapel Hill, NC 27599, USA</t>
         </is>
       </c>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q86" t="inlineStr">
         <is>
           <t>0000-0003-1292-0771</t>
@@ -7546,12 +7460,12 @@
           <t>on request</t>
         </is>
       </c>
-      <c r="Z86">
-        <v>1</v>
-      </c>
-      <c r="AA86" t="inlineStr">
-        <is>
-          <t>["reclaimed water", "water reuse", "water-supply systems", "agro-wastewater", "risk assessment"]</t>
+      <c r="AA86">
+        <v>1</v>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>c("reclaimedwater", "waterreuse", "water-supplysystems", "agro-wastewater", "riskassessment")</t>
         </is>
       </c>
     </row>
@@ -7590,6 +7504,9 @@
       <c r="H87" t="b">
         <v>0</v>
       </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
       <c r="L87">
         <v>8</v>
       </c>
@@ -7605,24 +7522,24 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>Meredith Hovis</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>Department of Forestry and Environmental Resources, North Carolina State University, Raleigh, NC 27695, USA</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="R87" t="inlineStr">
-        <is>
-          <t>Meredith Hovis</t>
-        </is>
-      </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>Department of Forestry and Environmental Resources, North Carolina State University, Raleigh, NC 27695, USA</t>
-        </is>
-      </c>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W87" t="b">
         <v>1</v>
       </c>
@@ -7636,12 +7553,17 @@
           <t>available in online repository</t>
         </is>
       </c>
-      <c r="Z87">
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>c("https://www.nconemap.gov/", "https://www.nrcs.usda.gov/wps/portal/nrcs/detail/soils/survey/geo/?cid=nrcs142p2_053628", "https://www.nconemap.gov/", "https://www.nconemap.gov/")</t>
+        </is>
+      </c>
+      <c r="AA87">
         <v>4</v>
       </c>
-      <c r="AA87" t="inlineStr">
-        <is>
-          <t>["geospatial analysis", "land suitability", "flood mitigation", "nature-based solutions (NBS)", "rural landscapes", "Geographic Information Systems (GIS)", "flood resilience"]</t>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>c("geospatialanalysis", "landsuitability", "floodmitigation", "nature-basedsolutions(NBS)", "rurallandscapes", "GeographicInformationSystems(GIS)", "floodresilience")</t>
         </is>
       </c>
     </row>
@@ -7706,11 +7628,6 @@
           <t>Department of Environmental Sciences and Engineering, Gillings School of Global Public Health, The University of North Carolina at Chapel Hill, Chapel Hill, NC 27599, USA</t>
         </is>
       </c>
-      <c r="O88" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q88" t="inlineStr">
         <is>
           <t>0000-0003-1292-0771</t>
@@ -7729,12 +7646,12 @@
           <t>on request</t>
         </is>
       </c>
-      <c r="Z88">
-        <v>1</v>
-      </c>
-      <c r="AA88" t="inlineStr">
-        <is>
-          <t>["reclaimed water", "water reuse", "water-supply systems", "agro-wastewater", "risk assessment"]</t>
+      <c r="AA88">
+        <v>1</v>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>c("reclaimedwater", "waterreuse", "water-supplysystems", "agro-wastewater", "riskassessment")</t>
         </is>
       </c>
     </row>
@@ -7799,11 +7716,6 @@
           <t>Department of Health Education and Promotion, East Carolina University, Greenville, NC 27858, USA</t>
         </is>
       </c>
-      <c r="O89" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q89" t="inlineStr">
         <is>
           <t>0000-0003-2664-4763</t>
@@ -7822,12 +7734,12 @@
           <t>on request</t>
         </is>
       </c>
-      <c r="Z89">
+      <c r="AA89">
         <v>2</v>
       </c>
-      <c r="AA89" t="inlineStr">
-        <is>
-          <t>["coastal", "eutrophication septic systems"]</t>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>c("coastal", "eutrophicationsepticsystems")</t>
         </is>
       </c>
     </row>
@@ -7866,6 +7778,9 @@
       <c r="H90" t="b">
         <v>0</v>
       </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
       <c r="L90">
         <v>3</v>
       </c>
@@ -7879,20 +7794,15 @@
           <t>Department of Geosciences, Mississippi State University, Mississippi State, MS 39762, USA</t>
         </is>
       </c>
-      <c r="O90" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W90" t="b">
         <v>0</v>
       </c>
-      <c r="Z90">
+      <c r="AA90">
         <v>8</v>
       </c>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>["hydrologic drought", "Southeast US", "National Water Model"]</t>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>c("hydrologicdrought", "SoutheastUS", "NationalWaterModel")</t>
         </is>
       </c>
     </row>
@@ -7957,11 +7867,6 @@
           <t>Department of Environmental, Agricultural, and Occupational Health, College of Public Health, University of Nebraska Medical Center, Omaha, NE 68198, USA</t>
         </is>
       </c>
-      <c r="O91" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q91" t="inlineStr">
         <is>
           <t>0000-0003-1143-1191</t>
@@ -7980,12 +7885,17 @@
           <t>available in online repository</t>
         </is>
       </c>
-      <c r="Z91">
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>c("https://www.census.gov/data/developers/data-sets/acs-5year.html", "https://www.epa.gov/ground-water-and-drinking-water/safe-drinking-water-information-system-sdwis-federal-reporting")</t>
+        </is>
+      </c>
+      <c r="AA91">
         <v>2</v>
       </c>
-      <c r="AA91" t="inlineStr">
-        <is>
-          <t>["drought and health", "drought risk", "Local Moran's I", "drought vulnerability", "U.S. drought"]</t>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>c("droughtandhealth", "droughtrisk", "LocalMoran", "sI", "droughtvulnerability", "U.S.drought")</t>
         </is>
       </c>
     </row>
@@ -8050,11 +7960,6 @@
           <t>Department of City and Regional Planning, University of North Carolina at Chapel Hill, Chapel Hill, NC 27599, USA</t>
         </is>
       </c>
-      <c r="O92" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q92" t="inlineStr">
         <is>
           <t>0000-0002-2834-3764</t>
@@ -8063,12 +7968,12 @@
       <c r="W92" t="b">
         <v>0</v>
       </c>
-      <c r="Z92">
-        <v>0</v>
-      </c>
-      <c r="AA92" t="inlineStr">
-        <is>
-          <t>["environmental planning", "policy evaluation", "riparian buffers"]</t>
+      <c r="AA92">
+        <v>0</v>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>c("environmentalplanning", "policyevaluation", "riparianbuffers")</t>
         </is>
       </c>
     </row>
@@ -8133,11 +8038,6 @@
           <t>Earth and Climate Sciences, Nicholas School of the Environment, Duke University, Durham, NC 27708, USA</t>
         </is>
       </c>
-      <c r="O93" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q93" t="inlineStr">
         <is>
           <t>0000-0001-5793-8583</t>
@@ -8156,12 +8056,17 @@
           <t>available in online repository</t>
         </is>
       </c>
-      <c r="Z93">
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>https://github.com/hkqcqq/CoastalWetlandDetection.git</t>
+        </is>
+      </c>
+      <c r="AA93">
         <v>6</v>
       </c>
-      <c r="AA93" t="inlineStr">
-        <is>
-          <t>["coastal wetland degradation", "remote sensing", "NDVI", "climate change", "sea-level rise", "saltwater intrusion", "hydrologic model", "Alligator River National Wildlife Refuge", "USA"]</t>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>c("coastalwetlanddegradation", "remotesensing", "NDVI", "climatechange", "sea-levelrise", "saltwaterintrusion", "hydrologicmodel", "AlligatorRiverNationalWildlifeRefuge", "USA")</t>
         </is>
       </c>
     </row>
@@ -8200,6 +8105,9 @@
       <c r="H94" t="b">
         <v>0</v>
       </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
       <c r="L94">
         <v>2</v>
       </c>
@@ -8215,24 +8123,24 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>Elizabeth A. Mack</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>Department of Geography, Environment, and Spatial Sciences, Michigan State University, 673 Auditorium Rd, East Lansing, MI 48824, USA</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="R94" t="inlineStr">
-        <is>
-          <t>Elizabeth A. Mack</t>
-        </is>
-      </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>Department of Geography, Environment, and Spatial Sciences, Michigan State University, 673 Auditorium Rd, East Lansing, MI 48824, USA</t>
-        </is>
-      </c>
-      <c r="T94" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W94" t="b">
         <v>1</v>
       </c>
@@ -8246,12 +8154,17 @@
           <t>available in online repository</t>
         </is>
       </c>
-      <c r="Z94">
-        <v>1</v>
-      </c>
-      <c r="AA94" t="inlineStr">
-        <is>
-          <t>["water infrastructure", "water services", "water utilities", "water bills", "billing frequency", "customer assistance programs (CAPS)", "affordability"]</t>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.7910/DVN/0ETQ74</t>
+        </is>
+      </c>
+      <c r="AA94">
+        <v>1</v>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>c("waterinfrastructure", "waterservices", "waterutilities", "waterbills", "billingfrequency", "customerassistanceprograms(CAPS)", "affordability")</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8208,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>pdf &amp; xlsx</t>
+          <t>c("pdf", "xlsx")</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -8316,11 +8229,6 @@
           <t>Center for Environmental and Health Effects of PFAS, Department of Biological Sciences, North Carolina State University, Raleigh, North Carolina 27695, United States</t>
         </is>
       </c>
-      <c r="O95" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q95" t="inlineStr">
         <is>
           <t>0000-0003-2954-1110</t>
@@ -8329,12 +8237,12 @@
       <c r="W95" t="b">
         <v>0</v>
       </c>
-      <c r="Z95">
-        <v>0</v>
-      </c>
-      <c r="AA95" t="inlineStr">
-        <is>
-          <t>["canine", "drinking water", "equine", "fluoroether", "One Health", "nafion by-product 2", "GenX chemicals", "PFOA", "PFOS"]</t>
+      <c r="AA95">
+        <v>0</v>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>c("canine", "drinkingwater", "equine", "fluoroether", "OneHealth", "nafionby-product2", "GenXchemicals", "PFOA", "PFOS")</t>
         </is>
       </c>
     </row>
@@ -8373,6 +8281,9 @@
       <c r="H96" t="b">
         <v>0</v>
       </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
       <c r="L96">
         <v>16</v>
       </c>
@@ -8386,11 +8297,6 @@
           <t>Department of Biological Sciences, North Carolina State University, Raleigh, North Carolina 27695, United States</t>
         </is>
       </c>
-      <c r="O96" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q96" t="inlineStr">
         <is>
           <t>0000-0002-5289-1218</t>
@@ -8399,12 +8305,12 @@
       <c r="W96" t="b">
         <v>0</v>
       </c>
-      <c r="Z96">
+      <c r="AA96">
         <v>249</v>
       </c>
-      <c r="AA96" t="inlineStr">
-        <is>
-          <t>["drinking water", "fluoropolymers", "food", "safety", "toxins"]</t>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>c("drinkingwater", "fluoropolymers", "food", "safety", "toxins")</t>
         </is>
       </c>
     </row>
@@ -8443,6 +8349,9 @@
       <c r="H97" t="b">
         <v>0</v>
       </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
       <c r="L97">
         <v>4</v>
       </c>
@@ -8459,12 +8368,12 @@
       <c r="W97" t="b">
         <v>0</v>
       </c>
-      <c r="Z97">
-        <v>0</v>
-      </c>
-      <c r="AA97" t="inlineStr">
-        <is>
-          <t>["Air pollution", "Color", "Environmental pollution", "Environmental science", "Impurities"]</t>
+      <c r="AA97">
+        <v>0</v>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>c("Airpollution", "Color", "Environmentalpollution", "Environmentalscience", "Impurities")</t>
         </is>
       </c>
     </row>
@@ -8508,7 +8417,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>pdf &amp; html</t>
+          <t>c("pdf", "html")</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -8529,11 +8438,6 @@
           <t>RTI International, Research Triangle Park, North Carolina 27709, United States</t>
         </is>
       </c>
-      <c r="O98" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q98" t="inlineStr">
         <is>
           <t>0000-0001-6293-3672</t>
@@ -8552,12 +8456,17 @@
           <t>available in online repository</t>
         </is>
       </c>
-      <c r="Z98">
-        <v>1</v>
-      </c>
-      <c r="AA98" t="inlineStr">
-        <is>
-          <t>["lead", "Children's health", "drinking water", "machine learning", "risk assessment"]</t>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5281/zenodo.7477787</t>
+        </is>
+      </c>
+      <c r="AA98">
+        <v>1</v>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>c("lead", "Children", "shealth", "drinkingwater", "machinelearning", "riskassessment")</t>
         </is>
       </c>
     </row>
@@ -8624,29 +8533,29 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>0000-0002-3915-634X</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>Christopher P. Higgins</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>Department of Civil and Environmental Engineering, Colorado School of Mines, Golden, Colorado 80401, United States</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="Q99" t="inlineStr">
-        <is>
-          <t>0000-0002-3915-634X</t>
-        </is>
-      </c>
-      <c r="R99" t="inlineStr">
-        <is>
-          <t>Christopher P. Higgins</t>
-        </is>
-      </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>Department of Civil and Environmental Engineering, Colorado School of Mines, Golden, Colorado 80401, United States</t>
-        </is>
-      </c>
-      <c r="T99" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="V99" t="inlineStr">
         <is>
           <t>0000-0001-6220-8673</t>
@@ -8655,12 +8564,12 @@
       <c r="W99" t="b">
         <v>0</v>
       </c>
-      <c r="Z99">
-        <v>0</v>
-      </c>
-      <c r="AA99" t="inlineStr">
-        <is>
-          <t>["PFAS air-water interfacial adsorption", "QSPR", "nonequilibrium", "unsaturated columns", "pan film"]</t>
+      <c r="AA99">
+        <v>0</v>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>c("PFASair-waterinterfacialadsorption", "QSPR", "nonequilibrium", "unsaturatedcolumns", "panfilm")</t>
         </is>
       </c>
     </row>
@@ -8699,6 +8608,9 @@
       <c r="H100" t="b">
         <v>0</v>
       </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
       <c r="L100">
         <v>3</v>
       </c>
@@ -8714,33 +8626,33 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>Sherine O. Obare</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>Department of Nanoengineering, Joint School of Nanoscience and Nanoengineering, North Carolina A&amp;T State University, Greensboro, North Carolina 27401, United States</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="R100" t="inlineStr">
-        <is>
-          <t>Sherine O. Obare</t>
-        </is>
-      </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>Department of Nanoengineering, Joint School of Nanoscience and Nanoengineering, North Carolina A&amp;T State University, Greensboro, North Carolina 27401, United States</t>
-        </is>
-      </c>
-      <c r="T100" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W100" t="b">
         <v>0</v>
       </c>
-      <c r="Z100">
-        <v>1</v>
-      </c>
-      <c r="AA100" t="inlineStr">
-        <is>
-          <t>["adsorption", "membranes, "molecules", "nanofibers", "remediation"]</t>
+      <c r="AA100">
+        <v>1</v>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>c("adsorption", "molecules", "nanofibers", "remediation")</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8696,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>pdf &amp; xlsx</t>
+          <t>c("pdf", "xlsx")</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -8807,24 +8719,24 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>Erin S. Baker</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>Department of Chemistry, North Carolina State University, Raleigh, North Carolina 27695, United States</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="R101" t="inlineStr">
-        <is>
-          <t>Erin S. Baker</t>
-        </is>
-      </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>Department of Chemistry, North Carolina State University, Raleigh, North Carolina 27695, United States</t>
-        </is>
-      </c>
-      <c r="T101" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="V101" t="inlineStr">
         <is>
           <t>0000-0001-5246-2213</t>
@@ -8833,12 +8745,12 @@
       <c r="W101" t="b">
         <v>0</v>
       </c>
-      <c r="Z101">
-        <v>1</v>
-      </c>
-      <c r="AA101" t="inlineStr">
-        <is>
-          <t>["nontargeted analysis", "anthropogenic chemicals", "wastewater", "landfill leachate", "reverse osmosis"]</t>
+      <c r="AA101">
+        <v>1</v>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>c("nontargetedanalysis", "anthropogenicchemicals", "wastewater", "landfillleachate", "reverseosmosis")</t>
         </is>
       </c>
     </row>
@@ -8905,29 +8817,29 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>0000-0003-3909-9311</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>Alissa Cordner</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>Department of Sociology, Whitman College, Walla Walla, Washington 99362, United States</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="Q102" t="inlineStr">
-        <is>
-          <t>0000-0003-3909-9311</t>
-        </is>
-      </c>
-      <c r="R102" t="inlineStr">
-        <is>
-          <t>Alissa Cordner</t>
-        </is>
-      </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>Department of Sociology, Whitman College, Walla Walla, Washington 99362, United States</t>
-        </is>
-      </c>
-      <c r="T102" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="V102" t="inlineStr">
         <is>
           <t>0000-0001-5223-2848</t>
@@ -8936,12 +8848,12 @@
       <c r="W102" t="b">
         <v>0</v>
       </c>
-      <c r="Z102">
+      <c r="AA102">
         <v>9</v>
       </c>
-      <c r="AA102" t="inlineStr">
-        <is>
-          <t>["per- and polyfluoroalkyl substances (PFAS)", "presumptive contamination", "PFAS testing and investigation", "AFFF", "PFAS waste and disposal"]</t>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>c("per-andpolyfluoroalkylsubstances(PFAS)", "presumptivecontamination", "PFAStestingandinvestigation", "AFFF", "PFASwasteanddisposal")</t>
         </is>
       </c>
     </row>
@@ -8980,6 +8892,9 @@
       <c r="H103" t="b">
         <v>0</v>
       </c>
+      <c r="I103">
+        <v>0</v>
+      </c>
       <c r="L103">
         <v>16</v>
       </c>
@@ -8993,11 +8908,6 @@
           <t>EPCOR Water Services Inc., Edmonton, Alberta T5H 0E8, Canada</t>
         </is>
       </c>
-      <c r="O103" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
       <c r="Q103" t="inlineStr">
         <is>
           <t>0000-0001-9488-8124</t>
@@ -9006,12 +8916,12 @@
       <c r="W103" t="b">
         <v>0</v>
       </c>
-      <c r="Z103">
-        <v>0</v>
-      </c>
-      <c r="AA103" t="inlineStr">
-        <is>
-          <t>["anatomy", "genetics", "infectious diseases", "viruses", "wastewater"]</t>
+      <c r="AA103">
+        <v>0</v>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>c("anatomy", "genetics", "infectiousdiseases", "viruses", "wastewater")</t>
         </is>
       </c>
     </row>
@@ -9078,24 +8988,24 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>Avner Vengosh</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>Nicholas School of the Environment, Duke University, Durham, North Carolina 27708, United States</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="R104" t="inlineStr">
-        <is>
-          <t>Avner Vengosh</t>
-        </is>
-      </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>Nicholas School of the Environment, Duke University, Durham, North Carolina 27708, United States</t>
-        </is>
-      </c>
-      <c r="T104" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="V104" t="inlineStr">
         <is>
           <t>0000-0001-8928-0157</t>
@@ -9104,12 +9014,12 @@
       <c r="W104" t="b">
         <v>0</v>
       </c>
-      <c r="Z104">
+      <c r="AA104">
         <v>4</v>
       </c>
-      <c r="AA104" t="inlineStr">
-        <is>
-          <t>["coal ash", "lacustrine sediment", "multiproxy tracing", "aquatic ecosystems"]</t>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>c("coalash", "lacustrinesediment", "multiproxytracing", "aquaticecosystems")</t>
         </is>
       </c>
     </row>
@@ -9148,6 +9058,9 @@
       <c r="H105" t="b">
         <v>0</v>
       </c>
+      <c r="I105">
+        <v>0</v>
+      </c>
       <c r="L105">
         <v>8</v>
       </c>
@@ -9161,11 +9074,6 @@
           <t>Department of Anthropology, University of South Florida, Tampa, Florida 33620, United States</t>
         </is>
       </c>
-      <c r="O105" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q105" t="inlineStr">
         <is>
           <t>0000-0003-1966-2680</t>
@@ -9174,12 +9082,12 @@
       <c r="W105" t="b">
         <v>0</v>
       </c>
-      <c r="Z105">
+      <c r="AA105">
         <v>4</v>
       </c>
-      <c r="AA105" t="inlineStr">
-        <is>
-          <t>["water and sanitation infrastructure", "disadvantaged unincorporated communities", "environmetal justice", "participatory process", "sociotechnical design"]</t>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>c("waterandsanitationinfrastructure", "disadvantagedunincorporatedcommunities", "environmetaljustice", "participatoryprocess", "sociotechnicaldesign")</t>
         </is>
       </c>
     </row>
@@ -9246,24 +9154,24 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>Januka Budhathoki-Uprety</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>Department of Textile Engineering, Chemistry and Science, Wilson College of Textiles, North Carolina State University, Raleigh, North Carolina 27695, United States</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="R106" t="inlineStr">
-        <is>
-          <t>Januka Budhathoki-Uprety</t>
-        </is>
-      </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>Department of Textile Engineering, Chemistry and Science, Wilson College of Textiles, North Carolina State University, Raleigh, North Carolina 27695, United States</t>
-        </is>
-      </c>
-      <c r="T106" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="V106" t="inlineStr">
         <is>
           <t>0000-0003-3395-4823</t>
@@ -9272,12 +9180,12 @@
       <c r="W106" t="b">
         <v>0</v>
       </c>
-      <c r="Z106">
+      <c r="AA106">
         <v>2</v>
       </c>
-      <c r="AA106" t="inlineStr">
-        <is>
-          <t>["textile dyes", "environmental pollution", "clean water", "sustainability", "polycarbodiimide", "topological polar surface area (TPSA)", "molecular transport"]</t>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>c("textiledyes", "environmentalpollution", "cleanwater", "sustainability", "polycarbodiimide", "topologicalpolarsurfacearea(TPSA)", "moleculartransport")</t>
         </is>
       </c>
     </row>
@@ -9344,38 +9252,38 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>0000-0002-5845-1969</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>Marc L. Serre</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>Gillings School of Global Public Health, Department of Environmental Sciences and Engineering, University of North Carolina at Chapel Hill, Chapel Hill, North Carolina 27599-7400, United States</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="Q107" t="inlineStr">
-        <is>
-          <t>0000-0002-5845-1969</t>
-        </is>
-      </c>
-      <c r="R107" t="inlineStr">
-        <is>
-          <t>Marc L. Serre</t>
-        </is>
-      </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>Gillings School of Global Public Health, Department of Environmental Sciences and Engineering, University of North Carolina at Chapel Hill, Chapel Hill, North Carolina 27599-7400, United States</t>
-        </is>
-      </c>
-      <c r="T107" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W107" t="b">
         <v>0</v>
       </c>
-      <c r="Z107">
+      <c r="AA107">
         <v>5</v>
       </c>
-      <c r="AA107" t="inlineStr">
-        <is>
-          <t>["land-use regression", "molecular microbial source tracking", "surface water", "sediment", "river networks", "animal feeding operations", "septic systems"]</t>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>c("land-useregression", "molecularmicrobialsourcetracking", "surfacewater", "sediment", "rivernetworks", "animalfeedingoperations", "septicsystems")</t>
         </is>
       </c>
     </row>
@@ -9440,20 +9348,15 @@
           <t>Department of Civil, Construction, and Environmental Engineering, North Carolina State University, Fitts-Woolard Hall, 915 Partners Way, Rm 3250, Raleigh, North Carolina 27695, United States</t>
         </is>
       </c>
-      <c r="O108" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W108" t="b">
         <v>0</v>
       </c>
-      <c r="Z108">
+      <c r="AA108">
         <v>5</v>
       </c>
-      <c r="AA108" t="inlineStr">
-        <is>
-          <t>["multiple water source use", "supplemental unimproved source use", "fecal contamination", "Monte Carlo simulations", "drinking water quality", "low- and middle-income countries"]</t>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>c("multiplewatersourceuse", "supplementalunimprovedsourceuse", "fecalcontamination", "MonteCarlosimulations", "drinkingwaterquality", "low-andmiddle-incomecountries")</t>
         </is>
       </c>
     </row>
@@ -9518,11 +9421,6 @@
           <t>School of Geography, Earth and Environmental Sciences, University of Birmingham, Edgbaston, Birmingham B15 2TT, United Kingdom</t>
         </is>
       </c>
-      <c r="O109" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
       <c r="Q109" t="inlineStr">
         <is>
           <t>0000-0002-7008-0371</t>
@@ -9541,12 +9439,12 @@
           <t>on request</t>
         </is>
       </c>
-      <c r="Z109">
-        <v>1</v>
-      </c>
-      <c r="AA109" t="inlineStr">
-        <is>
-          <t>["Microplastics in rivers", "Water management", "DiversionsAbstraction", "Paired catchment approach", "Global models"]</t>
+      <c r="AA109">
+        <v>1</v>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>c("Microplasticsinrivers", "Watermanagement", "DiversionsAbstraction", "Pairedcatchmentapproach", "Globalmodels")</t>
         </is>
       </c>
     </row>
@@ -9611,11 +9509,6 @@
           <t>Duke University Wetland Center, Nicholas School of the Environment, Duke University, Box 90333, Durham, NC 27708, USA</t>
         </is>
       </c>
-      <c r="O110" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W110" t="b">
         <v>1</v>
       </c>
@@ -9629,12 +9522,12 @@
           <t>on request</t>
         </is>
       </c>
-      <c r="Z110">
-        <v>0</v>
-      </c>
-      <c r="AA110" t="inlineStr">
-        <is>
-          <t>["Pocosin", "Carbon", "Methane", "GHG", "Net ecosystem exchange", "Hydrologic restoration", "Peatland", "Evergreen shrub bog", "Water table depth", "Eddy covariance", '"Carbon dioxide"]</t>
+      <c r="AA110">
+        <v>0</v>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>c("Pocosin", "Carbon", "Methane", "GHG", "Netecosystemexchange", "Hydrologicrestoration", "Peatland", "Evergreenshrubbog", "Watertabledepth", "Eddycovariance", "", "Carbondioxide")</t>
         </is>
       </c>
     </row>
@@ -9699,11 +9592,6 @@
           <t>Nicholas School of the Environment, Duke University, Durham 27710, NC, USA</t>
         </is>
       </c>
-      <c r="O111" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W111" t="b">
         <v>1</v>
       </c>
@@ -9717,12 +9605,12 @@
           <t>on request</t>
         </is>
       </c>
-      <c r="Z111">
-        <v>1</v>
-      </c>
-      <c r="AA111" t="inlineStr">
-        <is>
-          <t>["Per- and polyfluoroalkyl substances", "PFAS", "Drinking water", "Serum", "Human health outcomes"]</t>
+      <c r="AA111">
+        <v>1</v>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>c("Per-andpolyfluoroalkylsubstances", "PFAS", "Drinkingwater", "Serum", "Humanhealthoutcomes")</t>
         </is>
       </c>
     </row>
@@ -9766,7 +9654,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>pdf &amp; xlsx</t>
+          <t>c("pdf", "xlsx")</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -9787,11 +9675,6 @@
           <t>U.S. Geological Survey, Lawrenceville, NJ, US</t>
         </is>
       </c>
-      <c r="O112" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q112" t="inlineStr">
         <is>
           <t>0000-0002-1214-4920</t>
@@ -9810,12 +9693,17 @@
           <t>available in online repository</t>
         </is>
       </c>
-      <c r="Z112">
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>c("https://www.sciencebase.gov/catalog/item/5fad56aad34eb413d5df459c", "https://www.sciencebase.gov/catalog/item/5ab3d60be4b081f61ab5e3d4")</t>
+        </is>
+      </c>
+      <c r="AA112">
         <v>11</v>
       </c>
-      <c r="AA112" t="inlineStr">
-        <is>
-          <t>["Per- and polyfluoroalkyl substances", "Drinking-water", "Public-supply", "Private-wellsSources", "Health effect"]</t>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>c("Per-andpolyfluoroalkylsubstances", "Drinking-water", "Public-supply", "Private-wellsSources", "Healtheffect")</t>
         </is>
       </c>
     </row>
@@ -9882,29 +9770,29 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>0000-0002-4625-2276</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>Christine E. Stauber</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>Department of Population Health Sciences, School of Public Health, Georgia State University, Atlanta, GA 30303, USA</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="Q113" t="inlineStr">
-        <is>
-          <t>0000-0002-4625-2276</t>
-        </is>
-      </c>
-      <c r="R113" t="inlineStr">
-        <is>
-          <t>Christine E. Stauber</t>
-        </is>
-      </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>Department of Population Health Sciences, School of Public Health, Georgia State University, Atlanta, GA 30303, USA</t>
-        </is>
-      </c>
-      <c r="T113" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W113" t="b">
         <v>1</v>
       </c>
@@ -9918,12 +9806,12 @@
           <t>on request</t>
         </is>
       </c>
-      <c r="Z113">
+      <c r="AA113">
         <v>3</v>
       </c>
-      <c r="AA113" t="inlineStr">
-        <is>
-          <t>["Zika virus", "wastewater-based epidemiology", "resource-constrained settings"]</t>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>c("Zikavirus", "wastewater-basedepidemiology", "resource-constrainedsettings")</t>
         </is>
       </c>
     </row>
@@ -10021,12 +9909,12 @@
           <t>in paper or supp</t>
         </is>
       </c>
-      <c r="Z114">
-        <v>1</v>
-      </c>
-      <c r="AA114" t="inlineStr">
-        <is>
-          <t>["Air pollution control", "Biological gas treatment", "Capillary reactor", "Hydrophobic pollutants", "Segmented flow"]</t>
+      <c r="AA114">
+        <v>1</v>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>c("Airpollutioncontrol", "Biologicalgastreatment", "Capillaryreactor", "Hydrophobicpollutants", "Segmentedflow")</t>
         </is>
       </c>
     </row>
@@ -10091,11 +9979,6 @@
           <t>Department of Civil, Construction, and Environmental Engineering, North Carolina State University, 915 Partners Way, Raleigh, NC 27695, USA</t>
         </is>
       </c>
-      <c r="O115" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W115" t="b">
         <v>1</v>
       </c>
@@ -10109,12 +9992,12 @@
           <t>on request</t>
         </is>
       </c>
-      <c r="Z115">
-        <v>1</v>
-      </c>
-      <c r="AA115" t="inlineStr">
-        <is>
-          <t>["Marine microalgae", "Dunaliella viridis", "Flocculation", "Harvesting", "Water reuse", "Dissolved organic matter"]</t>
+      <c r="AA115">
+        <v>1</v>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>c("Marinemicroalgae", "Dunaliellaviridis", "Flocculation", "Harvesting", "Waterreuse", "Dissolvedorganicmatter")</t>
         </is>
       </c>
     </row>
@@ -10158,7 +10041,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>pdf &amp; xlsx</t>
+          <t>c("pdf", "xlsx")</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -10179,11 +10062,6 @@
           <t>U.S. Geological Survey, Florence Bascom Geoscience Center, MS 926A, Reston, VA, USA</t>
         </is>
       </c>
-      <c r="O116" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W116" t="b">
         <v>1</v>
       </c>
@@ -10197,12 +10075,17 @@
           <t>available in online repository</t>
         </is>
       </c>
-      <c r="Z116">
-        <v>1</v>
-      </c>
-      <c r="AA116" t="inlineStr">
-        <is>
-          <t>["Palynology","Plant macrofossil", "Charcoal", "Paleoclimate reconstruction", "Sea-level rise", "Wildfire", "Wetland development", "Hydroperiod"]</t>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>c("https://www.ncei.noaa.gov", "https://github.com/davidfastovich/gds_climate_reconstruction")</t>
+        </is>
+      </c>
+      <c r="AA116">
+        <v>1</v>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>c("Palynology", "Plantmacrofossil", "Charcoal", "Paleoclimatereconstruction", "Sea-levelrise", "Wildfire", "Wetlanddevelopment", "Hydroperiod")</t>
         </is>
       </c>
     </row>
@@ -10241,6 +10124,9 @@
       <c r="H117" t="b">
         <v>0</v>
       </c>
+      <c r="I117">
+        <v>0</v>
+      </c>
       <c r="L117">
         <v>15</v>
       </c>
@@ -10254,11 +10140,6 @@
           <t>United States Environmental Protection Agency, Center for Public Health and Environmental Assessment, Office of Research and Development, Research Triangle Park, NC, USA</t>
         </is>
       </c>
-      <c r="O117" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W117" t="b">
         <v>1</v>
       </c>
@@ -10272,12 +10153,12 @@
           <t>on request</t>
         </is>
       </c>
-      <c r="Z117">
-        <v>1</v>
-      </c>
-      <c r="AA117" t="inlineStr">
-        <is>
-          <t>["Microbiome", "Outdoor air", "Greenspace", "Airborne Bacteria", "16S rRNA", "Aerobiome"]</t>
+      <c r="AA117">
+        <v>1</v>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>c("Microbiome", "Outdoorair", "Greenspace", "AirborneBacteria", "16SrRNA", "Aerobiome")</t>
         </is>
       </c>
     </row>
@@ -10342,15 +10223,10 @@
           <t>Department of Environmental Sciences and Engineering, Gillings School of Global Public Health, University of North Carolina at Chapel Hill, Chapel Hill, NC, USA</t>
         </is>
       </c>
-      <c r="O118" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W118" t="b">
         <v>0</v>
       </c>
-      <c r="Z118">
+      <c r="AA118">
         <v>13</v>
       </c>
     </row>
@@ -10389,6 +10265,9 @@
       <c r="H119" t="b">
         <v>0</v>
       </c>
+      <c r="I119">
+        <v>0</v>
+      </c>
       <c r="L119">
         <v>1</v>
       </c>
@@ -10402,11 +10281,6 @@
           <t>The Roux Institute, Northeastern University 100 Fore St. Portland, ME USA 04101</t>
         </is>
       </c>
-      <c r="O119" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W119" t="b">
         <v>1</v>
       </c>
@@ -10420,12 +10294,12 @@
           <t>on request</t>
         </is>
       </c>
-      <c r="Z119">
-        <v>0</v>
-      </c>
-      <c r="AA119" t="inlineStr">
-        <is>
-          <t>["Water security", "Text analysis", "Structural topic modeling","Planning", "Environmental justice"]</t>
+      <c r="AA119">
+        <v>0</v>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>c("Watersecurity", "Textanalysis", "Structuraltopicmodeling", "Planning", "Environmentaljustice")</t>
         </is>
       </c>
     </row>
@@ -10492,29 +10366,29 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>0000-0001-8935-7759</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>Marirosa Molina</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>U.S. Environmental Protection Agency, Office of Research and Development, RTP, NC, 27709, USA</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="Q120" t="inlineStr">
-        <is>
-          <t>0000-0001-8935-7759</t>
-        </is>
-      </c>
-      <c r="R120" t="inlineStr">
-        <is>
-          <t>Marirosa Molina</t>
-        </is>
-      </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>U.S. Environmental Protection Agency, Office of Research and Development, RTP, NC, 27709, USA</t>
-        </is>
-      </c>
-      <c r="T120" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W120" t="b">
         <v>1</v>
       </c>
@@ -10528,12 +10402,12 @@
           <t>on request</t>
         </is>
       </c>
-      <c r="Z120">
+      <c r="AA120">
         <v>3</v>
       </c>
-      <c r="AA120" t="inlineStr">
-        <is>
-          <t>["crAssphage", "Municipal untreated wastewater", "Temporal variations", "Spatial variations", "Enteric pathogens correlations", "Bacteria", "And viruses", "qPCR", "rt-qPCR"]</t>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>c("crAssphage", "Municipaluntreatedwastewater", "Temporalvariations", "Spatialvariations", "Entericpathogenscorrelations", "Bacteria", "Andviruses", "qPCR", "rt-qPCR")</t>
         </is>
       </c>
     </row>
@@ -10598,11 +10472,6 @@
           <t>Haub School of Environment and Natural Resources, University of Wyoming, USA</t>
         </is>
       </c>
-      <c r="O121" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W121" t="b">
         <v>1</v>
       </c>
@@ -10616,12 +10485,12 @@
           <t>not shareable</t>
         </is>
       </c>
-      <c r="Z121">
-        <v>1</v>
-      </c>
-      <c r="AA121" t="inlineStr">
-        <is>
-          <t>["Groundwater contamination", "Swine lagoons", "Private wells", "Atmospheric stressors", "Environmental pollution"]</t>
+      <c r="AA121">
+        <v>1</v>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>c("Groundwatercontamination", "Swinelagoons", "Privatewells", "Atmosphericstressors", "Environmentalpollution")</t>
         </is>
       </c>
     </row>
@@ -10686,11 +10555,6 @@
           <t>Biological and Agricultural Engineering, North Carolina State University, Raleigh, NC, USA</t>
         </is>
       </c>
-      <c r="O122" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W122" t="b">
         <v>1</v>
       </c>
@@ -10704,12 +10568,12 @@
           <t>on request</t>
         </is>
       </c>
-      <c r="Z122">
+      <c r="AA122">
         <v>4</v>
       </c>
-      <c r="AA122" t="inlineStr">
-        <is>
-          <t>["Microplastics", "Streamflow", "Urban development", "Sediment", "Watershed", "Sampling method"]</t>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>c("Microplastics", "Streamflow", "Urbandevelopment", "Sediment", "Watershed", "Samplingmethod")</t>
         </is>
       </c>
     </row>
@@ -10774,11 +10638,6 @@
           <t>School of Forest, Fisheries, and Geomatics Sciences, University of Florida, Gainesville, FL, USA</t>
         </is>
       </c>
-      <c r="O123" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q123" t="inlineStr">
         <is>
           <t>0000-0002-2843-4965</t>
@@ -10797,12 +10656,12 @@
           <t>on request</t>
         </is>
       </c>
-      <c r="Z123">
-        <v>1</v>
-      </c>
-      <c r="AA123" t="inlineStr">
-        <is>
-          <t>["UAV", "UAS", "Rugosity", "Geomorphometry", "Coastal habitat", "Remote sensing"]</t>
+      <c r="AA123">
+        <v>1</v>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>c("UAV", "UAS", "Rugosity", "Geomorphometry", "Coastalhabitat", "Remotesensing")</t>
         </is>
       </c>
     </row>
@@ -10846,7 +10705,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>docx &amp; pdf</t>
+          <t>c("docx", "pdf")</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -10867,11 +10726,6 @@
           <t>Institute of Hygiene and Environmental Medicine, Charité–Universitätsmedizin Berlin, Corporate Member of Freie Universität Berlin, Humboldt-Universität zu Berlin and Berlin Institute of Health, Berlin, Germany</t>
         </is>
       </c>
-      <c r="O124" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
       <c r="Q124" t="inlineStr">
         <is>
           <t>0000-0002-1225-9023</t>
@@ -10880,12 +10734,12 @@
       <c r="W124" t="b">
         <v>0</v>
       </c>
-      <c r="Z124">
+      <c r="AA124">
         <v>4</v>
       </c>
-      <c r="AA124" t="inlineStr">
-        <is>
-          <t>["Hospital-aquired infection", "Multidrug-resistant pathogen", "Environmental cleaning", "Probiotic", "Randomized-controlled trial", "Environmental hygiene", "MRSAVRE", "Multidrug-resistant Gram-negative"]</t>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>c("Hospital-aquiredinfection", "Multidrug-resistantpathogen", "Environmentalcleaning", "Probiotic", "Randomized-controlledtrial", "Environmentalhygiene", "MRSAVRE", "Multidrug-resistantGram-negative")</t>
         </is>
       </c>
     </row>
@@ -10924,6 +10778,9 @@
       <c r="H125" t="b">
         <v>0</v>
       </c>
+      <c r="I125">
+        <v>0</v>
+      </c>
       <c r="L125">
         <v>6</v>
       </c>
@@ -10937,11 +10794,6 @@
           <t>University of North Carolina, Chapel Hill, NC, USA</t>
         </is>
       </c>
-      <c r="O125" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q125" t="inlineStr">
         <is>
           <t>0000-0001-6309-1403</t>
@@ -10960,12 +10812,12 @@
           <t>on request</t>
         </is>
       </c>
-      <c r="Z125">
-        <v>1</v>
-      </c>
-      <c r="AA125" t="inlineStr">
-        <is>
-          <t>["Atmospheric forcing", "Cape Hatteras", "PEACH", "Atmospheric cyclones", "Atmospheric warm and cool seasons"]</t>
+      <c r="AA125">
+        <v>1</v>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>c("Atmosphericforcing", "CapeHatteras", "PEACH", "Atmosphericcyclones", "Atmosphericwarmandcoolseasons")</t>
         </is>
       </c>
     </row>
@@ -11004,6 +10856,9 @@
       <c r="H126" t="b">
         <v>0</v>
       </c>
+      <c r="I126">
+        <v>0</v>
+      </c>
       <c r="L126">
         <v>6</v>
       </c>
@@ -11019,7 +10874,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>Bangladesh</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
@@ -11050,12 +10905,12 @@
           <t>on request</t>
         </is>
       </c>
-      <c r="Z126">
+      <c r="AA126">
         <v>15</v>
       </c>
-      <c r="AA126" t="inlineStr">
-        <is>
-          <t>["Contamination", "Distribution", "Environment", "Health impact", "North Carolina", "PFAS sources"]</t>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>c("Contamination", "Distribution", "Environment", "Healthimpact", "NorthCarolina", "PFASsources")</t>
         </is>
       </c>
     </row>
@@ -11094,6 +10949,9 @@
       <c r="H127" t="b">
         <v>0</v>
       </c>
+      <c r="I127">
+        <v>0</v>
+      </c>
       <c r="L127">
         <v>1</v>
       </c>
@@ -11107,11 +10965,6 @@
           <t>Earth Surface Systems Program, University of Kentucky, USA</t>
         </is>
       </c>
-      <c r="O127" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W127" t="b">
         <v>1</v>
       </c>
@@ -11125,12 +10978,12 @@
           <t>on request</t>
         </is>
       </c>
-      <c r="Z127">
-        <v>1</v>
-      </c>
-      <c r="AA127" t="inlineStr">
-        <is>
-          <t>["Landscape change", "Climate change", "Attribution", "Neuse River", "Sea-level rise", "Marsh loss"]</t>
+      <c r="AA127">
+        <v>1</v>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>c("Landscapechange", "Climatechange", "Attribution", "NeuseRiver", "Sea-levelrise", "Marshloss")</t>
         </is>
       </c>
     </row>
@@ -11169,6 +11022,9 @@
       <c r="H128" t="b">
         <v>0</v>
       </c>
+      <c r="I128">
+        <v>0</v>
+      </c>
       <c r="L128">
         <v>7</v>
       </c>
@@ -11184,24 +11040,24 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>Rebecca C. Fry</t>
+        </is>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>Department of Environmental Sciences and Engineering, Gillings School of Global Public Health, The University of North Carolina at Chapel Hill, Chapel Hill, NC, USA</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="R128" t="inlineStr">
-        <is>
-          <t>Rebecca C. Fry</t>
-        </is>
-      </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>Department of Environmental Sciences and Engineering, Gillings School of Global Public Health, The University of North Carolina at Chapel Hill, Chapel Hill, NC, USA</t>
-        </is>
-      </c>
-      <c r="T128" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W128" t="b">
         <v>1</v>
       </c>
@@ -11215,12 +11071,17 @@
           <t>available in online repository</t>
         </is>
       </c>
-      <c r="Z128">
-        <v>0</v>
-      </c>
-      <c r="AA128" t="inlineStr">
-        <is>
-          <t>["Clustering", "Metals", "Private wells", "Social vulnerability", "Geographic data"]</t>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>https://github.com/UNCSRP/CASS-IT</t>
+        </is>
+      </c>
+      <c r="AA128">
+        <v>0</v>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>c("Clustering", "Metals", "Privatewells", "Socialvulnerability", "Geographicdata")</t>
         </is>
       </c>
     </row>
@@ -11285,11 +11146,6 @@
           <t>Haub School of Environment and Natural Resources, University of Wyoming, USA</t>
         </is>
       </c>
-      <c r="O129" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W129" t="b">
         <v>1</v>
       </c>
@@ -11300,15 +11156,15 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>data not sharable</t>
-        </is>
-      </c>
-      <c r="Z129">
-        <v>1</v>
-      </c>
-      <c r="AA129" t="inlineStr">
-        <is>
-          <t>["Groundwater contamination", "Swine lagoons", "Private wells", "Atmospheric stressors", "Environmental pollution"]</t>
+          <t>not shareable</t>
+        </is>
+      </c>
+      <c r="AA129">
+        <v>1</v>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>c("Groundwatercontamination", "Swinelagoons", "Privatewells", "Atmosphericstressors", "Environmentalpollution")</t>
         </is>
       </c>
     </row>
@@ -11347,6 +11203,9 @@
       <c r="H130" t="b">
         <v>0</v>
       </c>
+      <c r="I130">
+        <v>0</v>
+      </c>
       <c r="L130">
         <v>3</v>
       </c>
@@ -11362,24 +11221,24 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>Marc A. Deshusses</t>
+        </is>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>Department of Civil and Environmental Engineering, Duke University, 207 Wilkinson Hall, Box 90287, Durham, NC 27708-0287, USA</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="R130" t="inlineStr">
-        <is>
-          <t>Marc A. Deshusses</t>
-        </is>
-      </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>Department of Civil and Environmental Engineering, Duke University, 207 Wilkinson Hall, Box 90287, Durham, NC 27708-0287, USA</t>
-        </is>
-      </c>
-      <c r="T130" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="V130" t="inlineStr">
         <is>
           <t>0000-0003-0639-7865</t>
@@ -11398,12 +11257,12 @@
           <t>on request</t>
         </is>
       </c>
-      <c r="Z130">
-        <v>1</v>
-      </c>
-      <c r="AA130" t="inlineStr">
-        <is>
-          <t>["Microbioreactor", "Volatile organic compound", "Biofiltration", "Modeling"]</t>
+      <c r="AA130">
+        <v>1</v>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>c("Microbioreactor", "Volatileorganiccompound", "Biofiltration", "Modeling")</t>
         </is>
       </c>
     </row>
@@ -11470,24 +11329,24 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>Detlef R.U. Knappe</t>
+        </is>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>Department of Civil, Construction, and Environmental Engineering, North Carolina State University, Raleigh, NC 27695, United States</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="R131" t="inlineStr">
-        <is>
-          <t>Detlef R.U. Knappe</t>
-        </is>
-      </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>Department of Civil, Construction, and Environmental Engineering, North Carolina State University, Raleigh, NC 27695, United States</t>
-        </is>
-      </c>
-      <c r="T131" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="V131" t="inlineStr">
         <is>
           <t>0000-0003-1315-1791</t>
@@ -11506,12 +11365,12 @@
           <t>on request</t>
         </is>
       </c>
-      <c r="Z131">
+      <c r="AA131">
         <v>2</v>
       </c>
-      <c r="AA131" t="inlineStr">
-        <is>
-          <t>["Biofiltration", "Cometabolism", "Adsorption", "Emerging contaminants"]</t>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>c("Biofiltration", "Cometabolism", "Adsorption", "Emergingcontaminants")</t>
         </is>
       </c>
     </row>
@@ -11578,29 +11437,29 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>0000-0002-1157-5120</t>
+        </is>
+      </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>Mohamed A. Youssef</t>
+        </is>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>Department of Biological and Agricultural Engineering, North Carolina State University, Raleigh, NC 27695–7625, USA</t>
+        </is>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="Q132" t="inlineStr">
-        <is>
-          <t>0000-0002-1157-5120</t>
-        </is>
-      </c>
-      <c r="R132" t="inlineStr">
-        <is>
-          <t>Mohamed A. Youssef</t>
-        </is>
-      </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>Department of Biological and Agricultural Engineering, North Carolina State University, Raleigh, NC 27695–7625, USA</t>
-        </is>
-      </c>
-      <c r="T132" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W132" t="b">
         <v>1</v>
       </c>
@@ -11614,12 +11473,12 @@
           <t>on request</t>
         </is>
       </c>
-      <c r="Z132">
+      <c r="AA132">
         <v>2</v>
       </c>
-      <c r="AA132" t="inlineStr">
-        <is>
-          <t>["Subsurface drainage", "Subirrigation", "On-farm water storage", "Drainage water reuse", "Supplemental irrigation", "Surface water quality"]</t>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>c("Subsurfacedrainage", "Subirrigation", "On-farmwaterstorage", "Drainagewaterreuse", "Supplementalirrigation", "Surfacewaterquality")</t>
         </is>
       </c>
     </row>
@@ -11658,6 +11517,9 @@
       <c r="H133" t="b">
         <v>0</v>
       </c>
+      <c r="I133">
+        <v>0</v>
+      </c>
       <c r="L133">
         <v>2</v>
       </c>
@@ -11671,15 +11533,10 @@
           <t>University of North Carolina at Chapel Hill, Institute of Marine Sciences, Morehead City NC 28557, USA</t>
         </is>
       </c>
-      <c r="O133" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W133" t="b">
         <v>0</v>
       </c>
-      <c r="Z133">
+      <c r="AA133">
         <v>1</v>
       </c>
     </row>
@@ -11746,24 +11603,24 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>Konstantinos T. Konstantinidis</t>
+        </is>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>School of Civil and Environmental Engineering, Georgia Institute of Technology, Atlanta, GA 30332, USA</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="R134" t="inlineStr">
-        <is>
-          <t>Konstantinos T. Konstantinidis</t>
-        </is>
-      </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>School of Civil and Environmental Engineering, Georgia Institute of Technology, Atlanta, GA 30332, USA</t>
-        </is>
-      </c>
-      <c r="T134" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W134" t="b">
         <v>1</v>
       </c>
@@ -11777,12 +11634,12 @@
           <t>on request</t>
         </is>
       </c>
-      <c r="Z134">
+      <c r="AA134">
         <v>5</v>
       </c>
-      <c r="AA134" t="inlineStr">
-        <is>
-          <t>["Wastewater-based epidemiology", "Passive sampling", "Moore swab"]</t>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>c("Wastewater-basedepidemiology", "Passivesampling", "Mooreswab")</t>
         </is>
       </c>
     </row>
@@ -11847,11 +11704,6 @@
           <t>Haub School of Environment and Natural Resources, University of Wyoming, USA</t>
         </is>
       </c>
-      <c r="O135" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W135" t="b">
         <v>1</v>
       </c>
@@ -11865,12 +11717,12 @@
           <t>not shareable</t>
         </is>
       </c>
-      <c r="Z135">
-        <v>1</v>
-      </c>
-      <c r="AA135" t="inlineStr">
-        <is>
-          <t>["Groundwater contamination", "Swine lagoons", "Private wells", "Atmospheric stressors", "Environmental pollution"]</t>
+      <c r="AA135">
+        <v>1</v>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>c("Groundwatercontamination", "Swinelagoons", "Privatewells", "Atmosphericstressors", "Environmentalpollution")</t>
         </is>
       </c>
     </row>
@@ -11968,12 +11820,12 @@
           <t>not shareable</t>
         </is>
       </c>
-      <c r="Z136">
+      <c r="AA136">
         <v>13</v>
       </c>
-      <c r="AA136" t="inlineStr">
-        <is>
-          <t>["SARS-CoV-2", "Wastewater-based epidemiology", "University campus", "Emerging contaminants", "Disinfectants"]</t>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>c("SARS-CoV-2", "Wastewater-basedepidemiology", "Universitycampus", "Emergingcontaminants", "Disinfectants")</t>
         </is>
       </c>
     </row>
@@ -12012,6 +11864,9 @@
       <c r="H137" t="b">
         <v>0</v>
       </c>
+      <c r="I137">
+        <v>0</v>
+      </c>
       <c r="L137">
         <v>5</v>
       </c>
@@ -12025,11 +11880,6 @@
           <t>North Carolina Central University, Department of Environmental, Earth and Geospatial Sciences, 1246 Mary M, Townes Science Complex, 1801 Fayetteville St., Durham, NC, 27707, USA</t>
         </is>
       </c>
-      <c r="O137" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q137" t="inlineStr">
         <is>
           <t>0000-0001-9333-9641</t>
@@ -12048,12 +11898,12 @@
           <t>on request</t>
         </is>
       </c>
-      <c r="Z137">
+      <c r="AA137">
         <v>3</v>
       </c>
-      <c r="AA137" t="inlineStr">
-        <is>
-          <t>["Geographic information systems", "Rural geography", "statistical analysis"]</t>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>c("Geographicinformationsystems", "Ruralgeography", "statisticalanalysis")</t>
         </is>
       </c>
     </row>
@@ -12092,6 +11942,9 @@
       <c r="H138" t="b">
         <v>0</v>
       </c>
+      <c r="I138">
+        <v>0</v>
+      </c>
       <c r="L138">
         <v>6</v>
       </c>
@@ -12105,11 +11958,6 @@
           <t>North Carolina State University, Department of Forestry and Environmental Resources, 2800 Faucette Dr, Raleigh, NC 27695, USA</t>
         </is>
       </c>
-      <c r="O138" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W138" t="b">
         <v>1</v>
       </c>
@@ -12123,12 +11971,12 @@
           <t>on request</t>
         </is>
       </c>
-      <c r="Z138">
+      <c r="AA138">
         <v>5</v>
       </c>
-      <c r="AA138" t="inlineStr">
-        <is>
-          <t>["Forested watersheds", "FUTURES model", "Land use land cover change (LULCC)", "Hydrologic modeling", "Soil and Water Assessment Tool (SWAT)", "Global climate model"]</t>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>c("Forestedwatersheds", "FUTURESmodel", "Landuselandcoverchange(LULCC)", "Hydrologicmodeling", "SoilandWaterAssessmentTool(SWAT)", "Globalclimatemodel")</t>
         </is>
       </c>
     </row>
@@ -12172,7 +12020,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>xlsx &amp; docx</t>
+          <t>c("xlsx", "docx")</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -12195,24 +12043,24 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>D.P. Genereux</t>
+        </is>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>Department of Marine, Earth, and Atmospheric Sciences, NC State University, Raleigh, NC, United States of America</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="R139" t="inlineStr">
-        <is>
-          <t>D.P. Genereux</t>
-        </is>
-      </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>Department of Marine, Earth, and Atmospheric Sciences, NC State University, Raleigh, NC, United States of America</t>
-        </is>
-      </c>
-      <c r="T139" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W139" t="b">
         <v>1</v>
       </c>
@@ -12226,12 +12074,12 @@
           <t>in paper or supp</t>
         </is>
       </c>
-      <c r="Z139">
+      <c r="AA139">
         <v>2</v>
       </c>
-      <c r="AA139" t="inlineStr">
-        <is>
-          <t>["VOC", "Contaminant flux", "Groundwater", "Stream"]</t>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>c("VOC", "Contaminantflux", "Groundwater", "Stream")</t>
         </is>
       </c>
     </row>
@@ -12270,6 +12118,9 @@
       <c r="H140" t="b">
         <v>0</v>
       </c>
+      <c r="I140">
+        <v>0</v>
+      </c>
       <c r="L140">
         <v>7</v>
       </c>
@@ -12283,11 +12134,6 @@
           <t>Ecosystems and Fishery Resources Laboratory, Institute of Fisheries and Aquatic Sciences, University of Douala, BP 2701 Douala, Cameroon</t>
         </is>
       </c>
-      <c r="O140" t="inlineStr">
-        <is>
-          <t>Cameroon</t>
-        </is>
-      </c>
       <c r="Q140" t="inlineStr">
         <is>
           <t>0000-0001-7724-5805</t>
@@ -12296,12 +12142,12 @@
       <c r="W140" t="b">
         <v>0</v>
       </c>
-      <c r="Z140">
+      <c r="AA140">
         <v>2</v>
       </c>
-      <c r="AA140" t="inlineStr">
-        <is>
-          <t>["Coastal altimetrySea level", "Waves", "Video camera", "Tide gauge", "Buoy", "Altimeter", "Significant wave height", "Re-tracking algorithm"]</t>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>c("CoastalaltimetrySealevel", "Waves", "Videocamera", "Tidegauge", "Buoy", "Altimeter", "Significantwaveheight", "Re-trackingalgorithm")</t>
         </is>
       </c>
     </row>
@@ -12368,24 +12214,24 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>Jill R. Stewart</t>
+        </is>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>Department of Environmental Sciences and Engineering, Gillings School of Global Public Health, University of North Carolina at Chapel Hill, 135 Dauer Drive, Chapel Hill, NC 27599, United States</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="R141" t="inlineStr">
-        <is>
-          <t>Jill R. Stewart</t>
-        </is>
-      </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>Department of Environmental Sciences and Engineering, Gillings School of Global Public Health, University of North Carolina at Chapel Hill, 135 Dauer Drive, Chapel Hill, NC 27599, United States</t>
-        </is>
-      </c>
-      <c r="T141" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W141" t="b">
         <v>1</v>
       </c>
@@ -12399,12 +12245,12 @@
           <t>on request</t>
         </is>
       </c>
-      <c r="Z141">
+      <c r="AA141">
         <v>6</v>
       </c>
-      <c r="AA141" t="inlineStr">
-        <is>
-          <t>["Wastewater-based epidemiology", "Sewage surveillance", "Coronavirus", "COVID", "ddPCR"]</t>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>c("Wastewater-basedepidemiology", "Sewagesurveillance", "Coronavirus", "COVID", "ddPCR")</t>
         </is>
       </c>
     </row>
@@ -12443,6 +12289,9 @@
       <c r="H142" t="b">
         <v>0</v>
       </c>
+      <c r="I142">
+        <v>0</v>
+      </c>
       <c r="L142">
         <v>7</v>
       </c>
@@ -12458,24 +12307,24 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>Rebecca C. Fry</t>
+        </is>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>Department of Environmental Sciences and Engineering, Gillings School of Global Public Health, The University of North Carolina at Chapel Hill, Chapel Hill, NC, USA</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="R142" t="inlineStr">
-        <is>
-          <t>Rebecca C. Fry</t>
-        </is>
-      </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>Department of Environmental Sciences and Engineering, Gillings School of Global Public Health, The University of North Carolina at Chapel Hill, Chapel Hill, NC, USA</t>
-        </is>
-      </c>
-      <c r="T142" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W142" t="b">
         <v>1</v>
       </c>
@@ -12489,12 +12338,17 @@
           <t>available in online repository</t>
         </is>
       </c>
-      <c r="Z142">
-        <v>0</v>
-      </c>
-      <c r="AA142" t="inlineStr">
-        <is>
-          <t>["Clustering", "Metals", "Private wells", "Social vulnerability", "Geographic data"]</t>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>https://github.com/UNCSRP/CASS-IT</t>
+        </is>
+      </c>
+      <c r="AA142">
+        <v>0</v>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>c("Clustering", "Metals", "Privatewells", "Socialvulnerability", "Geographicdata")</t>
         </is>
       </c>
     </row>
@@ -12561,29 +12415,29 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>0000-0002-5422-5104</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>Mahmoud Sharara</t>
+        </is>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>Biological and Agricultural Engineering, North Carolina State University, Raleigh, USA</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="Q143" t="inlineStr">
-        <is>
-          <t>0000-0002-5422-5104</t>
-        </is>
-      </c>
-      <c r="R143" t="inlineStr">
-        <is>
-          <t>Mahmoud Sharara</t>
-        </is>
-      </c>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>Biological and Agricultural Engineering, North Carolina State University, Raleigh, USA</t>
-        </is>
-      </c>
-      <c r="T143" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="V143" t="inlineStr">
         <is>
           <t>0000-0003-4519-8156</t>
@@ -12602,12 +12456,12 @@
           <t>on request</t>
         </is>
       </c>
-      <c r="Z143">
+      <c r="AA143">
         <v>3</v>
       </c>
-      <c r="AA143" t="inlineStr">
-        <is>
-          <t>["GHG Emissions", "Water extractable", "Phosphorus", "Zinc", "Copper", "North Carolina"]</t>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>c("GHGEmissions", "Waterextractable", "Phosphorus", "Zinc", "Copper", "NorthCarolina")</t>
         </is>
       </c>
     </row>
@@ -12646,6 +12500,9 @@
       <c r="H144" t="b">
         <v>0</v>
       </c>
+      <c r="I144">
+        <v>0</v>
+      </c>
       <c r="L144">
         <v>6</v>
       </c>
@@ -12659,11 +12516,6 @@
           <t>Dr. John Lining Professor of Physics and Director of the James B. Near Center for Climate Studies, The Citadel, 171 Moultrie Street, Charleston, SC, USA</t>
         </is>
       </c>
-      <c r="O144" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W144" t="b">
         <v>1</v>
       </c>
@@ -12677,12 +12529,12 @@
           <t>on request</t>
         </is>
       </c>
-      <c r="Z144">
+      <c r="AA144">
         <v>2</v>
       </c>
-      <c r="AA144" t="inlineStr">
-        <is>
-          <t>["Risk", "Compound hazard", "Flood", "Rural", "Emergency management", "Planning", "CCWE"]</t>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>c("Risk", "Compoundhazard", "Flood", "Rural", "Emergencymanagement", "Planning", "CCWE")</t>
         </is>
       </c>
     </row>
@@ -12749,24 +12601,24 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>Lawrence S. Engel</t>
+        </is>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>Department of Epidemiology, University of North Carolina, CB #7435, Chapel Hill, NC 27599-7435, USA.</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="R145" t="inlineStr">
-        <is>
-          <t>Lawrence S. Engel</t>
-        </is>
-      </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>Department of Epidemiology, University of North Carolina, CB #7435, Chapel Hill, NC 27599-7435, USA.</t>
-        </is>
-      </c>
-      <c r="T145" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W145" t="b">
         <v>1</v>
       </c>
@@ -12777,15 +12629,15 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>data not sharable</t>
-        </is>
-      </c>
-      <c r="Z145">
-        <v>0</v>
-      </c>
-      <c r="AA145" t="inlineStr">
-        <is>
-          <t>["Extraintestinal pathogenic E. coli (ExPEC)", "Foodborne urinary tract infection (fUTI)", "Concentrated animal feeding operation (CAFO)", "Syndromic surveillance", "Besag-York-Mollié (BYM) model", "Ecological regression analysis"]</t>
+          <t>not shareable</t>
+        </is>
+      </c>
+      <c r="AA145">
+        <v>0</v>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>c("ExtraintestinalpathogenicE.coli(ExPEC)", "Foodborneurinarytractinfection(fUTI)", "Concentratedanimalfeedingoperation(CAFO)", "Syndromicsurveillance", "Besag-York-Mollié(BYM)model", "Ecologicalregressionanalysis")</t>
         </is>
       </c>
     </row>
@@ -12850,11 +12702,6 @@
           <t>Department of Biological Sciences, North Carolina State University, Raleigh, NC, USA</t>
         </is>
       </c>
-      <c r="O146" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W146" t="b">
         <v>1</v>
       </c>
@@ -12868,12 +12715,12 @@
           <t>on request</t>
         </is>
       </c>
-      <c r="Z146">
+      <c r="AA146">
         <v>4</v>
       </c>
-      <c r="AA146" t="inlineStr">
-        <is>
-          <t>["Source apportionment", "Receptor models", "PFAS", "Perfluoroalkyl substances"]</t>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>c("Sourceapportionment", "Receptormodels", "PFAS", "Perfluoroalkylsubstances")</t>
         </is>
       </c>
     </row>
@@ -12938,11 +12785,6 @@
           <t>UNC-Chapel Hill, Earth, Marine, and Environmental Sciences, Institute of Marine Sciences, 3431 Arendell St., Morehead City, NC 28577, United States of America</t>
         </is>
       </c>
-      <c r="O147" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q147" t="inlineStr">
         <is>
           <t>0000-0001-8823-0457</t>
@@ -12961,12 +12803,12 @@
           <t>on request</t>
         </is>
       </c>
-      <c r="Z147">
+      <c r="AA147">
         <v>8</v>
       </c>
-      <c r="AA147" t="inlineStr">
-        <is>
-          <t>["Water quality", "Toxic Cyanobacteria", "Air quality", "PM2.5", "Microcystis", "Dolichospermum"]</t>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>c("Waterquality", "ToxicCyanobacteria", "Airquality", "PM2.5", "Microcystis", "Dolichospermum")</t>
         </is>
       </c>
     </row>
@@ -13033,24 +12875,24 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>Orlando Coronell</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>Department of Environmental Sciences and Engineering, Gillings School of Global Public Health, University of North Carolina at Chapel Hill, Chapel Hill, NC, 27599, USA</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="R148" t="inlineStr">
-        <is>
-          <t>Orlando Coronell</t>
-        </is>
-      </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>Department of Environmental Sciences and Engineering, Gillings School of Global Public Health, University of North Carolina at Chapel Hill, Chapel Hill, NC, 27599, USA</t>
-        </is>
-      </c>
-      <c r="T148" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="V148" t="inlineStr">
         <is>
           <t>0000-0002-7018-391X</t>
@@ -13069,12 +12911,12 @@
           <t>on request</t>
         </is>
       </c>
-      <c r="Z148">
+      <c r="AA148">
         <v>4</v>
       </c>
-      <c r="AA148" t="inlineStr">
-        <is>
-          <t>["Permeance", "Selectivity", "Rejection", "Advective transport", "Diffusive transport"]</t>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>c("Permeance", "Selectivity", "Rejection", "Advectivetransport", "Diffusivetransport")</t>
         </is>
       </c>
     </row>
@@ -13141,24 +12983,24 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>Danica Schaffer-Smith</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>Center for Biodiversity Outcomes, Arizona State University, Tempe, AZ, USA</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="R149" t="inlineStr">
-        <is>
-          <t>Danica Schaffer-Smith</t>
-        </is>
-      </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>Center for Biodiversity Outcomes, Arizona State University, Tempe, AZ, USA</t>
-        </is>
-      </c>
-      <c r="T149" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="V149" t="inlineStr">
         <is>
           <t>0000-0003-3896-1483</t>
@@ -13167,12 +13009,12 @@
       <c r="W149" t="b">
         <v>0</v>
       </c>
-      <c r="Z149">
+      <c r="AA149">
         <v>6</v>
       </c>
-      <c r="AA149" t="inlineStr">
-        <is>
-          <t>["Nutrient management", "Livestock", "Agriculture", "Machine learning", "Satellite radarSentinel-1"]</t>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>c("Nutrientmanagement", "Livestock", "Agriculture", "Machinelearning", "SatelliteradarSentinel-1")</t>
         </is>
       </c>
     </row>
@@ -13216,7 +13058,7 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>xlsx &amp; docx</t>
+          <t>c("xlsx", "docx")</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -13237,11 +13079,6 @@
           <t>Department of Biological Sciences, Virginia Institute of Marine Science, William &amp; Mary, Gloucester Point, VA, USA</t>
         </is>
       </c>
-      <c r="O150" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q150" t="inlineStr">
         <is>
           <t>0000-0002-0689-2498</t>
@@ -13260,12 +13097,12 @@
           <t>in paper or supp</t>
         </is>
       </c>
-      <c r="Z150">
-        <v>1</v>
-      </c>
-      <c r="AA150" t="inlineStr">
-        <is>
-          <t>["Nitrogen removal", "Denitrification", "Anammox", "nosZ", "hzo", "Sediments"]</t>
+      <c r="AA150">
+        <v>1</v>
+      </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>c("Nitrogenremoval", "Denitrification", "Anammox", "nosZ", "hzo", "Sediments")</t>
         </is>
       </c>
     </row>
@@ -13330,20 +13167,15 @@
           <t>Department of Epidemiology, Gillings School of Global Public Health, University of North Carolina, Chapel Hill, NC 27599, USA</t>
         </is>
       </c>
-      <c r="O151" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W151" t="b">
         <v>0</v>
       </c>
-      <c r="Z151">
+      <c r="AA151">
         <v>6</v>
       </c>
-      <c r="AA151" t="inlineStr">
-        <is>
-          <t>["CAFOs", "Swine", "Hog production", "Animal farming", "Environmental justice", "Gastrointestinal illness"]</t>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>c("CAFOs", "Swine", "Hogproduction", "Animalfarming", "Environmentaljustice", "Gastrointestinalillness")</t>
         </is>
       </c>
     </row>
@@ -13387,7 +13219,7 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>xlsx &amp; docx</t>
+          <t>c("xlsx", "docx")</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -13408,20 +13240,15 @@
           <t>Department of Marine, Earth, and Atmospheric Sciences, North Carolina State University, Raleigh, NC, United States</t>
         </is>
       </c>
-      <c r="O152" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W152" t="b">
         <v>0</v>
       </c>
-      <c r="Z152">
+      <c r="AA152">
         <v>19</v>
       </c>
-      <c r="AA152" t="inlineStr">
-        <is>
-          <t>["PFAS", "Mass load", "Model", "Source tracking", "Environmental monitoring", "Drinking water"]</t>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>c("PFAS", "Massload", "Model", "Sourcetracking", "Environmentalmonitoring", "Drinkingwater")</t>
         </is>
       </c>
     </row>
@@ -13488,33 +13315,33 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>Angela R. Harris</t>
+        </is>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>Department of Civil, Construction, and Environmental Engineering, NC State University, Raleigh, NC, United States</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="R153" t="inlineStr">
-        <is>
-          <t>Angela R. Harris</t>
-        </is>
-      </c>
-      <c r="S153" t="inlineStr">
-        <is>
-          <t>Department of Civil, Construction, and Environmental Engineering, NC State University, Raleigh, NC, United States</t>
-        </is>
-      </c>
-      <c r="T153" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W153" t="b">
         <v>0</v>
       </c>
-      <c r="Z153">
+      <c r="AA153">
         <v>3</v>
       </c>
-      <c r="AA153" t="inlineStr">
-        <is>
-          <t>["Animal husbandry", "Fecal contamination", "Sanitation", "Hygiene", "Animal feces management", "Enteric pathogens"]</t>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>c("Animalhusbandry", "Fecalcontamination", "Sanitation", "Hygiene", "Animalfecesmanagement", "Entericpathogens")</t>
         </is>
       </c>
     </row>
@@ -13553,6 +13380,9 @@
       <c r="H154" t="b">
         <v>0</v>
       </c>
+      <c r="I154">
+        <v>0</v>
+      </c>
       <c r="L154">
         <v>6</v>
       </c>
@@ -13566,20 +13396,15 @@
           <t>Department of Biological and Agricultural Engineering, North Carolina State University, 3100 Faucette Dr., Raleigh, NC 27695, United States of America</t>
         </is>
       </c>
-      <c r="O154" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W154" t="b">
         <v>0</v>
       </c>
-      <c r="Z154">
+      <c r="AA154">
         <v>3</v>
       </c>
-      <c r="AA154" t="inlineStr">
-        <is>
-          <t>["Natural infrastructure", "Wetland restoration", "Reforestation", "Watershed modeling", SWAT"]</t>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>c("Naturalinfrastructure", "Wetlandrestoration", "Reforestation", "Watershedmodeling")</t>
         </is>
       </c>
     </row>
@@ -13618,6 +13443,9 @@
       <c r="H155" t="b">
         <v>0</v>
       </c>
+      <c r="I155">
+        <v>0</v>
+      </c>
       <c r="L155">
         <v>2</v>
       </c>
@@ -13631,11 +13459,6 @@
           <t>School for Environment and Sustainability, University of Michigan, MI, 48109, Ann Arbor, USA</t>
         </is>
       </c>
-      <c r="O155" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W155" t="b">
         <v>1</v>
       </c>
@@ -13649,12 +13472,12 @@
           <t>on request</t>
         </is>
       </c>
-      <c r="Z155">
-        <v>0</v>
-      </c>
-      <c r="AA155" t="inlineStr">
-        <is>
-          <t>["Hydrogeology", "Climate change", "Sea-level rise", "Saltwater intrusion", "Barrier-island aquifers"]</t>
+      <c r="AA155">
+        <v>0</v>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>c("Hydrogeology", "Climatechange", "Sea-levelrise", "Saltwaterintrusion", "Barrier-islandaquifers")</t>
         </is>
       </c>
     </row>
@@ -13693,6 +13516,9 @@
       <c r="H156" t="b">
         <v>0</v>
       </c>
+      <c r="I156">
+        <v>0</v>
+      </c>
       <c r="L156">
         <v>2</v>
       </c>
@@ -13706,11 +13532,6 @@
           <t>North Carolina State University, Department of Civil, Construction and Environmental Engineering Raleigh, NC, USA</t>
         </is>
       </c>
-      <c r="O156" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q156" t="inlineStr">
         <is>
           <t>0000-0003-1322-1948</t>
@@ -13726,15 +13547,15 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>data not sharable</t>
-        </is>
-      </c>
-      <c r="Z156">
+          <t>not shareable</t>
+        </is>
+      </c>
+      <c r="AA156">
         <v>4</v>
       </c>
-      <c r="AA156" t="inlineStr">
-        <is>
-          <t>["Advanced metering infrastructure", "Water service interruption", "Water Utilities", "Smart meters"]</t>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>c("Advancedmeteringinfrastructure", "Waterserviceinterruption", "WaterUtilities", "Smartmeters")</t>
         </is>
       </c>
     </row>
@@ -13801,24 +13622,24 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>Danica Schaffer-Smith</t>
+        </is>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>Center for Biodiversity Outcomes, Arizona State University, Tempe, AZ, USA</t>
+        </is>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="R157" t="inlineStr">
-        <is>
-          <t>Danica Schaffer-Smith</t>
-        </is>
-      </c>
-      <c r="S157" t="inlineStr">
-        <is>
-          <t>Center for Biodiversity Outcomes, Arizona State University, Tempe, AZ, USA</t>
-        </is>
-      </c>
-      <c r="T157" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="V157" t="inlineStr">
         <is>
           <t>0000-0003-3896-1483</t>
@@ -13827,12 +13648,12 @@
       <c r="W157" t="b">
         <v>0</v>
       </c>
-      <c r="Z157">
+      <c r="AA157">
         <v>6</v>
       </c>
-      <c r="AA157" t="inlineStr">
-        <is>
-          <t>["Nutrient management", "Livestock", "Agriculture", "Machine learning", "Satellite radarSentinel-1"]</t>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>c("Nutrientmanagement", "Livestock", "Agriculture", "Machinelearning", "SatelliteradarSentinel-1")</t>
         </is>
       </c>
     </row>
@@ -13899,33 +13720,33 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>Maria Argos</t>
+        </is>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>Division of Epidemiology and Biostatistics, School of Public Health, University of Illinois at Chicago, 1603 West Taylor Street, Office 878A, Chicago, IL 60612, USA</t>
+        </is>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="R158" t="inlineStr">
-        <is>
-          <t>Maria Argos</t>
-        </is>
-      </c>
-      <c r="S158" t="inlineStr">
-        <is>
-          <t>Division of Epidemiology and Biostatistics, School of Public Health, University of Illinois at Chicago, 1603 West Taylor Street, Office 878A, Chicago, IL 60612, USA</t>
-        </is>
-      </c>
-      <c r="T158" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W158" t="b">
         <v>0</v>
       </c>
-      <c r="Z158">
+      <c r="AA158">
         <v>5</v>
       </c>
-      <c r="AA158" t="inlineStr">
-        <is>
-          <t>["Arsenic", "Private wells", "Water contamination", "Birth outcomes", "Epidemiology"]</t>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>c("Arsenic", "Privatewells", "Watercontamination", "Birthoutcomes", "Epidemiology")</t>
         </is>
       </c>
     </row>
@@ -13990,20 +13811,15 @@
           <t>Key Laboratory of Eco-environments in Three Gorges Reservoir Region, Ministry of Education, College of Environment and Ecology, Chongqing University, Chongqing 400044, China</t>
         </is>
       </c>
-      <c r="O159" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
       <c r="W159" t="b">
         <v>0</v>
       </c>
-      <c r="Z159">
+      <c r="AA159">
         <v>8</v>
       </c>
-      <c r="AA159" t="inlineStr">
-        <is>
-          <t>["Lanthanum containing material", "Lanthanum carbonate", "Phosphorus removal", "Wastewater treatment", "Mineral precipitation"]</t>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>c("Lanthanumcontainingmaterial", "Lanthanumcarbonate", "Phosphorusremoval", "Wastewatertreatment", "Mineralprecipitation")</t>
         </is>
       </c>
     </row>
@@ -14070,33 +13886,33 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>Sonia Grego</t>
+        </is>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>Center for Water, Sanitation, Hygiene and Infectious Disease (WASH-AID), Department of Electrical and Computer Engineering, Duke University, Durham, NC, United States of America</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="R160" t="inlineStr">
-        <is>
-          <t>Sonia Grego</t>
-        </is>
-      </c>
-      <c r="S160" t="inlineStr">
-        <is>
-          <t>Center for Water, Sanitation, Hygiene and Infectious Disease (WASH-AID), Department of Electrical and Computer Engineering, Duke University, Durham, NC, United States of America</t>
-        </is>
-      </c>
-      <c r="T160" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W160" t="b">
         <v>0</v>
       </c>
-      <c r="Z160">
+      <c r="AA160">
         <v>12</v>
       </c>
-      <c r="AA160" t="inlineStr">
-        <is>
-          <t>["Residence hall", "Asymptomatic surveillance", "Positive predictive value", "Clinical case"]</t>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>c("Residencehall", "Asymptomaticsurveillance", "Positivepredictivevalue", "Clinicalcase")</t>
         </is>
       </c>
     </row>
@@ -14163,24 +13979,24 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>Katherine L. Martin</t>
+        </is>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>Department of Forestry and Environmental Resources, North Carolina State University, Raleigh, NC, USA</t>
+        </is>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="R161" t="inlineStr">
-        <is>
-          <t>Katherine L. Martin</t>
-        </is>
-      </c>
-      <c r="S161" t="inlineStr">
-        <is>
-          <t>Department of Forestry and Environmental Resources, North Carolina State University, Raleigh, NC, USA</t>
-        </is>
-      </c>
-      <c r="T161" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="V161" t="inlineStr">
         <is>
           <t>0000-0001-6020-9250</t>
@@ -14189,12 +14005,12 @@
       <c r="W161" t="b">
         <v>0</v>
       </c>
-      <c r="Z161">
+      <c r="AA161">
         <v>6</v>
       </c>
-      <c r="AA161" t="inlineStr">
-        <is>
-          <t>["Infiltration capacity", "Urban hydrology", "Urban soil", "Rainfall-runoff models", "Random forest", "Stormwater"]</t>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>c("Infiltrationcapacity", "Urbanhydrology", "Urbansoil", "Rainfall-runoffmodels", "Randomforest", "Stormwater")</t>
         </is>
       </c>
     </row>
@@ -14233,6 +14049,9 @@
       <c r="H162" t="b">
         <v>0</v>
       </c>
+      <c r="I162">
+        <v>0</v>
+      </c>
       <c r="L162">
         <v>4</v>
       </c>
@@ -14248,24 +14067,24 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>Lok R. Pokhrel</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>Department of Public Health, East Carolina University, Greenville, NC, United States</t>
+        </is>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="R162" t="inlineStr">
-        <is>
-          <t>Lok R. Pokhrel</t>
-        </is>
-      </c>
-      <c r="S162" t="inlineStr">
-        <is>
-          <t>Department of Public Health, East Carolina University, Greenville, NC, United States</t>
-        </is>
-      </c>
-      <c r="T162" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="V162" t="inlineStr">
         <is>
           <t>0000-0002-4606-9973</t>
@@ -14274,12 +14093,12 @@
       <c r="W162" t="b">
         <v>0</v>
       </c>
-      <c r="Z162">
-        <v>0</v>
-      </c>
-      <c r="AA162" t="inlineStr">
-        <is>
-          <t>["Groundwater", "Microbe sampling", "North Carolina", "Coliform", "E. coli", "Water quality"]</t>
+      <c r="AA162">
+        <v>0</v>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>c("Groundwater", "Microbesampling", "NorthCarolina", "Coliform", "E.coli", "Waterquality")</t>
         </is>
       </c>
     </row>
@@ -14318,6 +14137,9 @@
       <c r="H163" t="b">
         <v>0</v>
       </c>
+      <c r="I163">
+        <v>0</v>
+      </c>
       <c r="L163">
         <v>10</v>
       </c>
@@ -14331,20 +14153,15 @@
           <t>Department of Forestry and Environmental Resources, North Carolina State University, Raleigh, N.C., U.SA.</t>
         </is>
       </c>
-      <c r="O163" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W163" t="b">
         <v>0</v>
       </c>
-      <c r="Z163">
-        <v>1</v>
-      </c>
-      <c r="AA163" t="inlineStr">
-        <is>
-          <t>["Rural landscapes", "Nature-based solutions", "Costs", "Economics", "Capital budgeting", "Flood mitigation"]</t>
+      <c r="AA163">
+        <v>1</v>
+      </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>c("Rurallandscapes", "Nature-basedsolutions", "Costs", "Economics", "Capitalbudgeting", "Floodmitigation")</t>
         </is>
       </c>
     </row>
@@ -14383,6 +14200,9 @@
       <c r="H164" t="b">
         <v>0</v>
       </c>
+      <c r="I164">
+        <v>0</v>
+      </c>
       <c r="L164">
         <v>1</v>
       </c>
@@ -14396,11 +14216,6 @@
           <t>University of North Carolina at Greensboro, Department of Geography, Environment, and Sustainability, 237 Graham Bldg., PO Box 26170, Greensboro, NC, 27402-6170, USA</t>
         </is>
       </c>
-      <c r="O164" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q164" t="inlineStr">
         <is>
           <t>0000-0002-9380-7625</t>
@@ -14409,12 +14224,12 @@
       <c r="W164" t="b">
         <v>0</v>
       </c>
-      <c r="Z164">
+      <c r="AA164">
         <v>2</v>
       </c>
-      <c r="AA164" t="inlineStr">
-        <is>
-          <t>["Aquatic ecosystems", "Hydrology", "Land use/land cover", "Physical habitat", "Urban streams", "Water quality"]</t>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>c("Aquaticecosystems", "Hydrology", "Landuse/landcover", "Physicalhabitat", "Urbanstreams", "Waterquality")</t>
         </is>
       </c>
     </row>
@@ -14458,7 +14273,7 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>xlsx &amp; docx</t>
+          <t>c("xlsx", "docx")</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -14479,20 +14294,15 @@
           <t>Department of Marine, Earth, and Atmospheric Sciences, North Carolina State University, Raleigh, NC, United States</t>
         </is>
       </c>
-      <c r="O165" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W165" t="b">
         <v>0</v>
       </c>
-      <c r="Z165">
+      <c r="AA165">
         <v>19</v>
       </c>
-      <c r="AA165" t="inlineStr">
-        <is>
-          <t>["PFAS", "Mass load", "Model", "Source tracking", "Environmental monitoring", "Drinking water"]</t>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>c("PFAS", "Massload", "Model", "Sourcetracking", "Environmentalmonitoring", "Drinkingwater")</t>
         </is>
       </c>
     </row>
@@ -14559,33 +14369,33 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>Mariya Munir</t>
+        </is>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>Department of Civil and Environmental Engineering, University of North Carolina Charlotte, 9201 University City Boulevard, Charlotte, NC 28223, USA</t>
+        </is>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="R166" t="inlineStr">
-        <is>
-          <t>Mariya Munir</t>
-        </is>
-      </c>
-      <c r="S166" t="inlineStr">
-        <is>
-          <t>Department of Civil and Environmental Engineering, University of North Carolina Charlotte, 9201 University City Boulevard, Charlotte, NC 28223, USA</t>
-        </is>
-      </c>
-      <c r="T166" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W166" t="b">
         <v>0</v>
       </c>
-      <c r="Z166">
+      <c r="AA166">
         <v>25</v>
       </c>
-      <c r="AA166" t="inlineStr">
-        <is>
-          <t>["SARS-CoV-2", "Wastewater", "COVID-19", "RT-qPCR", "RT-ddPCR", "Wastewater-based epidemiology (WBE)"]</t>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>c("SARS-CoV-2", "Wastewater", "COVID-19", "RT-qPCR", "RT-ddPCR", "Wastewater-basedepidemiology(WBE)")</t>
         </is>
       </c>
     </row>
@@ -14624,6 +14434,9 @@
       <c r="H167" t="b">
         <v>0</v>
       </c>
+      <c r="I167">
+        <v>0</v>
+      </c>
       <c r="L167">
         <v>3</v>
       </c>
@@ -14639,33 +14452,33 @@
       </c>
       <c r="O167" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>Mohamed A. Youssef</t>
+        </is>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>Department of Biological and Agricultural Engineering, North Carolina State University, Weaver Laboratory, 3110 Faucette Dr., Raleigh, NC 27695-7625, USA</t>
+        </is>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="R167" t="inlineStr">
-        <is>
-          <t>Mohamed A. Youssef</t>
-        </is>
-      </c>
-      <c r="S167" t="inlineStr">
-        <is>
-          <t>Department of Biological and Agricultural Engineering, North Carolina State University, Weaver Laboratory, 3110 Faucette Dr., Raleigh, NC 27695-7625, USA</t>
-        </is>
-      </c>
-      <c r="T167" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W167" t="b">
         <v>0</v>
       </c>
-      <c r="Z167">
+      <c r="AA167">
         <v>9</v>
       </c>
-      <c r="AA167" t="inlineStr">
-        <is>
-          <t>["Subsurface drainage", "Supplemental irrigation", "On-farm water storage", "Irrigation reservoir", "Drainage water reuse", "DRAINMOD-DWR"]</t>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>c("Subsurfacedrainage", "Supplementalirrigation", "On-farmwaterstorage", "Irrigationreservoir", "Drainagewaterreuse", "DRAINMOD-DWR")</t>
         </is>
       </c>
     </row>
@@ -14730,20 +14543,15 @@
           <t>Department of Epidemiology, Gillings School of Global Public Health, University of North Carolina, Chapel Hill, NC 27599, USA</t>
         </is>
       </c>
-      <c r="O168" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W168" t="b">
         <v>0</v>
       </c>
-      <c r="Z168">
+      <c r="AA168">
         <v>6</v>
       </c>
-      <c r="AA168" t="inlineStr">
-        <is>
-          <t>["CAFOs", "Swine", "Hog production", "Animal farming", "Environmental justice", "Gastrointestinal illness"]</t>
+      <c r="AB168" t="inlineStr">
+        <is>
+          <t>c("CAFOs", "Swine", "Hogproduction", "Animalfarming", "Environmentaljustice", "Gastrointestinalillness")</t>
         </is>
       </c>
     </row>
@@ -14782,6 +14590,9 @@
       <c r="H169" t="b">
         <v>0</v>
       </c>
+      <c r="I169">
+        <v>0</v>
+      </c>
       <c r="L169">
         <v>4</v>
       </c>
@@ -14797,24 +14608,24 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>Lok R. Pokhrel</t>
+        </is>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>Department of Public Health, East Carolina University, Greenville, NC, United States</t>
+        </is>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="R169" t="inlineStr">
-        <is>
-          <t>Lok R. Pokhrel</t>
-        </is>
-      </c>
-      <c r="S169" t="inlineStr">
-        <is>
-          <t>Department of Public Health, East Carolina University, Greenville, NC, United States</t>
-        </is>
-      </c>
-      <c r="T169" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="V169" t="inlineStr">
         <is>
           <t>0000-0002-4606-9973</t>
@@ -14823,12 +14634,12 @@
       <c r="W169" t="b">
         <v>0</v>
       </c>
-      <c r="Z169">
-        <v>0</v>
-      </c>
-      <c r="AA169" t="inlineStr">
-        <is>
-          <t>["Groundwater", "Microbe sampling", "North Carolina", "Coliform", "E. coli", "Water quality"]</t>
+      <c r="AA169">
+        <v>0</v>
+      </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>c("Groundwater", "Microbesampling", "NorthCarolina", "Coliform", "E.coli", "Waterquality")</t>
         </is>
       </c>
     </row>
@@ -14872,7 +14683,7 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>xlsx &amp; docx</t>
+          <t>c("xlsx", "docx")</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -14895,33 +14706,33 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>Rebecca C. Fry</t>
+        </is>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>Department of Environmental Sciences and Engineering, Gillings School of Global Public Health, The University of North Carolina at Chapel Hill, Chapel Hill, NC, USA</t>
+        </is>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="R170" t="inlineStr">
-        <is>
-          <t>Rebecca C. Fry</t>
-        </is>
-      </c>
-      <c r="S170" t="inlineStr">
-        <is>
-          <t>Department of Environmental Sciences and Engineering, Gillings School of Global Public Health, The University of North Carolina at Chapel Hill, Chapel Hill, NC, USA</t>
-        </is>
-      </c>
-      <c r="T170" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W170" t="b">
         <v>0</v>
       </c>
-      <c r="Z170">
+      <c r="AA170">
         <v>9</v>
       </c>
-      <c r="AA170" t="inlineStr">
-        <is>
-          <t>["Arsenic", "Manganese", "Lead", "Private wells", "K-means clustering", "Geocoding"]</t>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>c("Arsenic", "Manganese", "Lead", "Privatewells", "K-meansclustering", "Geocoding")</t>
         </is>
       </c>
     </row>
@@ -14986,20 +14797,15 @@
           <t>Department of Epidemiology, Gillings School of Global Public Health, University of North Carolina, Chapel Hill, NC 27599, USA</t>
         </is>
       </c>
-      <c r="O171" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W171" t="b">
         <v>0</v>
       </c>
-      <c r="Z171">
+      <c r="AA171">
         <v>16</v>
       </c>
-      <c r="AA171" t="inlineStr">
-        <is>
-          <t>["Floods", "Hurricanes", "Interrupted time series analysis", "Gastrointestinal illness", "Environmental epidemiology", "Disaster epidemiology"]</t>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>c("Floods", "Hurricanes", "Interruptedtimeseriesanalysis", "Gastrointestinalillness", "Environmentalepidemiology", "Disasterepidemiology")</t>
         </is>
       </c>
     </row>
@@ -15064,11 +14870,6 @@
           <t>Department of Environmental Sciences and Engineering, Gillings School of Global Public Health, University of North Carolina at Chapel Hill, 135 Dauer Drive, Chapel Hill, NC, 27599, USA</t>
         </is>
       </c>
-      <c r="O172" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="Q172" t="inlineStr">
         <is>
           <t>0000-0001-6293-3672</t>
@@ -15077,12 +14878,12 @@
       <c r="W172" t="b">
         <v>0</v>
       </c>
-      <c r="Z172">
+      <c r="AA172">
         <v>9</v>
       </c>
-      <c r="AA172" t="inlineStr">
-        <is>
-          <t>["Bayesian networks", "Drinking water", "Blood lead levels", "Machine learning", "Risk assessment", "Health disparity"]</t>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t>c("Bayesiannetworks", "Drinkingwater", "Bloodleadlevels", "Machinelearning", "Riskassessment", "Healthdisparity")</t>
         </is>
       </c>
     </row>
@@ -15149,33 +14950,33 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>Mariya Munir</t>
+        </is>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>Department of Civil and Environmental Engineering, University of North Carolina Charlotte, 9201 University City Boulevard, Charlotte, NC 28223, USA</t>
+        </is>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="R173" t="inlineStr">
-        <is>
-          <t>Mariya Munir</t>
-        </is>
-      </c>
-      <c r="S173" t="inlineStr">
-        <is>
-          <t>Department of Civil and Environmental Engineering, University of North Carolina Charlotte, 9201 University City Boulevard, Charlotte, NC 28223, USA</t>
-        </is>
-      </c>
-      <c r="T173" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W173" t="b">
         <v>0</v>
       </c>
-      <c r="Z173">
+      <c r="AA173">
         <v>25</v>
       </c>
-      <c r="AA173" t="inlineStr">
-        <is>
-          <t>["SARS-CoV-2", "Wastewater", "COVID-19", "RT-qPCR", "RT-ddPCR", "Wastewater-based epidemiology (WBE)"]</t>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>c("SARS-CoV-2", "Wastewater", "COVID-19", "RT-qPCR", "RT-ddPCR", "Wastewater-basedepidemiology(WBE)")</t>
         </is>
       </c>
     </row>
@@ -15240,20 +15041,15 @@
           <t>University of North Carolina at Chapel Hill, Gillings School of Global Public Health, Department of Environmental Science &amp; Engineering, 135 Dauer Drive, Chapel Hill, NC 27599, United States of America</t>
         </is>
       </c>
-      <c r="O174" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
       <c r="W174" t="b">
         <v>0</v>
       </c>
-      <c r="Z174">
+      <c r="AA174">
         <v>14</v>
       </c>
-      <c r="AA174" t="inlineStr">
-        <is>
-          <t>["Private wells", "Household water treatment", "Health belief model", "Self-efficacy", "Social cognitive theory", "Drinking water"]</t>
+      <c r="AB174" t="inlineStr">
+        <is>
+          <t>c("Privatewells", "Householdwatertreatment", "Healthbeliefmodel", "Self-efficacy", "Socialcognitivetheory", "Drinkingwater")</t>
         </is>
       </c>
     </row>

--- a/inst/extdata/uncnewsletter.xlsx
+++ b/inst/extdata/uncnewsletter.xlsx
@@ -570,7 +570,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>c("drinkingwater", "environmentalpolicy", "healthandsafety")</t>
+          <t>drinkingwater; environmentalpolicy; healthandsafety</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>c("Containerbreeding", "Mosquito", "Mosquitolarvae", "Rainwaterharvesting")</t>
+          <t>Containerbreeding; Mosquito; Mosquitolarvae; Rainwaterharvesting</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>c("https://deq.nc.gov/about/divisions/mitigation-services/dms-planning/dms-web-map", "https://www.nconemap.gov/", "https://doi.org/10.5066/P96HHBIE", "https://doi.org/10.5066/P9UUT74V", "https://websoilsurvey.nrcs.usda.gov/", "https://doi.org/10.5066/P95PTP5G")</t>
+          <t>https://deq.nc.gov/about/divisions/mitigation-services/dms-planning/dms-web-map; https://www.nconemap.gov/; https://doi.org/10.5066/P96HHBIE; https://doi.org/10.5066/P9UUT74V; https://websoilsurvey.nrcs.usda.gov/; https://doi.org/10.5066/P95PTP5G</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>c("compensatorymitigation", "decisionscience", "knowledgecoproduction", "naturalresourcesmanagement", "research-managementpartnerships", "watershedplanning")</t>
+          <t>compensatorymitigation; decisionscience; knowledgecoproduction; naturalresourcesmanagement; research-managementpartnerships; watershedplanning</t>
         </is>
       </c>
     </row>
@@ -987,7 +987,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>c("Drought", "Communications/decision-making", "Decisionsupport", "Localeffects", "Societalimpacts", "Community")</t>
+          <t>Drought; Communications/decision-making; Decisionsupport; Localeffects; Societalimpacts; Community</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>c("environmentaljustice", "privatewells", "toxicmetals")</t>
+          <t>environmentaljustice; privatewells; toxicmetals</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>c("Escherichiacoli", "Plasmid-mediatedquinoloneresistance", "Plasmid-mediatedcolistinresistance", "Poultryworkers", "Chicken", "PoultryEnvironments", "Nigeria")</t>
+          <t>Escherichiacoli; Plasmid-mediatedquinoloneresistance; Plasmid-mediatedcolistinresistance; Poultryworkers; Chicken; PoultryEnvironments; Nigeria</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>c("Stakeholderanalysis", "FEWS", "Environmentalsustainability", "Transdisciplinaryresearch", "Stakeholderengagement", "Livestockproduction")</t>
+          <t>Stakeholderanalysis; FEWS; Environmentalsustainability; Transdisciplinaryresearch; Stakeholderengagement; Livestockproduction</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>c("WaterResources", "Life", "EnvironmentalEducation", "Development", "UN2030Agenda")</t>
+          <t>WaterResources; Life; EnvironmentalEducation; Development; UN2030Agenda</t>
         </is>
       </c>
     </row>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>c("water", "safedrinkingwateract", "environmentallaw", "law", "policy", "publichealth", "NorthCarolina")</t>
+          <t>water; safedrinkingwateract; environmentallaw; law; policy; publichealth; NorthCarolina</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>c("Algalblooms", "dynamicalsystems", "mathmodelling", "nutrienttresholdforresolvableblooms")</t>
+          <t>Algalblooms; dynamicalsystems; mathmodelling; nutrienttresholdforresolvableblooms</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>c("xlsx", "docx")</t>
+          <t>xlsx; docx</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>c("autoantibodies", "autoimmune", "crocodilian", "immunetoxicity", "lupus", "onehealth")</t>
+          <t>autoantibodies; autoimmune; crocodilian; immunetoxicity; lupus; onehealth</t>
         </is>
       </c>
     </row>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>c("privatewells", "environmentaljustice", "drinkingwater", "testing", "metalcontamination")</t>
+          <t>privatewells; environmentaljustice; drinkingwater; testing; metalcontamination</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>c("Infrastructure", "NorthCarolina", "Hurricanes", "NaturalDisasters", "PublicOpinion", "WaterSystems")</t>
+          <t>Infrastructure; NorthCarolina; Hurricanes; NaturalDisasters; PublicOpinion; WaterSystems</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>c("Utilities", "FinancialAssistance", "Durham", "NorthCarolina")</t>
+          <t>Utilities; FinancialAssistance; Durham; NorthCarolina</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>c("PFAS", "Multimorbidity", "ElectronicHealthRecords", "PFOA", "PFHpA", "Chronicdisease")</t>
+          <t>PFAS; Multimorbidity; ElectronicHealthRecords; PFOA; PFHpA; Chronicdisease</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>c("DrinkingWater", "Nitrate", "Disinfectionbyproducts", "Trihalomethanes", "Exposureassessment", "Agriculture", "Cohort")</t>
+          <t>DrinkingWater; Nitrate; Disinfectionbyproducts; Trihalomethanes; Exposureassessment; Agriculture; Cohort</t>
         </is>
       </c>
     </row>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>c("pdf", "xlsx")</t>
+          <t>pdf; xlsx</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>c("pdf", "code")</t>
+          <t>pdf; code</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>c("COVID19", "Viralload", "SARSCoV2", "Epidemiology", "Publicandoccupationalhealth", "NorthCarolina", "Diseasesurveillance", "Virustesting")</t>
+          <t>COVID19; Viralload; SARSCoV2; Epidemiology; Publicandoccupationalhealth; NorthCarolina; Diseasesurveillance; Virustesting</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>c("xlsx", "docx")</t>
+          <t>xlsx; docx</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>c("TropicalCyclones", "Spectralwavemodelling", "Coastalhydrodynamics", "Oceancurrents", "Stormsurge", "Barrierislands")</t>
+          <t>TropicalCyclones; Spectralwavemodelling; Coastalhydrodynamics; Oceancurrents; Stormsurge; Barrierislands</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>c("Pocosin", "Greenhousegases", "Restoration", "Mitigation")</t>
+          <t>Pocosin; Greenhousegases; Restoration; Mitigation</t>
         </is>
       </c>
     </row>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>c("https://ameriflux.lbl.gov/sites/siteinfo/US-Cwt", "https://earthengine.google.com", "https://lpdaac.usgs.gov/products/mod16a2gfv006", "https://www.usgs.gov/core-science-systems/nli/landsat/landsat-provisional-actual-evapotranspiration", "https://www.fs.usda.gov/rds/archive/Catalog/RDS-2019-0026", "https://www.fs.usda.gov/rds/archive/catalog/RDS-2013-0013")</t>
+          <t>https://ameriflux.lbl.gov/sites/siteinfo/US-Cwt; https://earthengine.google.com; https://lpdaac.usgs.gov/products/mod16a2gfv006; https://www.usgs.gov/core-science-systems/nli/landsat/landsat-provisional-actual-evapotranspiration; https://www.fs.usda.gov/rds/archive/Catalog/RDS-2019-0026; https://www.fs.usda.gov/rds/archive/catalog/RDS-2013-0013</t>
         </is>
       </c>
       <c r="AA40">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>c("Evapotranspiration", "Remotesensing", "Topography", "Forestcomposition", "Landsat", "MODIS")</t>
+          <t>Evapotranspiration; Remotesensing; Topography; Forestcomposition; Landsat; MODIS</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>c("https://wastewater.covidsurge.mathematica.org", "https://covid19.ncdhhs.gov/dashboard/data-behind-dashboards")</t>
+          <t>https://wastewater.covidsurge.mathematica.org; https://covid19.ncdhhs.gov/dashboard/data-behind-dashboards</t>
         </is>
       </c>
       <c r="AA41">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>c("WastewaterMonitoring", "Sars-Covid-2", "Covid-19Surge", "EarlyWarning", "AlertAlgorithm")</t>
+          <t>WastewaterMonitoring; Sars-Covid-2; Covid-19Surge; EarlyWarning; AlertAlgorithm</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>c("NonmarketEvaluation", "Waterquality", "Urbanstreams", "Statedpreference")</t>
+          <t>NonmarketEvaluation; Waterquality; Urbanstreams; Statedpreference</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>c("https://scholarworks.iu.edu/dspace/handle/2022/27027", "https://scholarworks.iu.edu/dspace/handle/2022/25638")</t>
+          <t>https://scholarworks.iu.edu/dspace/handle/2022/27027; https://scholarworks.iu.edu/dspace/handle/2022/25638</t>
         </is>
       </c>
       <c r="AA43">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>c("Drinkingwater", "Children", "Leadexposure")</t>
+          <t>Drinkingwater; Children; Leadexposure</t>
         </is>
       </c>
     </row>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>c("FaecalSludgeTreatment", "Composting", "Temperature-timecritera", "pathogeninactivationmechanism", "compostsanitation")</t>
+          <t>FaecalSludgeTreatment; Composting; Temperature-timecritera; pathogeninactivationmechanism; compostsanitation</t>
         </is>
       </c>
     </row>
@@ -3828,7 +3828,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>c("Hazardmitigation", "compoundevent", "flooding", "ruralresilience", "climatechange")</t>
+          <t>Hazardmitigation; compoundevent; flooding; ruralresilience; climatechange</t>
         </is>
       </c>
     </row>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>c("Environmentaljustive", "Ambientwaterquality", "Interfaceswithsociety")</t>
+          <t>Environmentaljustive; Ambientwaterquality; Interfaceswithsociety</t>
         </is>
       </c>
     </row>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>c("urban", "nonpointsource", "watershed", "nitrogen", "hydrology", "management")</t>
+          <t>urban; nonpointsource; watershed; nitrogen; hydrology; management</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>c("sandhills", "seepageflux", "groundwater", "surfacewater", "spatialvariability", "hydrology")</t>
+          <t>sandhills; seepageflux; groundwater; surfacewater; spatialvariability; hydrology</t>
         </is>
       </c>
     </row>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>c("https://github.com/bernardoct/WaterPaths/tree/JLWTPAgreementsModel", "https://www.hydroshare.org/resource/3fc8e01960d948a2bd38189dd4e7fa69")</t>
+          <t>https://github.com/bernardoct/WaterPaths/tree/JLWTPAgreementsModel; https://www.hydroshare.org/resource/3fc8e01960d948a2bd38189dd4e7fa69</t>
         </is>
       </c>
       <c r="AA49">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>c("waterutility", "cooperation", "demand", "deepuncertainty", "optimization", "financialrisk")</t>
+          <t>waterutility; cooperation; demand; deepuncertainty; optimization; financialrisk</t>
         </is>
       </c>
     </row>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>c("https://github.com/acgold/HTF-on-roads", "https://doi.org/10.5281/zenodo.5562568")</t>
+          <t>https://github.com/acgold/HTF-on-roads; https://doi.org/10.5281/zenodo.5562568</t>
         </is>
       </c>
       <c r="AA50">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>c("coastaldevelopment", "stormwatermanagement", "infrastructure", "inundationmodeling", "high-tideflooding")</t>
+          <t>coastaldevelopment; stormwatermanagement; infrastructure; inundationmodeling; high-tideflooding</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>c("erosion", "land-usechange", "legacysediment", "slope-areatreshold", ".", "soilnutrients", "streamchannelinitiation")</t>
+          <t>erosion; land-usechange; legacysediment; slope-areatreshold; .; soilnutrients; streamchannelinitiation</t>
         </is>
       </c>
     </row>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>c("collaborativegovernance", "policybeliefs", "regionalwaterplanning", "Gobernanzacolaborativa", "creenciaspolíticas", "planificaciónregionaldelagua", "协作治理", "政策信念", "区域水资源规划")</t>
+          <t>collaborativegovernance; policybeliefs; regionalwaterplanning; Gobernanzacolaborativa; creenciaspolíticas; planificaciónregionaldelagua; 协作治理; 政策信念; 区域水资源规划</t>
         </is>
       </c>
     </row>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>c("biology-geologyfeebacks", "DMQ99", "evapotranspiration", "headwaterstreams", "landusechange", "seasonalflashiness", "specificconductance", "streamgauges")</t>
+          <t>biology-geologyfeebacks; DMQ99; evapotranspiration; headwaterstreams; landusechange; seasonalflashiness; specificconductance; streamgauges</t>
         </is>
       </c>
     </row>
@@ -4763,7 +4763,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>c("WASP", "environmentalmodeling", "nanocopper", "nanomaterials", "freswater")</t>
+          <t>WASP; environmentalmodeling; nanocopper; nanomaterials; freswater</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>c("healtheducation", "healthinformationneeds", "healthprofessionals", "informationdissemination", "informationliteracy", "informationseekingbehavior", "patienteducation", "research", "qualitative")</t>
+          <t>healtheducation; healthinformationneeds; healthprofessionals; informationdissemination; informationliteracy; informationseekingbehavior; patienteducation; research; qualitative</t>
         </is>
       </c>
     </row>
@@ -5002,7 +5002,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>c("crAssphage", "Municipaluntreatedwastewater", "Temporalvariations", "Spatialvariations", "Entericpathogenscorrelations", "Bacteria", "Andviruses", ";", "qPCR", "rt-qPCR")</t>
+          <t>crAssphage; Municipaluntreatedwastewater; Temporalvariations; Spatialvariations; Entericpathogenscorrelations; Bacteria; Andviruses; ;; qPCR; rt-qPCR</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>c("ArtificialNeuralNetworks", "Geneticprogramming", "Antedcedentenvironmentalconditions", "Temperature", "Salinity", "Oysters")</t>
+          <t>ArtificialNeuralNetworks; Geneticprogramming; Antedcedentenvironmentalconditions; Temperature; Salinity; Oysters</t>
         </is>
       </c>
     </row>
@@ -5336,8 +5336,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>c("https://www.ebi.ac.uk/ena/browser/view/PRJEB40798", "https://www.ebi.ac.uk/ena/browser/view/PRJEB40816", "https://www.ebi.ac.uk/ena/browser/view/PRJEB40815", "https://www.ebi.ac.uk/ena/browser/view/PRJEB27621", "https://www.ebi.ac.uk/ena/browser/view/PRJEB51229", "https://www.ebi.ac.uk/ena/browser/view/ERP015409", "https://bitbucket.org/genomicepidemiology/resfinder_db", "https://ccb-microbe.cs.uni-saarland.de/plsdb/plasmids/download/", "https://www.arb-silva.de/download/arb-files/", "https://benlangmead.github.io/aws-indexes/k2"
-)</t>
+          <t>https://www.ebi.ac.uk/ena/browser/view/PRJEB40798; https://www.ebi.ac.uk/ena/browser/view/PRJEB40816; https://www.ebi.ac.uk/ena/browser/view/PRJEB40815; https://www.ebi.ac.uk/ena/browser/view/PRJEB27621; https://www.ebi.ac.uk/ena/browser/view/PRJEB51229; https://www.ebi.ac.uk/ena/browser/view/ERP015409; https://bitbucket.org/genomicepidemiology/resfinder_db; https://ccb-microbe.cs.uni-saarland.de/plsdb/plasmids/download/; https://www.arb-silva.de/download/arb-files/; https://benlangmead.github.io/aws-indexes/k2</t>
         </is>
       </c>
       <c r="AA63">
@@ -5345,7 +5344,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>c("Antimicrobialresistance", "Metagenomics", "Microbialecology", "Policyandpublichealthinmicrobiology")</t>
+          <t>Antimicrobialresistance; Metagenomics; Microbialecology; Policyandpublichealthinmicrobiology</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5432,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>c("Pretermbirth", "Lowbirthweight", "Adversebirthoutcome", "Pollutedsites", "Superfund", "Industrialsites")</t>
+          <t>Pretermbirth; Lowbirthweight; Adversebirthoutcome; Pollutedsites; Superfund; Industrialsites</t>
         </is>
       </c>
     </row>
@@ -5551,7 +5550,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>c("Carboncycle", "Climate-changemitigation", "Environmentalimpact")</t>
+          <t>Carboncycle; Climate-changemitigation; Environmentalimpact</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5658,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>c("ChemicalEngineering", "Waterresources")</t>
+          <t>ChemicalEngineering; Waterresources</t>
         </is>
       </c>
     </row>
@@ -5745,7 +5744,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>c("https://github.com/TransformingDrainageProject/Drain-Flow-Gap-Filling", "https://github.com/isudatateam/datateam")</t>
+          <t>https://github.com/TransformingDrainageProject/Drain-Flow-Gap-Filling; https://github.com/isudatateam/datateam</t>
         </is>
       </c>
       <c r="AA67">
@@ -5753,7 +5752,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>c("Agriculture", "Environmentalimpact", "Hydrology", "Waterresources")</t>
+          <t>Agriculture; Environmentalimpact; Hydrology; Waterresources</t>
         </is>
       </c>
     </row>
@@ -5978,7 +5977,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>c("docx", "tif")</t>
+          <t>docx; tif</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -6374,7 +6373,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>c("Cryptosporidium", "Bacillusspores", "MS2coliphage", "bromine", "chlorine", "disinfection", "watertreatment")</t>
+          <t>Cryptosporidium; Bacillusspores; MS2coliphage; bromine; chlorine; disinfection; watertreatment</t>
         </is>
       </c>
     </row>
@@ -6477,7 +6476,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>c("PFASdestruction", "fluoroethers", "GenX", "Nafionbyproduct2", "photolysis")</t>
+          <t>PFASdestruction; fluoroethers; GenX; Nafionbyproduct2; photolysis</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6586,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>c("https://doi.org/10.5281/zenodo.7135955", "https://sunnydayflood.apps.cloudapps.unc.edu", "https://github.com/sunny-day-flooding-project", "https://doi.org/10.5281/zenodo.7017187")</t>
+          <t>https://doi.org/10.5281/zenodo.7135955; https://sunnydayflood.apps.cloudapps.unc.edu; https://github.com/sunny-day-flooding-project; https://doi.org/10.5281/zenodo.7017187</t>
         </is>
       </c>
       <c r="AA76">
@@ -6595,7 +6594,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>c("coastalflooding", "low-costsensors", "hightideflooding", "stormwatermanagement", "coastalinfrastructure", "sealevelrise")</t>
+          <t>coastalflooding; low-costsensors; hightideflooding; stormwatermanagement; coastalinfrastructure; sealevelrise</t>
         </is>
       </c>
     </row>
@@ -6639,7 +6638,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>c("docx", "csv")</t>
+          <t>docx; csv</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -6712,7 +6711,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>c("xlsx", "docx")</t>
+          <t>xlsx; docx</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -6761,7 +6760,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>c("PFAS", "Drinkingwater", "USEPA", "PFPrA", "Ultra-shortchain")</t>
+          <t>PFAS; Drinkingwater; USEPA; PFPrA; Ultra-shortchain</t>
         </is>
       </c>
     </row>
@@ -6849,7 +6848,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>c("coastal", "fecalbacteria", "runoff", "stormwater")</t>
+          <t>coastal; fecalbacteria; runoff; stormwater</t>
         </is>
       </c>
     </row>
@@ -6937,7 +6936,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>c("cyanobacteria", "cyanotoxin", "microcystin", "stormwaterpollution", "eutrophication")</t>
+          <t>cyanobacteria; cyanotoxin; microcystin; stormwaterpollution; eutrophication</t>
         </is>
       </c>
     </row>
@@ -7005,7 +7004,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>c("waterscarcity", "waterrecycling", "wastewatertreatmentplants", "nutrients", "phosphorus")</t>
+          <t>waterscarcity; waterrecycling; wastewatertreatmentplants; nutrients; phosphorus</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7117,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>c("HWTS", "POU", "chitosan", "coagulation", "sandfiltration", "bacterialreduction", "virusreduction")</t>
+          <t>HWTS; POU; chitosan; coagulation; sandfiltration; bacterialreduction; virusreduction</t>
         </is>
       </c>
     </row>
@@ -7221,7 +7220,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>c("environmentaljustice", "privatewells", "toxicmetals")</t>
+          <t>environmentaljustice; privatewells; toxicmetals</t>
         </is>
       </c>
     </row>
@@ -7284,7 +7283,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>c("explainability", "LSPmethod", "waterquality", "decision-making")</t>
+          <t>explainability; LSPmethod; waterquality; decision-making</t>
         </is>
       </c>
     </row>
@@ -7369,7 +7368,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>c("https://coast.noaa.gov/slrdata/", "https://coast.noaa.gov/slrdata/", "https://fris.nc.gov/fris/Home.aspx?ST=NC", "https://earthexplorer.usgs.gov/", "https://deq.nc.gov/about/divisions/coastal", "https://www.nconemap.gov/pages/parcels")</t>
+          <t>https://coast.noaa.gov/slrdata/; https://coast.noaa.gov/slrdata/; https://fris.nc.gov/fris/Home.aspx?ST=NC; https://earthexplorer.usgs.gov/; https://deq.nc.gov/about/divisions/coastal; https://www.nconemap.gov/pages/parcels</t>
         </is>
       </c>
       <c r="AA85">
@@ -7377,7 +7376,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>c("wetlands", "nature-basedsolutions", "floodmitigation", "coastalflooding", "tidalwatersheds")</t>
+          <t>wetlands; nature-basedsolutions; floodmitigation; coastalflooding; tidalwatersheds</t>
         </is>
       </c>
     </row>
@@ -7465,7 +7464,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>c("reclaimedwater", "waterreuse", "water-supplysystems", "agro-wastewater", "riskassessment")</t>
+          <t>reclaimedwater; waterreuse; water-supplysystems; agro-wastewater; riskassessment</t>
         </is>
       </c>
     </row>
@@ -7555,7 +7554,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>c("https://www.nconemap.gov/", "https://www.nrcs.usda.gov/wps/portal/nrcs/detail/soils/survey/geo/?cid=nrcs142p2_053628", "https://www.nconemap.gov/", "https://www.nconemap.gov/")</t>
+          <t>https://www.nconemap.gov/; https://www.nrcs.usda.gov/wps/portal/nrcs/detail/soils/survey/geo/?cid=nrcs142p2_053628; https://www.nconemap.gov/; https://www.nconemap.gov/</t>
         </is>
       </c>
       <c r="AA87">
@@ -7563,7 +7562,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>c("geospatialanalysis", "landsuitability", "floodmitigation", "nature-basedsolutions(NBS)", "rurallandscapes", "GeographicInformationSystems(GIS)", "floodresilience")</t>
+          <t>geospatialanalysis; landsuitability; floodmitigation; nature-basedsolutions(NBS); rurallandscapes; GeographicInformationSystems(GIS); floodresilience</t>
         </is>
       </c>
     </row>
@@ -7651,7 +7650,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>c("reclaimedwater", "waterreuse", "water-supplysystems", "agro-wastewater", "riskassessment")</t>
+          <t>reclaimedwater; waterreuse; water-supplysystems; agro-wastewater; riskassessment</t>
         </is>
       </c>
     </row>
@@ -7739,7 +7738,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>c("coastal", "eutrophicationsepticsystems")</t>
+          <t>coastal; eutrophicationsepticsystems</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7801,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>c("hydrologicdrought", "SoutheastUS", "NationalWaterModel")</t>
+          <t>hydrologicdrought; SoutheastUS; NationalWaterModel</t>
         </is>
       </c>
     </row>
@@ -7887,7 +7886,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>c("https://www.census.gov/data/developers/data-sets/acs-5year.html", "https://www.epa.gov/ground-water-and-drinking-water/safe-drinking-water-information-system-sdwis-federal-reporting")</t>
+          <t>https://www.census.gov/data/developers/data-sets/acs-5year.html; https://www.epa.gov/ground-water-and-drinking-water/safe-drinking-water-information-system-sdwis-federal-reporting</t>
         </is>
       </c>
       <c r="AA91">
@@ -7895,7 +7894,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>c("droughtandhealth", "droughtrisk", "LocalMoran", "sI", "droughtvulnerability", "U.S.drought")</t>
+          <t>droughtandhealth; droughtrisk; LocalMoran; sI; droughtvulnerability; U.S.drought</t>
         </is>
       </c>
     </row>
@@ -7973,7 +7972,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>c("environmentalplanning", "policyevaluation", "riparianbuffers")</t>
+          <t>environmentalplanning; policyevaluation; riparianbuffers</t>
         </is>
       </c>
     </row>
@@ -8066,7 +8065,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>c("coastalwetlanddegradation", "remotesensing", "NDVI", "climatechange", "sea-levelrise", "saltwaterintrusion", "hydrologicmodel", "AlligatorRiverNationalWildlifeRefuge", "USA")</t>
+          <t>coastalwetlanddegradation; remotesensing; NDVI; climatechange; sea-levelrise; saltwaterintrusion; hydrologicmodel; AlligatorRiverNationalWildlifeRefuge; USA</t>
         </is>
       </c>
     </row>
@@ -8164,7 +8163,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>c("waterinfrastructure", "waterservices", "waterutilities", "waterbills", "billingfrequency", "customerassistanceprograms(CAPS)", "affordability")</t>
+          <t>waterinfrastructure; waterservices; waterutilities; waterbills; billingfrequency; customerassistanceprograms(CAPS); affordability</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8207,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>c("pdf", "xlsx")</t>
+          <t>pdf; xlsx</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -8242,7 +8241,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>c("canine", "drinkingwater", "equine", "fluoroether", "OneHealth", "nafionby-product2", "GenXchemicals", "PFOA", "PFOS")</t>
+          <t>canine; drinkingwater; equine; fluoroether; OneHealth; nafionby-product2; GenXchemicals; PFOA; PFOS</t>
         </is>
       </c>
     </row>
@@ -8310,7 +8309,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>c("drinkingwater", "fluoropolymers", "food", "safety", "toxins")</t>
+          <t>drinkingwater; fluoropolymers; food; safety; toxins</t>
         </is>
       </c>
     </row>
@@ -8373,7 +8372,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>c("Airpollution", "Color", "Environmentalpollution", "Environmentalscience", "Impurities")</t>
+          <t>Airpollution; Color; Environmentalpollution; Environmentalscience; Impurities</t>
         </is>
       </c>
     </row>
@@ -8417,7 +8416,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>c("pdf", "html")</t>
+          <t>pdf; html</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -8466,7 +8465,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>c("lead", "Children", "shealth", "drinkingwater", "machinelearning", "riskassessment")</t>
+          <t>lead; Children; shealth; drinkingwater; machinelearning; riskassessment</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8568,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>c("PFASair-waterinterfacialadsorption", "QSPR", "nonequilibrium", "unsaturatedcolumns", "panfilm")</t>
+          <t>PFASair-waterinterfacialadsorption; QSPR; nonequilibrium; unsaturatedcolumns; panfilm</t>
         </is>
       </c>
     </row>
@@ -8652,7 +8651,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>c("adsorption", "molecules", "nanofibers", "remediation")</t>
+          <t>adsorption; molecules; nanofibers; remediation</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8695,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>c("pdf", "xlsx")</t>
+          <t>pdf; xlsx</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -8750,7 +8749,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>c("nontargetedanalysis", "anthropogenicchemicals", "wastewater", "landfillleachate", "reverseosmosis")</t>
+          <t>nontargetedanalysis; anthropogenicchemicals; wastewater; landfillleachate; reverseosmosis</t>
         </is>
       </c>
     </row>
@@ -8853,7 +8852,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>c("per-andpolyfluoroalkylsubstances(PFAS)", "presumptivecontamination", "PFAStestingandinvestigation", "AFFF", "PFASwasteanddisposal")</t>
+          <t>per-andpolyfluoroalkylsubstances(PFAS); presumptivecontamination; PFAStestingandinvestigation; AFFF; PFASwasteanddisposal</t>
         </is>
       </c>
     </row>
@@ -8921,7 +8920,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>c("anatomy", "genetics", "infectiousdiseases", "viruses", "wastewater")</t>
+          <t>anatomy; genetics; infectiousdiseases; viruses; wastewater</t>
         </is>
       </c>
     </row>
@@ -9019,7 +9018,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>c("coalash", "lacustrinesediment", "multiproxytracing", "aquaticecosystems")</t>
+          <t>coalash; lacustrinesediment; multiproxytracing; aquaticecosystems</t>
         </is>
       </c>
     </row>
@@ -9087,7 +9086,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>c("waterandsanitationinfrastructure", "disadvantagedunincorporatedcommunities", "environmetaljustice", "participatoryprocess", "sociotechnicaldesign")</t>
+          <t>waterandsanitationinfrastructure; disadvantagedunincorporatedcommunities; environmetaljustice; participatoryprocess; sociotechnicaldesign</t>
         </is>
       </c>
     </row>
@@ -9185,7 +9184,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>c("textiledyes", "environmentalpollution", "cleanwater", "sustainability", "polycarbodiimide", "topologicalpolarsurfacearea(TPSA)", "moleculartransport")</t>
+          <t>textiledyes; environmentalpollution; cleanwater; sustainability; polycarbodiimide; topologicalpolarsurfacearea(TPSA); moleculartransport</t>
         </is>
       </c>
     </row>
@@ -9283,7 +9282,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>c("land-useregression", "molecularmicrobialsourcetracking", "surfacewater", "sediment", "rivernetworks", "animalfeedingoperations", "septicsystems")</t>
+          <t>land-useregression; molecularmicrobialsourcetracking; surfacewater; sediment; rivernetworks; animalfeedingoperations; septicsystems</t>
         </is>
       </c>
     </row>
@@ -9356,7 +9355,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>c("multiplewatersourceuse", "supplementalunimprovedsourceuse", "fecalcontamination", "MonteCarlosimulations", "drinkingwaterquality", "low-andmiddle-incomecountries")</t>
+          <t>multiplewatersourceuse; supplementalunimprovedsourceuse; fecalcontamination; MonteCarlosimulations; drinkingwaterquality; low-andmiddle-incomecountries</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9443,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>c("Microplasticsinrivers", "Watermanagement", "DiversionsAbstraction", "Pairedcatchmentapproach", "Globalmodels")</t>
+          <t>Microplasticsinrivers; Watermanagement; DiversionsAbstraction; Pairedcatchmentapproach; Globalmodels</t>
         </is>
       </c>
     </row>
@@ -9527,7 +9526,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>c("Pocosin", "Carbon", "Methane", "GHG", "Netecosystemexchange", "Hydrologicrestoration", "Peatland", "Evergreenshrubbog", "Watertabledepth", "Eddycovariance", "", "Carbondioxide")</t>
+          <t>Pocosin; Carbon; Methane; GHG; Netecosystemexchange; Hydrologicrestoration; Peatland; Evergreenshrubbog; Watertabledepth; Eddycovariance; Carbondioxide</t>
         </is>
       </c>
     </row>
@@ -9610,7 +9609,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>c("Per-andpolyfluoroalkylsubstances", "PFAS", "Drinkingwater", "Serum", "Humanhealthoutcomes")</t>
+          <t>Per-andpolyfluoroalkylsubstances; PFAS; Drinkingwater; Serum; Humanhealthoutcomes</t>
         </is>
       </c>
     </row>
@@ -9654,7 +9653,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>c("pdf", "xlsx")</t>
+          <t>pdf; xlsx</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -9695,7 +9694,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>c("https://www.sciencebase.gov/catalog/item/5fad56aad34eb413d5df459c", "https://www.sciencebase.gov/catalog/item/5ab3d60be4b081f61ab5e3d4")</t>
+          <t>https://www.sciencebase.gov/catalog/item/5fad56aad34eb413d5df459c; https://www.sciencebase.gov/catalog/item/5ab3d60be4b081f61ab5e3d4</t>
         </is>
       </c>
       <c r="AA112">
@@ -9703,7 +9702,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>c("Per-andpolyfluoroalkylsubstances", "Drinking-water", "Public-supply", "Private-wellsSources", "Healtheffect")</t>
+          <t>Per-andpolyfluoroalkylsubstances; Drinking-water; Public-supply; Private-wellsSources; Healtheffect</t>
         </is>
       </c>
     </row>
@@ -9811,7 +9810,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>c("Zikavirus", "wastewater-basedepidemiology", "resource-constrainedsettings")</t>
+          <t>Zikavirus; wastewater-basedepidemiology; resource-constrainedsettings</t>
         </is>
       </c>
     </row>
@@ -9914,7 +9913,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>c("Airpollutioncontrol", "Biologicalgastreatment", "Capillaryreactor", "Hydrophobicpollutants", "Segmentedflow")</t>
+          <t>Airpollutioncontrol; Biologicalgastreatment; Capillaryreactor; Hydrophobicpollutants; Segmentedflow</t>
         </is>
       </c>
     </row>
@@ -9997,7 +9996,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>c("Marinemicroalgae", "Dunaliellaviridis", "Flocculation", "Harvesting", "Waterreuse", "Dissolvedorganicmatter")</t>
+          <t>Marinemicroalgae; Dunaliellaviridis; Flocculation; Harvesting; Waterreuse; Dissolvedorganicmatter</t>
         </is>
       </c>
     </row>
@@ -10041,7 +10040,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>c("pdf", "xlsx")</t>
+          <t>pdf; xlsx</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -10077,7 +10076,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>c("https://www.ncei.noaa.gov", "https://github.com/davidfastovich/gds_climate_reconstruction")</t>
+          <t>https://www.ncei.noaa.gov; https://github.com/davidfastovich/gds_climate_reconstruction</t>
         </is>
       </c>
       <c r="AA116">
@@ -10085,7 +10084,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>c("Palynology", "Plantmacrofossil", "Charcoal", "Paleoclimatereconstruction", "Sea-levelrise", "Wildfire", "Wetlanddevelopment", "Hydroperiod")</t>
+          <t>Palynology; Plantmacrofossil; Charcoal; Paleoclimatereconstruction; Sea-levelrise; Wildfire; Wetlanddevelopment; Hydroperiod</t>
         </is>
       </c>
     </row>
@@ -10158,7 +10157,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>c("Microbiome", "Outdoorair", "Greenspace", "AirborneBacteria", "16SrRNA", "Aerobiome")</t>
+          <t>Microbiome; Outdoorair; Greenspace; AirborneBacteria; 16SrRNA; Aerobiome</t>
         </is>
       </c>
     </row>
@@ -10299,7 +10298,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>c("Watersecurity", "Textanalysis", "Structuraltopicmodeling", "Planning", "Environmentaljustice")</t>
+          <t>Watersecurity; Textanalysis; Structuraltopicmodeling; Planning; Environmentaljustice</t>
         </is>
       </c>
     </row>
@@ -10407,7 +10406,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>c("crAssphage", "Municipaluntreatedwastewater", "Temporalvariations", "Spatialvariations", "Entericpathogenscorrelations", "Bacteria", "Andviruses", "qPCR", "rt-qPCR")</t>
+          <t>crAssphage; Municipaluntreatedwastewater; Temporalvariations; Spatialvariations; Entericpathogenscorrelations; Bacteria; Andviruses; qPCR; rt-qPCR</t>
         </is>
       </c>
     </row>
@@ -10490,7 +10489,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>c("Groundwatercontamination", "Swinelagoons", "Privatewells", "Atmosphericstressors", "Environmentalpollution")</t>
+          <t>Groundwatercontamination; Swinelagoons; Privatewells; Atmosphericstressors; Environmentalpollution</t>
         </is>
       </c>
     </row>
@@ -10573,7 +10572,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>c("Microplastics", "Streamflow", "Urbandevelopment", "Sediment", "Watershed", "Samplingmethod")</t>
+          <t>Microplastics; Streamflow; Urbandevelopment; Sediment; Watershed; Samplingmethod</t>
         </is>
       </c>
     </row>
@@ -10661,7 +10660,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>c("UAV", "UAS", "Rugosity", "Geomorphometry", "Coastalhabitat", "Remotesensing")</t>
+          <t>UAV; UAS; Rugosity; Geomorphometry; Coastalhabitat; Remotesensing</t>
         </is>
       </c>
     </row>
@@ -10705,7 +10704,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>c("docx", "pdf")</t>
+          <t>docx; pdf</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -10739,7 +10738,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>c("Hospital-aquiredinfection", "Multidrug-resistantpathogen", "Environmentalcleaning", "Probiotic", "Randomized-controlledtrial", "Environmentalhygiene", "MRSAVRE", "Multidrug-resistantGram-negative")</t>
+          <t>Hospital-aquiredinfection; Multidrug-resistantpathogen; Environmentalcleaning; Probiotic; Randomized-controlledtrial; Environmentalhygiene; MRSAVRE; Multidrug-resistantGram-negative</t>
         </is>
       </c>
     </row>
@@ -10817,7 +10816,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>c("Atmosphericforcing", "CapeHatteras", "PEACH", "Atmosphericcyclones", "Atmosphericwarmandcoolseasons")</t>
+          <t>Atmosphericforcing; CapeHatteras; PEACH; Atmosphericcyclones; Atmosphericwarmandcoolseasons</t>
         </is>
       </c>
     </row>
@@ -10910,7 +10909,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>c("Contamination", "Distribution", "Environment", "Healthimpact", "NorthCarolina", "PFASsources")</t>
+          <t>Contamination; Distribution; Environment; Healthimpact; NorthCarolina; PFASsources</t>
         </is>
       </c>
     </row>
@@ -10983,7 +10982,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>c("Landscapechange", "Climatechange", "Attribution", "NeuseRiver", "Sea-levelrise", "Marshloss")</t>
+          <t>Landscapechange; Climatechange; Attribution; NeuseRiver; Sea-levelrise; Marshloss</t>
         </is>
       </c>
     </row>
@@ -11081,7 +11080,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>c("Clustering", "Metals", "Privatewells", "Socialvulnerability", "Geographicdata")</t>
+          <t>Clustering; Metals; Privatewells; Socialvulnerability; Geographicdata</t>
         </is>
       </c>
     </row>
@@ -11164,7 +11163,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>c("Groundwatercontamination", "Swinelagoons", "Privatewells", "Atmosphericstressors", "Environmentalpollution")</t>
+          <t>Groundwatercontamination; Swinelagoons; Privatewells; Atmosphericstressors; Environmentalpollution</t>
         </is>
       </c>
     </row>
@@ -11262,7 +11261,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>c("Microbioreactor", "Volatileorganiccompound", "Biofiltration", "Modeling")</t>
+          <t>Microbioreactor; Volatileorganiccompound; Biofiltration; Modeling</t>
         </is>
       </c>
     </row>
@@ -11370,7 +11369,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>c("Biofiltration", "Cometabolism", "Adsorption", "Emergingcontaminants")</t>
+          <t>Biofiltration; Cometabolism; Adsorption; Emergingcontaminants</t>
         </is>
       </c>
     </row>
@@ -11478,7 +11477,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>c("Subsurfacedrainage", "Subirrigation", "On-farmwaterstorage", "Drainagewaterreuse", "Supplementalirrigation", "Surfacewaterquality")</t>
+          <t>Subsurfacedrainage; Subirrigation; On-farmwaterstorage; Drainagewaterreuse; Supplementalirrigation; Surfacewaterquality</t>
         </is>
       </c>
     </row>
@@ -11639,7 +11638,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>c("Wastewater-basedepidemiology", "Passivesampling", "Mooreswab")</t>
+          <t>Wastewater-basedepidemiology; Passivesampling; Mooreswab</t>
         </is>
       </c>
     </row>
@@ -11722,7 +11721,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>c("Groundwatercontamination", "Swinelagoons", "Privatewells", "Atmosphericstressors", "Environmentalpollution")</t>
+          <t>Groundwatercontamination; Swinelagoons; Privatewells; Atmosphericstressors; Environmentalpollution</t>
         </is>
       </c>
     </row>
@@ -11825,7 +11824,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>c("SARS-CoV-2", "Wastewater-basedepidemiology", "Universitycampus", "Emergingcontaminants", "Disinfectants")</t>
+          <t>SARS-CoV-2; Wastewater-basedepidemiology; Universitycampus; Emergingcontaminants; Disinfectants</t>
         </is>
       </c>
     </row>
@@ -11903,7 +11902,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>c("Geographicinformationsystems", "Ruralgeography", "statisticalanalysis")</t>
+          <t>Geographicinformationsystems; Ruralgeography; statisticalanalysis</t>
         </is>
       </c>
     </row>
@@ -11976,7 +11975,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>c("Forestedwatersheds", "FUTURESmodel", "Landuselandcoverchange(LULCC)", "Hydrologicmodeling", "SoilandWaterAssessmentTool(SWAT)", "Globalclimatemodel")</t>
+          <t>Forestedwatersheds; FUTURESmodel; Landuselandcoverchange(LULCC); Hydrologicmodeling; SoilandWaterAssessmentTool(SWAT); Globalclimatemodel</t>
         </is>
       </c>
     </row>
@@ -12020,7 +12019,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>c("xlsx", "docx")</t>
+          <t>xlsx; docx</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -12079,7 +12078,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>c("VOC", "Contaminantflux", "Groundwater", "Stream")</t>
+          <t>VOC; Contaminantflux; Groundwater; Stream</t>
         </is>
       </c>
     </row>
@@ -12147,7 +12146,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>c("CoastalaltimetrySealevel", "Waves", "Videocamera", "Tidegauge", "Buoy", "Altimeter", "Significantwaveheight", "Re-trackingalgorithm")</t>
+          <t>CoastalaltimetrySealevel; Waves; Videocamera; Tidegauge; Buoy; Altimeter; Significantwaveheight; Re-trackingalgorithm</t>
         </is>
       </c>
     </row>
@@ -12250,7 +12249,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>c("Wastewater-basedepidemiology", "Sewagesurveillance", "Coronavirus", "COVID", "ddPCR")</t>
+          <t>Wastewater-basedepidemiology; Sewagesurveillance; Coronavirus; COVID; ddPCR</t>
         </is>
       </c>
     </row>
@@ -12348,7 +12347,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>c("Clustering", "Metals", "Privatewells", "Socialvulnerability", "Geographicdata")</t>
+          <t>Clustering; Metals; Privatewells; Socialvulnerability; Geographicdata</t>
         </is>
       </c>
     </row>
@@ -12461,7 +12460,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>c("GHGEmissions", "Waterextractable", "Phosphorus", "Zinc", "Copper", "NorthCarolina")</t>
+          <t>GHGEmissions; Waterextractable; Phosphorus; Zinc; Copper; NorthCarolina</t>
         </is>
       </c>
     </row>
@@ -12534,7 +12533,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>c("Risk", "Compoundhazard", "Flood", "Rural", "Emergencymanagement", "Planning", "CCWE")</t>
+          <t>Risk; Compoundhazard; Flood; Rural; Emergencymanagement; Planning; CCWE</t>
         </is>
       </c>
     </row>
@@ -12637,7 +12636,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>c("ExtraintestinalpathogenicE.coli(ExPEC)", "Foodborneurinarytractinfection(fUTI)", "Concentratedanimalfeedingoperation(CAFO)", "Syndromicsurveillance", "Besag-York-Mollié(BYM)model", "Ecologicalregressionanalysis")</t>
+          <t>ExtraintestinalpathogenicE.coli(ExPEC); Foodborneurinarytractinfection(fUTI); Concentratedanimalfeedingoperation(CAFO); Syndromicsurveillance; Besag-York-Mollié(BYM)model; Ecologicalregressionanalysis</t>
         </is>
       </c>
     </row>
@@ -12720,7 +12719,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>c("Sourceapportionment", "Receptormodels", "PFAS", "Perfluoroalkylsubstances")</t>
+          <t>Sourceapportionment; Receptormodels; PFAS; Perfluoroalkylsubstances</t>
         </is>
       </c>
     </row>
@@ -12808,7 +12807,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>c("Waterquality", "ToxicCyanobacteria", "Airquality", "PM2.5", "Microcystis", "Dolichospermum")</t>
+          <t>Waterquality; ToxicCyanobacteria; Airquality; PM2.5; Microcystis; Dolichospermum</t>
         </is>
       </c>
     </row>
@@ -12916,7 +12915,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>c("Permeance", "Selectivity", "Rejection", "Advectivetransport", "Diffusivetransport")</t>
+          <t>Permeance; Selectivity; Rejection; Advectivetransport; Diffusivetransport</t>
         </is>
       </c>
     </row>
@@ -13014,7 +13013,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>c("Nutrientmanagement", "Livestock", "Agriculture", "Machinelearning", "SatelliteradarSentinel-1")</t>
+          <t>Nutrientmanagement; Livestock; Agriculture; Machinelearning; SatelliteradarSentinel-1</t>
         </is>
       </c>
     </row>
@@ -13058,7 +13057,7 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>c("xlsx", "docx")</t>
+          <t>xlsx; docx</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -13102,7 +13101,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>c("Nitrogenremoval", "Denitrification", "Anammox", "nosZ", "hzo", "Sediments")</t>
+          <t>Nitrogenremoval; Denitrification; Anammox; nosZ; hzo; Sediments</t>
         </is>
       </c>
     </row>
@@ -13175,7 +13174,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>c("CAFOs", "Swine", "Hogproduction", "Animalfarming", "Environmentaljustice", "Gastrointestinalillness")</t>
+          <t>CAFOs; Swine; Hogproduction; Animalfarming; Environmentaljustice; Gastrointestinalillness</t>
         </is>
       </c>
     </row>
@@ -13219,7 +13218,7 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>c("xlsx", "docx")</t>
+          <t>xlsx; docx</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -13248,7 +13247,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>c("PFAS", "Massload", "Model", "Sourcetracking", "Environmentalmonitoring", "Drinkingwater")</t>
+          <t>PFAS; Massload; Model; Sourcetracking; Environmentalmonitoring; Drinkingwater</t>
         </is>
       </c>
     </row>
@@ -13341,7 +13340,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>c("Animalhusbandry", "Fecalcontamination", "Sanitation", "Hygiene", "Animalfecesmanagement", "Entericpathogens")</t>
+          <t>Animalhusbandry; Fecalcontamination; Sanitation; Hygiene; Animalfecesmanagement; Entericpathogens</t>
         </is>
       </c>
     </row>
@@ -13404,7 +13403,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>c("Naturalinfrastructure", "Wetlandrestoration", "Reforestation", "Watershedmodeling")</t>
+          <t>Naturalinfrastructure; Wetlandrestoration; Reforestation; Watershedmodeling</t>
         </is>
       </c>
     </row>
@@ -13477,7 +13476,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>c("Hydrogeology", "Climatechange", "Sea-levelrise", "Saltwaterintrusion", "Barrier-islandaquifers")</t>
+          <t>Hydrogeology; Climatechange; Sea-levelrise; Saltwaterintrusion; Barrier-islandaquifers</t>
         </is>
       </c>
     </row>
@@ -13555,7 +13554,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>c("Advancedmeteringinfrastructure", "Waterserviceinterruption", "WaterUtilities", "Smartmeters")</t>
+          <t>Advancedmeteringinfrastructure; Waterserviceinterruption; WaterUtilities; Smartmeters</t>
         </is>
       </c>
     </row>
@@ -13653,7 +13652,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>c("Nutrientmanagement", "Livestock", "Agriculture", "Machinelearning", "SatelliteradarSentinel-1")</t>
+          <t>Nutrientmanagement; Livestock; Agriculture; Machinelearning; SatelliteradarSentinel-1</t>
         </is>
       </c>
     </row>
@@ -13746,7 +13745,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>c("Arsenic", "Privatewells", "Watercontamination", "Birthoutcomes", "Epidemiology")</t>
+          <t>Arsenic; Privatewells; Watercontamination; Birthoutcomes; Epidemiology</t>
         </is>
       </c>
     </row>
@@ -13819,7 +13818,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>c("Lanthanumcontainingmaterial", "Lanthanumcarbonate", "Phosphorusremoval", "Wastewatertreatment", "Mineralprecipitation")</t>
+          <t>Lanthanumcontainingmaterial; Lanthanumcarbonate; Phosphorusremoval; Wastewatertreatment; Mineralprecipitation</t>
         </is>
       </c>
     </row>
@@ -13912,7 +13911,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>c("Residencehall", "Asymptomaticsurveillance", "Positivepredictivevalue", "Clinicalcase")</t>
+          <t>Residencehall; Asymptomaticsurveillance; Positivepredictivevalue; Clinicalcase</t>
         </is>
       </c>
     </row>
@@ -14010,7 +14009,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>c("Infiltrationcapacity", "Urbanhydrology", "Urbansoil", "Rainfall-runoffmodels", "Randomforest", "Stormwater")</t>
+          <t>Infiltrationcapacity; Urbanhydrology; Urbansoil; Rainfall-runoffmodels; Randomforest; Stormwater</t>
         </is>
       </c>
     </row>
@@ -14098,7 +14097,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>c("Groundwater", "Microbesampling", "NorthCarolina", "Coliform", "E.coli", "Waterquality")</t>
+          <t>Groundwater; Microbesampling; NorthCarolina; Coliform; E.coli; Waterquality</t>
         </is>
       </c>
     </row>
@@ -14161,7 +14160,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>c("Rurallandscapes", "Nature-basedsolutions", "Costs", "Economics", "Capitalbudgeting", "Floodmitigation")</t>
+          <t>Rurallandscapes; Nature-basedsolutions; Costs; Economics; Capitalbudgeting; Floodmitigation</t>
         </is>
       </c>
     </row>
@@ -14229,7 +14228,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>c("Aquaticecosystems", "Hydrology", "Landuse/landcover", "Physicalhabitat", "Urbanstreams", "Waterquality")</t>
+          <t>Aquaticecosystems; Hydrology; Landuse/landcover; Physicalhabitat; Urbanstreams; Waterquality</t>
         </is>
       </c>
     </row>
@@ -14273,7 +14272,7 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>c("xlsx", "docx")</t>
+          <t>xlsx; docx</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -14302,7 +14301,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>c("PFAS", "Massload", "Model", "Sourcetracking", "Environmentalmonitoring", "Drinkingwater")</t>
+          <t>PFAS; Massload; Model; Sourcetracking; Environmentalmonitoring; Drinkingwater</t>
         </is>
       </c>
     </row>
@@ -14395,7 +14394,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>c("SARS-CoV-2", "Wastewater", "COVID-19", "RT-qPCR", "RT-ddPCR", "Wastewater-basedepidemiology(WBE)")</t>
+          <t>SARS-CoV-2; Wastewater; COVID-19; RT-qPCR; RT-ddPCR; Wastewater-basedepidemiology(WBE)</t>
         </is>
       </c>
     </row>
@@ -14478,7 +14477,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>c("Subsurfacedrainage", "Supplementalirrigation", "On-farmwaterstorage", "Irrigationreservoir", "Drainagewaterreuse", "DRAINMOD-DWR")</t>
+          <t>Subsurfacedrainage; Supplementalirrigation; On-farmwaterstorage; Irrigationreservoir; Drainagewaterreuse; DRAINMOD-DWR</t>
         </is>
       </c>
     </row>
@@ -14551,7 +14550,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>c("CAFOs", "Swine", "Hogproduction", "Animalfarming", "Environmentaljustice", "Gastrointestinalillness")</t>
+          <t>CAFOs; Swine; Hogproduction; Animalfarming; Environmentaljustice; Gastrointestinalillness</t>
         </is>
       </c>
     </row>
@@ -14639,7 +14638,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>c("Groundwater", "Microbesampling", "NorthCarolina", "Coliform", "E.coli", "Waterquality")</t>
+          <t>Groundwater; Microbesampling; NorthCarolina; Coliform; E.coli; Waterquality</t>
         </is>
       </c>
     </row>
@@ -14683,7 +14682,7 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>c("xlsx", "docx")</t>
+          <t>xlsx; docx</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -14732,7 +14731,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>c("Arsenic", "Manganese", "Lead", "Privatewells", "K-meansclustering", "Geocoding")</t>
+          <t>Arsenic; Manganese; Lead; Privatewells; K-meansclustering; Geocoding</t>
         </is>
       </c>
     </row>
@@ -14805,7 +14804,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>c("Floods", "Hurricanes", "Interruptedtimeseriesanalysis", "Gastrointestinalillness", "Environmentalepidemiology", "Disasterepidemiology")</t>
+          <t>Floods; Hurricanes; Interruptedtimeseriesanalysis; Gastrointestinalillness; Environmentalepidemiology; Disasterepidemiology</t>
         </is>
       </c>
     </row>
@@ -14883,7 +14882,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>c("Bayesiannetworks", "Drinkingwater", "Bloodleadlevels", "Machinelearning", "Riskassessment", "Healthdisparity")</t>
+          <t>Bayesiannetworks; Drinkingwater; Bloodleadlevels; Machinelearning; Riskassessment; Healthdisparity</t>
         </is>
       </c>
     </row>
@@ -14976,7 +14975,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>c("SARS-CoV-2", "Wastewater", "COVID-19", "RT-qPCR", "RT-ddPCR", "Wastewater-basedepidemiology(WBE)")</t>
+          <t>SARS-CoV-2; Wastewater; COVID-19; RT-qPCR; RT-ddPCR; Wastewater-basedepidemiology(WBE)</t>
         </is>
       </c>
     </row>
@@ -15049,7 +15048,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>c("Privatewells", "Householdwatertreatment", "Healthbeliefmodel", "Self-efficacy", "Socialcognitivetheory", "Drinkingwater")</t>
+          <t>Privatewells; Householdwatertreatment; Healthbeliefmodel; Self-efficacy; Socialcognitivetheory; Drinkingwater</t>
         </is>
       </c>
     </row>

--- a/inst/extdata/uncnewsletter.xlsx
+++ b/inst/extdata/uncnewsletter.xlsx
@@ -557,6 +557,11 @@
           <t>North Carolina State University</t>
         </is>
       </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q2" t="inlineStr">
         <is>
           <t>0000-0002-5778-354X</t>
@@ -635,6 +640,11 @@
           <t>North Carolina State University</t>
         </is>
       </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="W3" t="b">
         <v>0</v>
       </c>
@@ -703,6 +713,11 @@
           <t>University of North Carolina</t>
         </is>
       </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q4" t="inlineStr">
         <is>
           <t>0000-0002-1906-8692</t>
@@ -781,6 +796,11 @@
           <t>Shenyang Ligong University</t>
         </is>
       </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
       <c r="W5" t="b">
         <v>0</v>
       </c>
@@ -839,6 +859,11 @@
           <t>Longwood University</t>
         </is>
       </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="W6" t="b">
         <v>0</v>
       </c>
@@ -902,6 +927,11 @@
           <t>North Carolina State University</t>
         </is>
       </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>0000-0002-2365-6200</t>
@@ -982,6 +1012,11 @@
           <t>University of South Carolina</t>
         </is>
       </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="W8" t="b">
         <v>0</v>
       </c>
@@ -1064,7 +1099,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="W9" t="b">
@@ -1145,6 +1180,11 @@
           <t>North Carolina State University</t>
         </is>
       </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>0000-0003-4213-6929</t>
@@ -1223,6 +1263,11 @@
           <t>University of Nebraska-Lincoln</t>
         </is>
       </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q11" t="inlineStr">
         <is>
           <t>0000-0002-0371-7125</t>
@@ -1301,6 +1346,11 @@
           <t>University of North Carolina Wilmington</t>
         </is>
       </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="W12" t="b">
         <v>0</v>
       </c>
@@ -1359,6 +1409,11 @@
           <t>National Renewable Energy Lab NREL</t>
         </is>
       </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q13" t="inlineStr">
         <is>
           <t>0000-0002-3774-9571</t>
@@ -1419,6 +1474,11 @@
           <t>Universidade Regional do Noroeste do Estado do Rio Grande do Sul</t>
         </is>
       </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
       <c r="Q14" t="inlineStr">
         <is>
           <t>0000-0003-1591-3622</t>
@@ -1484,6 +1544,11 @@
           <t>Duke Law School</t>
         </is>
       </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="W15" t="b">
         <v>0</v>
       </c>
@@ -1544,6 +1609,11 @@
           <t>University of North Carolina at Chapel Hill</t>
         </is>
       </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>0000-0001-6999-8268</t>
@@ -1624,7 +1694,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="AA17">
@@ -1687,6 +1757,11 @@
           <t>University of North Carolina</t>
         </is>
       </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="AA18">
         <v>0</v>
       </c>
@@ -1731,7 +1806,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>xlsx; docx</t>
+          <t>xlsx; xlsx; docx</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1769,7 +1844,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -1855,6 +1930,11 @@
           <t>University of North Carolina</t>
         </is>
       </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q20" t="inlineStr">
         <is>
           <t>0000-0001-8681-0597</t>
@@ -1925,6 +2005,11 @@
           <t>North Carolina State University</t>
         </is>
       </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="W21" t="b">
         <v>1</v>
       </c>
@@ -1991,6 +2076,11 @@
       <c r="N22" t="inlineStr">
         <is>
           <t>University of North Carolina</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -2058,6 +2148,11 @@
           <t>University of North Carolina</t>
         </is>
       </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q23" t="inlineStr">
         <is>
           <t>0000-0002-3078-6716</t>
@@ -2146,6 +2241,11 @@
           <t>University of Georgia</t>
         </is>
       </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q24" t="inlineStr">
         <is>
           <t>0000-0003-2112-3846</t>
@@ -2219,6 +2319,11 @@
           <t>Duke University</t>
         </is>
       </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="W25" t="b">
         <v>0</v>
       </c>
@@ -2279,6 +2384,11 @@
           <t>North Carolina State University</t>
         </is>
       </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="W26" t="b">
         <v>0</v>
       </c>
@@ -2349,6 +2459,11 @@
           <t>US EPA</t>
         </is>
       </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q27" t="inlineStr">
         <is>
           <t>0000-0002-6322-4349</t>
@@ -2434,7 +2549,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -2537,7 +2652,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="W29" t="b">
@@ -2654,6 +2769,11 @@
           <t>University of California</t>
         </is>
       </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q31" t="inlineStr">
         <is>
           <t>0000-0002-1050-6721</t>
@@ -2734,6 +2854,11 @@
           <t>WHO</t>
         </is>
       </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
       <c r="W32" t="b">
         <v>1</v>
       </c>
@@ -2834,7 +2959,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -2894,7 +3019,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>xlsx; docx</t>
+          <t>xlsx; xlsx; docx</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2913,6 +3038,11 @@
       <c r="N34" t="inlineStr">
         <is>
           <t>North Carolina State University</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -3010,7 +3140,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -3109,6 +3239,11 @@
           <t>independent</t>
         </is>
       </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="AA37">
         <v>0</v>
       </c>
@@ -3279,7 +3414,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -3370,6 +3505,11 @@
           <t>North Carolina State University</t>
         </is>
       </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="W40" t="b">
         <v>1</v>
       </c>
@@ -3458,6 +3598,11 @@
           <t>Mathematice Inc.</t>
         </is>
       </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q41" t="inlineStr">
         <is>
           <t>0000-0002-4324-6807</t>
@@ -3551,6 +3696,11 @@
           <t>North Carolina State University</t>
         </is>
       </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q42" t="inlineStr">
         <is>
           <t>0000-0002-5604-8754</t>
@@ -3644,6 +3794,11 @@
           <t>Indiana University</t>
         </is>
       </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q43" t="inlineStr">
         <is>
           <t>0000-0002-5468-0713</t>
@@ -3737,6 +3892,11 @@
           <t>University of North Carolina</t>
         </is>
       </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q44" t="inlineStr">
         <is>
           <t>0000-0002-3317-7318</t>
@@ -3815,6 +3975,11 @@
           <t>East Carolina University</t>
         </is>
       </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q45" t="inlineStr">
         <is>
           <t>0000-0003-2315-7062</t>
@@ -3893,6 +4058,11 @@
           <t>North Carolina State University</t>
         </is>
       </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q46" t="inlineStr">
         <is>
           <t>0000-0003-3160-5363</t>
@@ -3971,6 +4141,11 @@
           <t>University of North Carolina</t>
         </is>
       </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q47" t="inlineStr">
         <is>
           <t>0000-0002-6982-8768</t>
@@ -4043,7 +4218,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>docx; xlsx; zip; zip; zip</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4062,6 +4237,11 @@
       <c r="N48" t="inlineStr">
         <is>
           <t>University of Utah</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -4157,6 +4337,11 @@
           <t>University of North Carolina</t>
         </is>
       </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q49" t="inlineStr">
         <is>
           <t>0000-0002-3078-6716</t>
@@ -4250,6 +4435,11 @@
           <t>University of North Carolina</t>
         </is>
       </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q50" t="inlineStr">
         <is>
           <t>0000-0002-0921-0384</t>
@@ -4343,6 +4533,11 @@
           <t>North Carolina State University</t>
         </is>
       </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q51" t="inlineStr">
         <is>
           <t>0000-0001-6115-6322</t>
@@ -4421,6 +4616,11 @@
           <t>University of Georgia</t>
         </is>
       </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q52" t="inlineStr">
         <is>
           <t>0000-0003-2112-3846</t>
@@ -4521,7 +4721,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -4587,6 +4787,11 @@
           <t>Davidson College</t>
         </is>
       </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q54" t="inlineStr">
         <is>
           <t>0000-0002-3799-5019</t>
@@ -4677,6 +4882,11 @@
           <t>Research Triangle Institute</t>
         </is>
       </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q55" t="inlineStr">
         <is>
           <t>0000-0003-3641-737X</t>
@@ -4750,6 +4960,11 @@
           <t>Center for Environmental Measurement &amp; Modeling</t>
         </is>
       </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q56" t="inlineStr">
         <is>
           <t>0000-0001-6231-9437</t>
@@ -4818,6 +5033,11 @@
           <t>North Carolina State University</t>
         </is>
       </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q57" t="inlineStr">
         <is>
           <t>0000-0001-7360-0021</t>
@@ -4886,6 +5106,11 @@
           <t>University of California</t>
         </is>
       </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q58" t="inlineStr">
         <is>
           <t>0000-0002-3039-9927</t>
@@ -4976,7 +5201,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -5074,7 +5299,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -5157,7 +5382,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -5248,6 +5473,11 @@
           <t>North Carolina State University</t>
         </is>
       </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="W62" t="b">
         <v>0</v>
       </c>
@@ -5295,7 +5525,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>pdf; pdf; xlsx; zip; pdf</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -5314,6 +5544,11 @@
       <c r="N63" t="inlineStr">
         <is>
           <t>Technical University of Denmark</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -5409,6 +5644,11 @@
           <t>University of North Carolina</t>
         </is>
       </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q64" t="inlineStr">
         <is>
           <t>0000-0002-3445-6589</t>
@@ -5476,7 +5716,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>pdf; pdf; pdf; pdf; xlsx</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -5519,7 +5759,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -5632,7 +5872,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -5723,6 +5963,11 @@
           <t>USDA-ARS</t>
         </is>
       </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q67" t="inlineStr">
         <is>
           <t>0000-0002-0176-7815</t>
@@ -5819,7 +6064,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -5884,7 +6129,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>pdf; pdf; pdf; pdf</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -5922,7 +6167,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -5977,7 +6222,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>docx; tif</t>
+          <t>docx; tif; tif; tif</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -5996,6 +6241,11 @@
       <c r="N70" t="inlineStr">
         <is>
           <t>Department of Biological &amp; Agricultural Engineering, NC State University, Raleigh, NC, United States of America</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
@@ -6065,7 +6315,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>docx</t>
+          <t>docx; docx; docx</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -6084,6 +6334,11 @@
       <c r="N71" t="inlineStr">
         <is>
           <t>Nelson Mandela African Institution of Science and Technology, Arusha, Tanzania</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>United Republic of Tanzania</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
@@ -6196,7 +6451,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="W72" t="b">
@@ -6267,6 +6522,11 @@
           <t>Environmental Intervention Unit, Infectious Disease Division, icddr,b, Dhaka, Bangladesh</t>
         </is>
       </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
       <c r="Q73" t="inlineStr">
         <is>
           <t>0000-0003-0520-2683</t>
@@ -6362,7 +6622,7 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="W74" t="b">
@@ -6460,7 +6720,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -6563,7 +6823,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
@@ -6659,6 +6919,11 @@
           <t>Nicholas Institute for Energy, Environment and Sustainability, Duke University, Durham, North Carolina, United States of America</t>
         </is>
       </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q77" t="inlineStr">
         <is>
           <t>0000-0002-7512-7845</t>
@@ -6732,6 +6997,11 @@
           <t>Natural Resources Defense Council, 111 Sutter St. Floor 20, San Francisco, CA 94104, USA</t>
         </is>
       </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="R78" t="inlineStr">
         <is>
           <t>Anna Reade</t>
@@ -6825,6 +7095,11 @@
           <t>Department of Health Education and Promotion, East Carolina University, Greenville, NC 27858, USA</t>
         </is>
       </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q79" t="inlineStr">
         <is>
           <t>0000-0003-2664-4763</t>
@@ -6913,6 +7188,11 @@
           <t>Center for Marine Sciences, University of North Carolina Wilmington, 5600 Marvin K. Moss Ln., Wilmington, NC 28409, USA</t>
         </is>
       </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q80" t="inlineStr">
         <is>
           <t>0000-0001-8701-7654</t>
@@ -6991,6 +7271,11 @@
           <t>CIEPQPF, Department of Chemical Engineering, University of Coimbra, 3030-790 Coimbra, Portugal</t>
         </is>
       </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
       <c r="Q81" t="inlineStr">
         <is>
           <t>0000-0002-0944-8632</t>
@@ -7091,7 +7376,7 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
@@ -7194,7 +7479,7 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="W83" t="b">
@@ -7275,6 +7560,11 @@
           <t>Department of Computer Science, San Francisco State University, 1600 Holloway Ave, San Francisco, CA 94132, USA</t>
         </is>
       </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="W84" t="b">
         <v>0</v>
       </c>
@@ -7348,6 +7638,11 @@
           <t>Department of Earth and Ocean Sciences, University of North Carolina Wilmington, 601 S College Rd., Wilmington, NC 28403, USA</t>
         </is>
       </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q85" t="inlineStr">
         <is>
           <t>0000-0002-6591-7237</t>
@@ -7441,6 +7736,11 @@
           <t>Department of Environmental Sciences and Engineering, Gillings School of Global Public Health, The University of North Carolina at Chapel Hill, Chapel Hill, NC 27599, USA</t>
         </is>
       </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q86" t="inlineStr">
         <is>
           <t>0000-0003-1292-0771</t>
@@ -7536,7 +7836,7 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="W87" t="b">
@@ -7627,6 +7927,11 @@
           <t>Department of Environmental Sciences and Engineering, Gillings School of Global Public Health, The University of North Carolina at Chapel Hill, Chapel Hill, NC 27599, USA</t>
         </is>
       </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q88" t="inlineStr">
         <is>
           <t>0000-0003-1292-0771</t>
@@ -7715,6 +8020,11 @@
           <t>Department of Health Education and Promotion, East Carolina University, Greenville, NC 27858, USA</t>
         </is>
       </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q89" t="inlineStr">
         <is>
           <t>0000-0003-2664-4763</t>
@@ -7793,6 +8103,11 @@
           <t>Department of Geosciences, Mississippi State University, Mississippi State, MS 39762, USA</t>
         </is>
       </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="W90" t="b">
         <v>0</v>
       </c>
@@ -7866,6 +8181,11 @@
           <t>Department of Environmental, Agricultural, and Occupational Health, College of Public Health, University of Nebraska Medical Center, Omaha, NE 68198, USA</t>
         </is>
       </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q91" t="inlineStr">
         <is>
           <t>0000-0003-1143-1191</t>
@@ -7959,6 +8279,11 @@
           <t>Department of City and Regional Planning, University of North Carolina at Chapel Hill, Chapel Hill, NC 27599, USA</t>
         </is>
       </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q92" t="inlineStr">
         <is>
           <t>0000-0002-2834-3764</t>
@@ -8037,6 +8362,11 @@
           <t>Earth and Climate Sciences, Nicholas School of the Environment, Duke University, Durham, NC 27708, USA</t>
         </is>
       </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q93" t="inlineStr">
         <is>
           <t>0000-0001-5793-8583</t>
@@ -8137,7 +8467,7 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="W94" t="b">
@@ -8228,6 +8558,11 @@
           <t>Center for Environmental and Health Effects of PFAS, Department of Biological Sciences, North Carolina State University, Raleigh, North Carolina 27695, United States</t>
         </is>
       </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q95" t="inlineStr">
         <is>
           <t>0000-0003-2954-1110</t>
@@ -8296,6 +8631,11 @@
           <t>Department of Biological Sciences, North Carolina State University, Raleigh, North Carolina 27695, United States</t>
         </is>
       </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q96" t="inlineStr">
         <is>
           <t>0000-0002-5289-1218</t>
@@ -8437,6 +8777,11 @@
           <t>RTI International, Research Triangle Park, North Carolina 27709, United States</t>
         </is>
       </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q98" t="inlineStr">
         <is>
           <t>0000-0001-6293-3672</t>
@@ -8552,7 +8897,7 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="V99" t="inlineStr">
@@ -8640,7 +8985,7 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="W100" t="b">
@@ -8733,7 +9078,7 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="V101" t="inlineStr">
@@ -8836,7 +9181,7 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
@@ -8907,6 +9252,11 @@
           <t>EPCOR Water Services Inc., Edmonton, Alberta T5H 0E8, Canada</t>
         </is>
       </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
       <c r="Q103" t="inlineStr">
         <is>
           <t>0000-0001-9488-8124</t>
@@ -8964,7 +9314,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>xlsx</t>
+          <t>xlsx; xlsx; xlsx; xlsx; xlsx; pdf</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -9002,7 +9352,7 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="V104" t="inlineStr">
@@ -9073,6 +9423,11 @@
           <t>Department of Anthropology, University of South Florida, Tampa, Florida 33620, United States</t>
         </is>
       </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q105" t="inlineStr">
         <is>
           <t>0000-0003-1966-2680</t>
@@ -9168,7 +9523,7 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="V106" t="inlineStr">
@@ -9271,7 +9626,7 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="W107" t="b">
@@ -9347,6 +9702,11 @@
           <t>Department of Civil, Construction, and Environmental Engineering, North Carolina State University, Fitts-Woolard Hall, 915 Partners Way, Rm 3250, Raleigh, North Carolina 27695, United States</t>
         </is>
       </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="W108" t="b">
         <v>0</v>
       </c>
@@ -9420,6 +9780,11 @@
           <t>School of Geography, Earth and Environmental Sciences, University of Birmingham, Edgbaston, Birmingham B15 2TT, United Kingdom</t>
         </is>
       </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>United Kingdom of Great Britain and Northern Ireland</t>
+        </is>
+      </c>
       <c r="Q109" t="inlineStr">
         <is>
           <t>0000-0002-7008-0371</t>
@@ -9508,6 +9873,11 @@
           <t>Duke University Wetland Center, Nicholas School of the Environment, Duke University, Box 90333, Durham, NC 27708, USA</t>
         </is>
       </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="W110" t="b">
         <v>1</v>
       </c>
@@ -9591,6 +9961,11 @@
           <t>Nicholas School of the Environment, Duke University, Durham 27710, NC, USA</t>
         </is>
       </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="W111" t="b">
         <v>1</v>
       </c>
@@ -9674,6 +10049,11 @@
           <t>U.S. Geological Survey, Lawrenceville, NJ, US</t>
         </is>
       </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q112" t="inlineStr">
         <is>
           <t>0000-0002-1214-4920</t>
@@ -9789,7 +10169,7 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="W113" t="b">
@@ -9978,6 +10358,11 @@
           <t>Department of Civil, Construction, and Environmental Engineering, North Carolina State University, 915 Partners Way, Raleigh, NC 27695, USA</t>
         </is>
       </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="W115" t="b">
         <v>1</v>
       </c>
@@ -10040,7 +10425,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>pdf; xlsx</t>
+          <t>pdf; xlsx; xlsx</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -10059,6 +10444,11 @@
       <c r="N116" t="inlineStr">
         <is>
           <t>U.S. Geological Survey, Florence Bascom Geoscience Center, MS 926A, Reston, VA, USA</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="W116" t="b">
@@ -10139,6 +10529,11 @@
           <t>United States Environmental Protection Agency, Center for Public Health and Environmental Assessment, Office of Research and Development, Research Triangle Park, NC, USA</t>
         </is>
       </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="W117" t="b">
         <v>1</v>
       </c>
@@ -10222,6 +10617,11 @@
           <t>Department of Environmental Sciences and Engineering, Gillings School of Global Public Health, University of North Carolina at Chapel Hill, Chapel Hill, NC, USA</t>
         </is>
       </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="W118" t="b">
         <v>0</v>
       </c>
@@ -10280,6 +10680,11 @@
           <t>The Roux Institute, Northeastern University 100 Fore St. Portland, ME USA 04101</t>
         </is>
       </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="W119" t="b">
         <v>1</v>
       </c>
@@ -10385,7 +10790,7 @@
       </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="W120" t="b">
@@ -10471,6 +10876,11 @@
           <t>Haub School of Environment and Natural Resources, University of Wyoming, USA</t>
         </is>
       </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="W121" t="b">
         <v>1</v>
       </c>
@@ -10554,6 +10964,11 @@
           <t>Biological and Agricultural Engineering, North Carolina State University, Raleigh, NC, USA</t>
         </is>
       </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="W122" t="b">
         <v>1</v>
       </c>
@@ -10637,6 +11052,11 @@
           <t>School of Forest, Fisheries, and Geomatics Sciences, University of Florida, Gainesville, FL, USA</t>
         </is>
       </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q123" t="inlineStr">
         <is>
           <t>0000-0002-2843-4965</t>
@@ -10725,6 +11145,11 @@
           <t>Institute of Hygiene and Environmental Medicine, Charité–Universitätsmedizin Berlin, Corporate Member of Freie Universität Berlin, Humboldt-Universität zu Berlin and Berlin Institute of Health, Berlin, Germany</t>
         </is>
       </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
       <c r="Q124" t="inlineStr">
         <is>
           <t>0000-0002-1225-9023</t>
@@ -10793,6 +11218,11 @@
           <t>University of North Carolina, Chapel Hill, NC, USA</t>
         </is>
       </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q125" t="inlineStr">
         <is>
           <t>0000-0001-6309-1403</t>
@@ -10873,7 +11303,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
@@ -10888,7 +11318,7 @@
       </c>
       <c r="T126" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="W126" t="b">
@@ -10964,6 +11394,11 @@
           <t>Earth Surface Systems Program, University of Kentucky, USA</t>
         </is>
       </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="W127" t="b">
         <v>1</v>
       </c>
@@ -11054,7 +11489,7 @@
       </c>
       <c r="T128" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="W128" t="b">
@@ -11145,6 +11580,11 @@
           <t>Haub School of Environment and Natural Resources, University of Wyoming, USA</t>
         </is>
       </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="W129" t="b">
         <v>1</v>
       </c>
@@ -11235,7 +11675,7 @@
       </c>
       <c r="T130" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="V130" t="inlineStr">
@@ -11343,7 +11783,7 @@
       </c>
       <c r="T131" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="V131" t="inlineStr">
@@ -11456,7 +11896,7 @@
       </c>
       <c r="T132" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="W132" t="b">
@@ -11532,6 +11972,11 @@
           <t>University of North Carolina at Chapel Hill, Institute of Marine Sciences, Morehead City NC 28557, USA</t>
         </is>
       </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="W133" t="b">
         <v>0</v>
       </c>
@@ -11617,7 +12062,7 @@
       </c>
       <c r="T134" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="W134" t="b">
@@ -11703,6 +12148,11 @@
           <t>Haub School of Environment and Natural Resources, University of Wyoming, USA</t>
         </is>
       </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="W135" t="b">
         <v>1</v>
       </c>
@@ -11879,6 +12329,11 @@
           <t>North Carolina Central University, Department of Environmental, Earth and Geospatial Sciences, 1246 Mary M, Townes Science Complex, 1801 Fayetteville St., Durham, NC, 27707, USA</t>
         </is>
       </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q137" t="inlineStr">
         <is>
           <t>0000-0001-9333-9641</t>
@@ -11957,6 +12412,11 @@
           <t>North Carolina State University, Department of Forestry and Environmental Resources, 2800 Faucette Dr, Raleigh, NC 27695, USA</t>
         </is>
       </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="W138" t="b">
         <v>1</v>
       </c>
@@ -12057,7 +12517,7 @@
       </c>
       <c r="T139" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="W139" t="b">
@@ -12133,6 +12593,11 @@
           <t>Ecosystems and Fishery Resources Laboratory, Institute of Fisheries and Aquatic Sciences, University of Douala, BP 2701 Douala, Cameroon</t>
         </is>
       </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>Cameroon</t>
+        </is>
+      </c>
       <c r="Q140" t="inlineStr">
         <is>
           <t>0000-0001-7724-5805</t>
@@ -12228,7 +12693,7 @@
       </c>
       <c r="T141" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="W141" t="b">
@@ -12321,7 +12786,7 @@
       </c>
       <c r="T142" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="W142" t="b">
@@ -12434,7 +12899,7 @@
       </c>
       <c r="T143" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="V143" t="inlineStr">
@@ -12515,6 +12980,11 @@
           <t>Dr. John Lining Professor of Physics and Director of the James B. Near Center for Climate Studies, The Citadel, 171 Moultrie Street, Charleston, SC, USA</t>
         </is>
       </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="W144" t="b">
         <v>1</v>
       </c>
@@ -12615,7 +13085,7 @@
       </c>
       <c r="T145" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="W145" t="b">
@@ -12676,11 +13146,11 @@
         <v>1</v>
       </c>
       <c r="I146">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>docx; zip</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -12699,6 +13169,11 @@
       <c r="N146" t="inlineStr">
         <is>
           <t>Department of Biological Sciences, North Carolina State University, Raleigh, NC, USA</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="W146" t="b">
@@ -12784,6 +13259,11 @@
           <t>UNC-Chapel Hill, Earth, Marine, and Environmental Sciences, Institute of Marine Sciences, 3431 Arendell St., Morehead City, NC 28577, United States of America</t>
         </is>
       </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q147" t="inlineStr">
         <is>
           <t>0000-0001-8823-0457</t>
@@ -12889,7 +13369,7 @@
       </c>
       <c r="T148" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="V148" t="inlineStr">
@@ -12997,7 +13477,7 @@
       </c>
       <c r="T149" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="V149" t="inlineStr">
@@ -13057,7 +13537,7 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>xlsx; docx</t>
+          <t>xlsx; xlsx; xlsx; xlsx; xlsx; xlsx; xlsx; xlsx; xlsx; xlsx; docx; docx</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -13076,6 +13556,11 @@
       <c r="N150" t="inlineStr">
         <is>
           <t>Department of Biological Sciences, Virginia Institute of Marine Science, William &amp; Mary, Gloucester Point, VA, USA</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="Q150" t="inlineStr">
@@ -13166,6 +13651,11 @@
           <t>Department of Epidemiology, Gillings School of Global Public Health, University of North Carolina, Chapel Hill, NC 27599, USA</t>
         </is>
       </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="W151" t="b">
         <v>0</v>
       </c>
@@ -13218,7 +13708,7 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>xlsx; docx</t>
+          <t>xlsx; xlsx; docx</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -13237,6 +13727,11 @@
       <c r="N152" t="inlineStr">
         <is>
           <t>Department of Marine, Earth, and Atmospheric Sciences, North Carolina State University, Raleigh, NC, United States</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="W152" t="b">
@@ -13287,11 +13782,11 @@
         <v>1</v>
       </c>
       <c r="I153">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>pdf; docx</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -13329,7 +13824,7 @@
       </c>
       <c r="T153" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="W153" t="b">
@@ -13395,6 +13890,11 @@
           <t>Department of Biological and Agricultural Engineering, North Carolina State University, 3100 Faucette Dr., Raleigh, NC 27695, United States of America</t>
         </is>
       </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="W154" t="b">
         <v>0</v>
       </c>
@@ -13458,6 +13958,11 @@
           <t>School for Environment and Sustainability, University of Michigan, MI, 48109, Ann Arbor, USA</t>
         </is>
       </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="W155" t="b">
         <v>1</v>
       </c>
@@ -13531,6 +14036,11 @@
           <t>North Carolina State University, Department of Civil, Construction and Environmental Engineering Raleigh, NC, USA</t>
         </is>
       </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q156" t="inlineStr">
         <is>
           <t>0000-0003-1322-1948</t>
@@ -13636,7 +14146,7 @@
       </c>
       <c r="T157" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="V157" t="inlineStr">
@@ -13734,7 +14244,7 @@
       </c>
       <c r="T158" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="W158" t="b">
@@ -13810,6 +14320,11 @@
           <t>Key Laboratory of Eco-environments in Three Gorges Reservoir Region, Ministry of Education, College of Environment and Ecology, Chongqing University, Chongqing 400044, China</t>
         </is>
       </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
       <c r="W159" t="b">
         <v>0</v>
       </c>
@@ -13900,7 +14415,7 @@
       </c>
       <c r="T160" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="W160" t="b">
@@ -13993,7 +14508,7 @@
       </c>
       <c r="T161" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="V161" t="inlineStr">
@@ -14081,7 +14596,7 @@
       </c>
       <c r="T162" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="V162" t="inlineStr">
@@ -14152,6 +14667,11 @@
           <t>Department of Forestry and Environmental Resources, North Carolina State University, Raleigh, N.C., U.SA.</t>
         </is>
       </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="W163" t="b">
         <v>0</v>
       </c>
@@ -14215,6 +14735,11 @@
           <t>University of North Carolina at Greensboro, Department of Geography, Environment, and Sustainability, 237 Graham Bldg., PO Box 26170, Greensboro, NC, 27402-6170, USA</t>
         </is>
       </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q164" t="inlineStr">
         <is>
           <t>0000-0002-9380-7625</t>
@@ -14272,7 +14797,7 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>xlsx; docx</t>
+          <t>xlsx; xlsx; docx</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -14291,6 +14816,11 @@
       <c r="N165" t="inlineStr">
         <is>
           <t>Department of Marine, Earth, and Atmospheric Sciences, North Carolina State University, Raleigh, NC, United States</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="W165" t="b">
@@ -14383,7 +14913,7 @@
       </c>
       <c r="T166" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="W166" t="b">
@@ -14466,7 +14996,7 @@
       </c>
       <c r="T167" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="W167" t="b">
@@ -14542,6 +15072,11 @@
           <t>Department of Epidemiology, Gillings School of Global Public Health, University of North Carolina, Chapel Hill, NC 27599, USA</t>
         </is>
       </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="W168" t="b">
         <v>0</v>
       </c>
@@ -14622,7 +15157,7 @@
       </c>
       <c r="T169" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="V169" t="inlineStr">
@@ -14682,7 +15217,7 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>xlsx; docx</t>
+          <t>xlsx; docx; docx</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -14720,7 +15255,7 @@
       </c>
       <c r="T170" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="W170" t="b">
@@ -14796,6 +15331,11 @@
           <t>Department of Epidemiology, Gillings School of Global Public Health, University of North Carolina, Chapel Hill, NC 27599, USA</t>
         </is>
       </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="W171" t="b">
         <v>0</v>
       </c>
@@ -14869,6 +15409,11 @@
           <t>Department of Environmental Sciences and Engineering, Gillings School of Global Public Health, University of North Carolina at Chapel Hill, 135 Dauer Drive, Chapel Hill, NC, 27599, USA</t>
         </is>
       </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
       <c r="Q172" t="inlineStr">
         <is>
           <t>0000-0001-6293-3672</t>
@@ -14964,7 +15509,7 @@
       </c>
       <c r="T173" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="W173" t="b">
@@ -15038,6 +15583,11 @@
       <c r="N174" t="inlineStr">
         <is>
           <t>University of North Carolina at Chapel Hill, Gillings School of Global Public Health, Department of Environmental Science &amp; Engineering, 135 Dauer Drive, Chapel Hill, NC 27599, United States of America</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="W174" t="b">

--- a/inst/extdata/uncnewsletter.xlsx
+++ b/inst/extdata/uncnewsletter.xlsx
@@ -4832,7 +4832,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar_url?url=https://ajph.aphapublications.org/doi/pdf/10.2105/AJPH.2022.307003%3Fdownload%3Dtrue&amp;hl=en&amp;sa=X&amp;d=3962241131938486649&amp;ei=H1Q7Y6aFPO2KywSS3bH4Bg&amp;scisig=AAGBfm3Q4X2sCbJJGTgTcSrsGU_FdUVJcw&amp;oi=scholaralrt&amp;hist=hZvSJggAAAAJ:7463423130094204642:AAGBfm306n8jEm7p9E06Y9mqflGSBiV6Pg&amp;html=&amp;pos=0&amp;folt=kw-top</t>
+          <t>https://ajph.aphapublications.org/doi/pdf/10.2105/AJPH.2022.307003?download=true</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4910,7 +4910,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar_url?url=https://pubs.acs.org/doi/full/10.1021/acsestwater.2c00157&amp;hl=en&amp;sa=X&amp;d=1709742523088559831&amp;ei=Dg_7YtkJhJjLBKCbvNAC&amp;scisig=AAGBfm0jov0_aWmZMwe4s6j4e9vubbdcbA&amp;oi=scholaralrt&amp;hist=hZvSJggAAAAJ:3226461804228696973:AAGBfm3ju-C3kL6mSiPesevK78XQ69Qd6A&amp;html=&amp;pos=2&amp;folt=kw</t>
+          <t>https://pubs.acs.org/doi/full/10.1021/acsestwater.2c00157</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar_url?url=https://onlinelibrary.wiley.com/doi/pdfdirect/10.1111/hir.12445&amp;hl=en&amp;sa=X&amp;d=7293212103073901469&amp;ei=2fm2YrzQKtHjmQGNwb84&amp;scisig=AAGBfm1zjx3-V2aCgS0L1xZx26MYDvF-tg&amp;oi=scholaralrt&amp;hist=hZvSJggAAAAJ:3552202248086981277:AAGBfm3xoOKMdpREzJ__fgBb7pdlMpLHFA&amp;html=&amp;pos=1&amp;folt=kw</t>
+          <t>https://onlinelibrary.wiley.com/doi/pdfdirect/10.1111/hir.12445</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">

--- a/inst/extdata/uncnewsletter.xlsx
+++ b/inst/extdata/uncnewsletter.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AB174"/>
+  <dimension ref="A1:AC174"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -495,6 +495,11 @@
           <t>keywords</t>
         </is>
       </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>doi</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -578,6 +583,11 @@
           <t>drinkingwater; environmentalpolicy; healthandsafety</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>10.1002/ep.13800</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -651,6 +661,11 @@
       <c r="AA3">
         <v>3</v>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>10.2105/ajph.2022.307108</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -744,6 +759,11 @@
       <c r="AA4">
         <v>4</v>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>10.1002/lom3.10469</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -807,6 +827,11 @@
       <c r="AA5">
         <v>0</v>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>10.2112/jcoastres-d-22-00047.1</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -875,6 +900,11 @@
           <t>Containerbreeding; Mosquito; Mosquitolarvae; Rainwaterharvesting</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>10.13031/ja.15189</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -960,6 +990,11 @@
           <t>compensatorymitigation; decisionscience; knowledgecoproduction; naturalresourcesmanagement; research-managementpartnerships; watershedplanning</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>10.1002/eap.2766</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8">
@@ -1025,6 +1060,11 @@
           <t>Drought; Communications/decision-making; Decisionsupport; Localeffects; Societalimpacts; Community</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>10.1175/bams-d-21-0157.1</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -1128,6 +1168,11 @@
           <t>environmentaljustice; privatewells; toxicmetals</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>10.3390/w14132088</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -1211,6 +1256,11 @@
           <t>Escherichiacoli; Plasmid-mediatedquinoloneresistance; Plasmid-mediatedcolistinresistance; Poultryworkers; Chicken; PoultryEnvironments; Nigeria</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>10.1186/s42522-023-00079-0</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11">
@@ -1357,6 +1407,11 @@
       <c r="AA12">
         <v>2</v>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>10.1039/d2em00246a</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -1422,6 +1477,11 @@
       <c r="W13" t="b">
         <v>0</v>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>10.1287/inte.2022.1136</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -1492,6 +1552,11 @@
           <t>WaterResources; Life; EnvironmentalEducation; Development; UN2030Agenda</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>10.24857/rgsa.v17n7-013</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -1705,6 +1770,11 @@
           <t>Algalblooms; dynamicalsystems; mathmodelling; nutrienttresholdforresolvableblooms</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>10.3934/dcdss.2021151</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -1765,6 +1835,11 @@
       <c r="AA18">
         <v>0</v>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>10.1016/j.ajog.2022.11.683</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19">
@@ -1878,6 +1953,11 @@
           <t>autoantibodies; autoimmune; crocodilian; immunetoxicity; lupus; onehealth</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>10.3389/ftox.2022.1010185</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -1943,6 +2023,11 @@
       <c r="W20" t="b">
         <v>0</v>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>10.1017/ice.2022.8</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -2026,6 +2111,11 @@
       <c r="AA21">
         <v>2</v>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>10.3389/fenvs.2022.958784</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22">
@@ -2094,6 +2184,11 @@
       <c r="AB22" t="inlineStr">
         <is>
           <t>privatewells; environmentaljustice; drinkingwater; testing; metalcontamination</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>10.1089/env.2022.0100</t>
         </is>
       </c>
     </row>
@@ -2179,6 +2274,11 @@
       <c r="AA23">
         <v>4</v>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>10.1061/jwrmd5.wreng-5863</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24">
@@ -2267,6 +2367,11 @@
       <c r="AA24">
         <v>2</v>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>10.1061/(asce)wr.1943-5452.0001604</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25">
@@ -2332,6 +2437,11 @@
           <t>Infrastructure; NorthCarolina; Hurricanes; NaturalDisasters; PublicOpinion; WaterSystems</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>10.1002/awwa.2109</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26">
@@ -2397,6 +2507,11 @@
           <t>Utilities; FinancialAssistance; Durham; NorthCarolina</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>10.1002/awwa.1977</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27">
@@ -2480,6 +2595,11 @@
           <t>PFAS; Multimorbidity; ElectronicHealthRecords; PFOA; PFHpA; Chronicdisease</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>10.1097/ee9.0000000000000217</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28">
@@ -2568,6 +2688,11 @@
           <t>DrinkingWater; Nitrate; Disinfectionbyproducts; Trihalomethanes; Exposureassessment; Agriculture; Cohort</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>10.1097/ee9.0000000000000210</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29">
@@ -2671,6 +2796,11 @@
       <c r="AA29">
         <v>1</v>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>10.1016/j.agwat.2023.108179</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30">
@@ -2792,6 +2922,11 @@
           <t>on request</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>10.1016/s2542-5196(23)00028-1</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32">
@@ -2875,6 +3010,11 @@
       <c r="AA32">
         <v>46</v>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>10.1016/s0140-6736(22)00937-0</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33">
@@ -2978,6 +3118,11 @@
           <t>COVID19; Viralload; SARSCoV2; Epidemiology; Publicandoccupationalhealth; NorthCarolina; Diseasesurveillance; Virustesting</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>10.1371/journal.pwat.0000140</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -3056,6 +3201,11 @@
       <c r="AA34">
         <v>15</v>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>10.1016/j.scitotenv.2022.154763</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35">
@@ -3154,6 +3304,11 @@
       <c r="AA35">
         <v>8</v>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>10.1289/ehp11033</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36">
@@ -3187,6 +3342,11 @@
       <c r="I36">
         <v>0</v>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>10.1289/ehp11033</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37">
@@ -3247,6 +3407,11 @@
       <c r="AA37">
         <v>0</v>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>10.1289/ehp11633</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38">
@@ -3345,6 +3510,11 @@
           <t>TropicalCyclones; Spectralwavemodelling; Coastalhydrodynamics; Oceancurrents; Stormsurge; Barrierislands</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>10.1007/s12237-023-01242-6</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39">
@@ -3443,6 +3613,11 @@
           <t>Pocosin; Greenhousegases; Restoration; Mitigation</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>10.1007/s13157-022-01605-y</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40">
@@ -3536,6 +3711,11 @@
           <t>Evapotranspiration; Remotesensing; Topography; Forestcomposition; Landsat; MODIS</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>10.1007/s10980-022-01425-9</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41">
@@ -3634,6 +3814,11 @@
           <t>WastewaterMonitoring; Sars-Covid-2; Covid-19Surge; EarlyWarning; AlertAlgorithm</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>10.1073/pnas.2216021120</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42">
@@ -3732,6 +3917,11 @@
           <t>NonmarketEvaluation; Waterquality; Urbanstreams; Statedpreference</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>10.1073/pnas.2120252120</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43">
@@ -3830,6 +4020,11 @@
           <t>Drinkingwater; Children; Leadexposure</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>10.1073/pnas.2110694119</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44">
@@ -3913,6 +4108,11 @@
           <t>FaecalSludgeTreatment; Composting; Temperature-timecritera; pathogeninactivationmechanism; compostsanitation</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>10.1080/21622515.2023.2182719</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45">
@@ -3996,6 +4196,11 @@
           <t>Hazardmitigation; compoundevent; flooding; ruralresilience; climatechange</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>10.1080/09640568.2023.2183112</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46">
@@ -4079,6 +4284,11 @@
           <t>Environmentaljustive; Ambientwaterquality; Interfaceswithsociety</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>10.1080/02626667.2022.2052073</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47">
@@ -4177,6 +4387,11 @@
           <t>urban; nonpointsource; watershed; nitrogen; hydrology; management</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>10.1029/2021wr031533</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48">
@@ -4275,6 +4490,11 @@
           <t>sandhills; seepageflux; groundwater; surfacewater; spatialvariability; hydrology</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>10.1029/2021wr030711</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49">
@@ -4373,6 +4593,11 @@
           <t>waterutility; cooperation; demand; deepuncertainty; optimization; financialrisk</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>10.1029/2021wr030700</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50">
@@ -4471,6 +4696,11 @@
           <t>coastaldevelopment; stormwatermanagement; infrastructure; inundationmodeling; high-tideflooding</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>10.1029/2021ef002139</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51">
@@ -4564,6 +4794,11 @@
           <t>erosion; land-usechange; legacysediment; slope-areatreshold; .; soilnutrients; streamchannelinitiation</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>10.1002/esp.5495</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52">
@@ -4637,6 +4872,11 @@
           <t>collaborativegovernance; policybeliefs; regionalwaterplanning; Gobernanzacolaborativa; creenciaspolíticas; planificaciónregionaldelagua; 协作治理; 政策信念; 区域水资源规划</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>10.1111/psj.12473</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53">
@@ -4820,6 +5060,11 @@
           <t>biology-geologyfeebacks; DMQ99; evapotranspiration; headwaterstreams; landusechange; seasonalflashiness; specificconductance; streamgauges</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>10.1002/hyp.14550</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55">
@@ -4898,6 +5143,11 @@
       <c r="AA55">
         <v>4</v>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>10.2105/ajph.2022.307003</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56">
@@ -4981,6 +5231,11 @@
           <t>WASP; environmentalmodeling; nanocopper; nanomaterials; freswater</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>10.1021/acsestwater.2c00157</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57">
@@ -5054,6 +5309,11 @@
           <t>healtheducation; healthinformationneeds; healthprofessionals; informationdissemination; informationliteracy; informationseekingbehavior; patienteducation; research; qualitative</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>10.1111/hir.12445</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58">
@@ -5122,6 +5382,11 @@
       <c r="AA58">
         <v>9</v>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>10.1001/jamaneurol.2023.1168</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59">
@@ -5230,6 +5495,11 @@
           <t>crAssphage; Municipaluntreatedwastewater; Temporalvariations; Spatialvariations; Entericpathogenscorrelations; Bacteria; Andviruses; ;; qPCR; rt-qPCR</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>10.1016/j.watres.2023.120008</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60">
@@ -5313,6 +5583,11 @@
       <c r="AA60">
         <v>4</v>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>10.1021/acs.accounts.2c00591</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61">
@@ -5411,6 +5686,11 @@
           <t>ArtificialNeuralNetworks; Geneticprogramming; Antedcedentenvironmentalconditions; Temperature; Salinity; Oysters</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>10.1007/s10661-022-10836-9</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62">
@@ -5484,6 +5764,11 @@
       <c r="AA62">
         <v>3</v>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>10.2105/ajph.2022.307108</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63">
@@ -5675,6 +5960,11 @@
           <t>Pretermbirth; Lowbirthweight; Adversebirthoutcome; Pollutedsites; Superfund; Industrialsites</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>10.1038/s41370-022-00475-0</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65">
@@ -5793,6 +6083,11 @@
           <t>Carboncycle; Climate-changemitigation; Environmentalimpact</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>10.1038/s43247-022-00501-x</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66">
@@ -5901,6 +6196,11 @@
           <t>ChemicalEngineering; Waterresources</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>10.1038/s41545-021-00128-z</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67">
@@ -6000,6 +6300,11 @@
           <t>Agriculture; Environmentalimpact; Hydrology; Waterresources</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>10.1038/s41597-022-01358-7</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68">
@@ -6088,6 +6393,11 @@
       <c r="AA68">
         <v>0</v>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>10.1371/journal.pntd.0011496</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69">
@@ -6181,6 +6491,11 @@
       <c r="AA69">
         <v>5</v>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>10.1371/journal.pwat.0000039</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70">
@@ -6274,6 +6589,11 @@
       <c r="AA70">
         <v>5</v>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>10.1371/journal.pwat.0000032</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71">
@@ -6367,6 +6687,11 @@
       <c r="AA71">
         <v>0</v>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>10.1371/journal.pone.0270688</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72">
@@ -6460,6 +6785,11 @@
       <c r="AA72">
         <v>17</v>
       </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>10.1371/journal.pone.0270659</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73">
@@ -6538,6 +6868,11 @@
       <c r="AA73">
         <v>1</v>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>10.1371/journal.pntd.0010495</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74">
@@ -6636,6 +6971,11 @@
           <t>Cryptosporidium; Bacillusspores; MS2coliphage; bromine; chlorine; disinfection; watertreatment</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>10.1021/acs.est.3c00536</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75">
@@ -6739,6 +7079,11 @@
           <t>PFASdestruction; fluoroethers; GenX; Nafionbyproduct2; photolysis</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>10.1021/acs.est.3c00947</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76">
@@ -6857,6 +7202,11 @@
           <t>coastalflooding; low-costsensors; hightideflooding; stormwatermanagement; coastalinfrastructure; sealevelrise</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>10.1029/2022wr032392</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77">
@@ -6935,6 +7285,11 @@
       <c r="AA77">
         <v>0</v>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>10.1371/journal.pwat.0000123</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78">
@@ -7033,6 +7388,11 @@
           <t>PFAS; Drinkingwater; USEPA; PFPrA; Ultra-shortchain</t>
         </is>
       </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>10.1016/j.scitotenv.2023.162978</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79">
@@ -7126,6 +7486,11 @@
           <t>coastal; fecalbacteria; runoff; stormwater</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>10.3390/hydrology10070156</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80">
@@ -7219,6 +7584,11 @@
           <t>cyanobacteria; cyanotoxin; microcystin; stormwaterpollution; eutrophication</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>10.3390/w15132436</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81">
@@ -7292,6 +7662,11 @@
           <t>waterscarcity; waterrecycling; wastewatertreatmentplants; nutrients; phosphorus</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>10.3390/environments10020017</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82">
@@ -7405,6 +7780,11 @@
           <t>HWTS; POU; chitosan; coagulation; sandfiltration; bacterialreduction; virusreduction</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>10.3390/ijms24021295</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83">
@@ -7508,6 +7888,11 @@
           <t>environmentaljustice; privatewells; toxicmetals</t>
         </is>
       </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>10.3390/w14132088</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84">
@@ -7576,6 +7961,11 @@
           <t>explainability; LSPmethod; waterquality; decision-making</t>
         </is>
       </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>10.3390/info13120551</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85">
@@ -7674,6 +8064,11 @@
           <t>wetlands; nature-basedsolutions; floodmitigation; coastalflooding; tidalwatersheds</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>10.3390/hydrology9120218</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86">
@@ -7767,6 +8162,11 @@
           <t>reclaimedwater; waterreuse; water-supplysystems; agro-wastewater; riskassessment</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>10.3390/app121910159</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87">
@@ -7865,6 +8265,11 @@
           <t>geospatialanalysis; landsuitability; floodmitigation; nature-basedsolutions(NBS); rurallandscapes; GeographicInformationSystems(GIS); floodresilience</t>
         </is>
       </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>10.3390/land11091504</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88">
@@ -7958,6 +8363,11 @@
           <t>reclaimedwater; waterreuse; water-supplysystems; agro-wastewater; riskassessment</t>
         </is>
       </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>10.3390/app121910159</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89">
@@ -8051,6 +8461,11 @@
           <t>coastal; eutrophicationsepticsystems</t>
         </is>
       </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>10.3390/earth3020039</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90">
@@ -8119,6 +8534,11 @@
           <t>hydrologicdrought; SoutheastUS; NationalWaterModel</t>
         </is>
       </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>10.3390/w14101525</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91">
@@ -8217,6 +8637,11 @@
           <t>droughtandhealth; droughtrisk; LocalMoran; sI; droughtvulnerability; U.S.drought</t>
         </is>
       </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>10.3390/ijerph19084628</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92">
@@ -8300,6 +8725,11 @@
           <t>environmentalplanning; policyevaluation; riparianbuffers</t>
         </is>
       </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>10.3390/su14073889</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93">
@@ -8398,6 +8828,11 @@
           <t>coastalwetlanddegradation; remotesensing; NDVI; climatechange; sea-levelrise; saltwaterintrusion; hydrologicmodel; AlligatorRiverNationalWildlifeRefuge; USA</t>
         </is>
       </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>10.3390/f13030411</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94">
@@ -8496,6 +8931,11 @@
           <t>waterinfrastructure; waterservices; waterutilities; waterbills; billingfrequency; customerassistanceprograms(CAPS); affordability</t>
         </is>
       </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>10.3390/w14020247</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95">
@@ -8579,6 +9019,11 @@
           <t>canine; drinkingwater; equine; fluoroether; OneHealth; nafionby-product2; GenXchemicals; PFOA; PFOS</t>
         </is>
       </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>10.1021/acs.est.3c01146</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96">
@@ -8652,6 +9097,11 @@
           <t>drinkingwater; fluoropolymers; food; safety; toxins</t>
         </is>
       </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>10.1021/acs.estlett.0c00255</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97">
@@ -8715,6 +9165,11 @@
           <t>Airpollution; Color; Environmentalpollution; Environmentalscience; Impurities</t>
         </is>
       </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>10.1021/acs.est.3c05429</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98">
@@ -8813,6 +9268,11 @@
           <t>lead; Children; shealth; drinkingwater; machinelearning; riskassessment</t>
         </is>
       </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>10.1021/acs.est.2c07477</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99">
@@ -8916,6 +9376,11 @@
           <t>PFASair-waterinterfacialadsorption; QSPR; nonequilibrium; unsaturatedcolumns; panfilm</t>
         </is>
       </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>10.1021/acs.est.2c07316</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100">
@@ -8999,6 +9464,11 @@
           <t>adsorption; molecules; nanofibers; remediation</t>
         </is>
       </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>10.1021/acs.accounts.2c00591</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101">
@@ -9097,6 +9567,11 @@
           <t>nontargetedanalysis; anthropogenicchemicals; wastewater; landfillleachate; reverseosmosis</t>
         </is>
       </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>10.1021/acsestwater.2c00320</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102">
@@ -9200,6 +9675,11 @@
           <t>per-andpolyfluoroalkylsubstances(PFAS); presumptivecontamination; PFAStestingandinvestigation; AFFF; PFASwasteanddisposal</t>
         </is>
       </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>10.1021/acs.estlett.2c00502</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103">
@@ -9273,6 +9753,11 @@
           <t>anatomy; genetics; infectiousdiseases; viruses; wastewater</t>
         </is>
       </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>10.1021/acsestwater.2c00287</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104">
@@ -9371,6 +9856,11 @@
           <t>coalash; lacustrinesediment; multiproxytracing; aquaticecosystems</t>
         </is>
       </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>10.1021/acs.est.2c04717.s005</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105">
@@ -9444,6 +9934,11 @@
           <t>waterandsanitationinfrastructure; disadvantagedunincorporatedcommunities; environmetaljustice; participatoryprocess; sociotechnicaldesign</t>
         </is>
       </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>10.1021/acs.est.2c03076</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106">
@@ -9542,6 +10037,11 @@
           <t>textiledyes; environmentalpollution; cleanwater; sustainability; polycarbodiimide; topologicalpolarsurfacearea(TPSA); moleculartransport</t>
         </is>
       </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>10.1021/acsapm.2c00959</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107">
@@ -9640,6 +10140,11 @@
           <t>land-useregression; molecularmicrobialsourcetracking; surfacewater; sediment; rivernetworks; animalfeedingoperations; septicsystems</t>
         </is>
       </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>10.1021/acs.est.2c00224</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108">
@@ -9718,6 +10223,11 @@
           <t>multiplewatersourceuse; supplementalunimprovedsourceuse; fecalcontamination; MonteCarlosimulations; drinkingwaterquality; low-andmiddle-incomecountries</t>
         </is>
       </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>10.1021/acs.est.1c05683</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109">
@@ -9811,6 +10321,11 @@
           <t>Microplasticsinrivers; Watermanagement; DiversionsAbstraction; Pairedcatchmentapproach; Globalmodels</t>
         </is>
       </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>10.1016/j.watres.2023.120112</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110">
@@ -9899,6 +10414,11 @@
           <t>Pocosin; Carbon; Methane; GHG; Netecosystemexchange; Hydrologicrestoration; Peatland; Evergreenshrubbog; Watertabledepth; Eddycovariance; Carbondioxide</t>
         </is>
       </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>10.1016/j.ecoleng.2023.107011</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111">
@@ -9987,6 +10507,11 @@
           <t>Per-andpolyfluoroalkylsubstances; PFAS; Drinkingwater; Serum; Humanhealthoutcomes</t>
         </is>
       </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>10.1016/j.scitotenv.2023.165091</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112">
@@ -10085,6 +10610,11 @@
           <t>Per-andpolyfluoroalkylsubstances; Drinking-water; Public-supply; Private-wellsSources; Healtheffect</t>
         </is>
       </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>10.1016/j.envint.2023.108033</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113">
@@ -10193,6 +10723,11 @@
           <t>Zikavirus; wastewater-basedepidemiology; resource-constrainedsettings</t>
         </is>
       </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>10.1016/j.watres.2023.120116</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114">
@@ -10296,6 +10831,11 @@
           <t>Airpollutioncontrol; Biologicalgastreatment; Capillaryreactor; Hydrophobicpollutants; Segmentedflow</t>
         </is>
       </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>10.1016/j.jece.2023.110502</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115">
@@ -10384,6 +10924,11 @@
           <t>Marinemicroalgae; Dunaliellaviridis; Flocculation; Harvesting; Waterreuse; Dissolvedorganicmatter</t>
         </is>
       </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>10.1016/j.scitotenv.2023.164087</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116">
@@ -10477,6 +11022,11 @@
           <t>Palynology; Plantmacrofossil; Charcoal; Paleoclimatereconstruction; Sea-levelrise; Wildfire; Wetlanddevelopment; Hydroperiod</t>
         </is>
       </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>10.1016/j.quascirev.2023.108153</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117">
@@ -10555,6 +11105,11 @@
           <t>Microbiome; Outdoorair; Greenspace; AirborneBacteria; 16SrRNA; Aerobiome</t>
         </is>
       </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>10.1016/j.scitotenv.2023.163266</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118">
@@ -10628,6 +11183,11 @@
       <c r="AA118">
         <v>13</v>
       </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>10.1016/s2214-109x(23)00006-2</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119">
@@ -10706,6 +11266,11 @@
           <t>Watersecurity; Textanalysis; Structuraltopicmodeling; Planning; Environmentaljustice</t>
         </is>
       </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>10.1016/j.jenvman.2023.117600</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120">
@@ -10814,6 +11379,11 @@
           <t>crAssphage; Municipaluntreatedwastewater; Temporalvariations; Spatialvariations; Entericpathogenscorrelations; Bacteria; Andviruses; qPCR; rt-qPCR</t>
         </is>
       </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>10.1016/j.watres.2023.120008</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121">
@@ -10902,6 +11472,11 @@
           <t>Groundwatercontamination; Swinelagoons; Privatewells; Atmosphericstressors; Environmentalpollution</t>
         </is>
       </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>10.1016/j.scitotenv.2023.161426</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122">
@@ -10990,6 +11565,11 @@
           <t>Microplastics; Streamflow; Urbandevelopment; Sediment; Watershed; Samplingmethod</t>
         </is>
       </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>10.1016/j.scitotenv.2023.162940</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123">
@@ -11083,6 +11663,11 @@
           <t>UAV; UAS; Rugosity; Geomorphometry; Coastalhabitat; Remotesensing</t>
         </is>
       </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>10.1016/j.ecolind.2023.110190</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124">
@@ -11166,6 +11751,11 @@
           <t>Hospital-aquiredinfection; Multidrug-resistantpathogen; Environmentalcleaning; Probiotic; Randomized-controlledtrial; Environmentalhygiene; MRSAVRE; Multidrug-resistantGram-negative</t>
         </is>
       </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>10.1016/j.eclinm.2023.101958</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125">
@@ -11249,6 +11839,11 @@
           <t>Atmosphericforcing; CapeHatteras; PEACH; Atmosphericcyclones; Atmosphericwarmandcoolseasons</t>
         </is>
       </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>10.1016/j.dynatmoce.2023.101364</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126">
@@ -11342,6 +11937,11 @@
           <t>Contamination; Distribution; Environment; Healthimpact; NorthCarolina; PFASsources</t>
         </is>
       </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>10.1016/j.scitotenv.2023.163123</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127">
@@ -11420,6 +12020,11 @@
           <t>Landscapechange; Climatechange; Attribution; NeuseRiver; Sea-levelrise; Marshloss</t>
         </is>
       </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>10.1016/j.geomorph.2023.108666</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128">
@@ -11518,6 +12123,11 @@
           <t>Clustering; Metals; Privatewells; Socialvulnerability; Geographicdata</t>
         </is>
       </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>10.2139/ssrn.4161726</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129">
@@ -11606,6 +12216,11 @@
           <t>Groundwatercontamination; Swinelagoons; Privatewells; Atmosphericstressors; Environmentalpollution</t>
         </is>
       </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>10.1016/j.scitotenv.2023.161426</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130">
@@ -11704,6 +12319,11 @@
           <t>Microbioreactor; Volatileorganiccompound; Biofiltration; Modeling</t>
         </is>
       </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>10.1016/j.cej.2023.141636</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131">
@@ -11812,6 +12432,11 @@
           <t>Biofiltration; Cometabolism; Adsorption; Emergingcontaminants</t>
         </is>
       </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>10.1016/j.watres.2023.119652</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132">
@@ -11920,6 +12545,11 @@
           <t>Subsurfacedrainage; Subirrigation; On-farmwaterstorage; Drainagewaterreuse; Supplementalirrigation; Surfacewaterquality</t>
         </is>
       </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>10.1016/j.agwat.2023.108179</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133">
@@ -11983,6 +12613,11 @@
       <c r="AA133">
         <v>1</v>
       </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>10.1016/j.scib.2022.12.015</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134">
@@ -12086,6 +12721,11 @@
           <t>Wastewater-basedepidemiology; Passivesampling; Mooreswab</t>
         </is>
       </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>10.1016/j.scitotenv.2022.161101</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135">
@@ -12174,6 +12814,11 @@
           <t>Groundwatercontamination; Swinelagoons; Privatewells; Atmosphericstressors; Environmentalpollution</t>
         </is>
       </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>10.1016/j.scitotenv.2023.161426</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136">
@@ -12277,6 +12922,11 @@
           <t>SARS-CoV-2; Wastewater-basedepidemiology; Universitycampus; Emergingcontaminants; Disinfectants</t>
         </is>
       </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>10.1016/j.jhazmat.2022.130690</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137">
@@ -12360,6 +13010,11 @@
           <t>Geographicinformationsystems; Ruralgeography; statisticalanalysis</t>
         </is>
       </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>10.1016/j.jrurstud.2022.11.011</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138">
@@ -12438,6 +13093,11 @@
           <t>Forestedwatersheds; FUTURESmodel; Landuselandcoverchange(LULCC); Hydrologicmodeling; SoilandWaterAssessmentTool(SWAT); Globalclimatemodel</t>
         </is>
       </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>10.2139/ssrn.4230110</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139">
@@ -12541,6 +13201,11 @@
           <t>VOC; Contaminantflux; Groundwater; Stream</t>
         </is>
       </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>10.1016/j.jconhyd.2022.104124</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140">
@@ -12614,6 +13279,11 @@
           <t>CoastalaltimetrySealevel; Waves; Videocamera; Tidegauge; Buoy; Altimeter; Significantwaveheight; Re-trackingalgorithm</t>
         </is>
       </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>10.1016/j.coastaleng.2022.104275</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141">
@@ -12717,6 +13387,11 @@
           <t>Wastewater-basedepidemiology; Sewagesurveillance; Coronavirus; COVID; ddPCR</t>
         </is>
       </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>10.1016/j.scitotenv.2022.159996</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142">
@@ -12815,6 +13490,11 @@
           <t>Clustering; Metals; Privatewells; Socialvulnerability; Geographicdata</t>
         </is>
       </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>10.2139/ssrn.4161726</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143">
@@ -12928,6 +13608,11 @@
           <t>GHGEmissions; Waterextractable; Phosphorus; Zinc; Copper; NorthCarolina</t>
         </is>
       </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>10.2139/ssrn.4225062</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144">
@@ -13006,6 +13691,11 @@
           <t>Risk; Compoundhazard; Flood; Rural; Emergencymanagement; Planning; CCWE</t>
         </is>
       </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>10.1016/j.pdisas.2022.100266</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145">
@@ -13109,6 +13799,11 @@
           <t>ExtraintestinalpathogenicE.coli(ExPEC); Foodborneurinarytractinfection(fUTI); Concentratedanimalfeedingoperation(CAFO); Syndromicsurveillance; Besag-York-Mollié(BYM)model; Ecologicalregressionanalysis</t>
         </is>
       </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>10.1016/j.scitotenv.2022.158749</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146">
@@ -13197,6 +13892,11 @@
           <t>Sourceapportionment; Receptormodels; PFAS; Perfluoroalkylsubstances</t>
         </is>
       </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>10.1016/j.scitotenv.2022.158842</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147">
@@ -13290,6 +13990,11 @@
           <t>Waterquality; ToxicCyanobacteria; Airquality; PM2.5; Microcystis; Dolichospermum</t>
         </is>
       </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>10.2139/ssrn.4125290</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148">
@@ -13398,6 +14103,11 @@
           <t>Permeance; Selectivity; Rejection; Advectivetransport; Diffusivetransport</t>
         </is>
       </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>10.1016/j.memsci.2022.120856</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149">
@@ -13496,6 +14206,11 @@
           <t>Nutrientmanagement; Livestock; Agriculture; Machinelearning; SatelliteradarSentinel-1</t>
         </is>
       </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>10.1016/j.jenvman.2022.115334</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150">
@@ -13589,6 +14304,11 @@
           <t>Nitrogenremoval; Denitrification; Anammox; nosZ; hzo; Sediments</t>
         </is>
       </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>10.1016/j.ecss.2022.107973</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151">
@@ -13667,6 +14387,11 @@
           <t>CAFOs; Swine; Hogproduction; Animalfarming; Environmentaljustice; Gastrointestinalillness</t>
         </is>
       </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>10.1289/isee.2021.p-321</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152">
@@ -13745,6 +14470,11 @@
           <t>PFAS; Massload; Model; Sourcetracking; Environmentalmonitoring; Drinkingwater</t>
         </is>
       </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>10.1016/j.scitotenv.2022.154763</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153">
@@ -13838,6 +14568,11 @@
           <t>Animalhusbandry; Fecalcontamination; Sanitation; Hygiene; Animalfecesmanagement; Entericpathogens</t>
         </is>
       </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>10.2139/ssrn.3978613</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154">
@@ -13906,6 +14641,11 @@
           <t>Naturalinfrastructure; Wetlandrestoration; Reforestation; Watershedmodeling</t>
         </is>
       </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>10.1016/j.ecoleng.2022.106696</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155">
@@ -13984,6 +14724,11 @@
           <t>Hydrogeology; Climatechange; Sea-levelrise; Saltwaterintrusion; Barrier-islandaquifers</t>
         </is>
       </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>10.1016/j.csr.2022.104789</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156">
@@ -14067,6 +14812,11 @@
           <t>Advancedmeteringinfrastructure; Waterserviceinterruption; WaterUtilities; Smartmeters</t>
         </is>
       </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>10.1016/j.watres.2022.118802</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157">
@@ -14165,6 +14915,11 @@
           <t>Nutrientmanagement; Livestock; Agriculture; Machinelearning; SatelliteradarSentinel-1</t>
         </is>
       </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>10.1016/j.jenvman.2022.115334</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158">
@@ -14258,6 +15013,11 @@
           <t>Arsenic; Privatewells; Watercontamination; Birthoutcomes; Epidemiology</t>
         </is>
       </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>10.1289/isee.2020.virtual.p-0506</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159">
@@ -14336,6 +15096,11 @@
           <t>Lanthanumcontainingmaterial; Lanthanumcarbonate; Phosphorusremoval; Wastewatertreatment; Mineralprecipitation</t>
         </is>
       </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>10.1016/j.scitotenv.2022.153153</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160">
@@ -14429,6 +15194,11 @@
           <t>Residencehall; Asymptomaticsurveillance; Positivepredictivevalue; Clinicalcase</t>
         </is>
       </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>10.2139/ssrn.4028264</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161">
@@ -14527,6 +15297,11 @@
           <t>Infiltrationcapacity; Urbanhydrology; Urbansoil; Rainfall-runoffmodels; Randomforest; Stormwater</t>
         </is>
       </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>10.1016/j.jenvman.2022.115004</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162">
@@ -14615,6 +15390,11 @@
           <t>Groundwater; Microbesampling; NorthCarolina; Coliform; E.coli; Waterquality</t>
         </is>
       </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>10.1016/j.gsd.2022.100759</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163">
@@ -14683,6 +15463,11 @@
           <t>Rurallandscapes; Nature-basedsolutions; Costs; Economics; Capitalbudgeting; Floodmitigation</t>
         </is>
       </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>10.1016/j.nbsj.2022.100016</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164">
@@ -14756,6 +15541,11 @@
           <t>Aquaticecosystems; Hydrology; Landuse/landcover; Physicalhabitat; Urbanstreams; Waterquality</t>
         </is>
       </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>10.1016/j.apgeog.2022.102637</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165">
@@ -14834,6 +15624,11 @@
           <t>PFAS; Massload; Model; Sourcetracking; Environmentalmonitoring; Drinkingwater</t>
         </is>
       </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>10.1016/j.scitotenv.2022.154763</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166">
@@ -14927,6 +15722,11 @@
           <t>SARS-CoV-2; Wastewater; COVID-19; RT-qPCR; RT-ddPCR; Wastewater-basedepidemiology(WBE)</t>
         </is>
       </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>10.1016/j.scitotenv.2021.152503</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167">
@@ -15010,6 +15810,11 @@
           <t>Subsurfacedrainage; Supplementalirrigation; On-farmwaterstorage; Irrigationreservoir; Drainagewaterreuse; DRAINMOD-DWR</t>
         </is>
       </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>10.1016/j.agwat.2022.107592</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168">
@@ -15088,6 +15893,11 @@
           <t>CAFOs; Swine; Hogproduction; Animalfarming; Environmentaljustice; Gastrointestinalillness</t>
         </is>
       </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>10.1289/isee.2021.p-321</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169">
@@ -15176,6 +15986,11 @@
           <t>Groundwater; Microbesampling; NorthCarolina; Coliform; E.coli; Waterquality</t>
         </is>
       </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>10.1016/j.gsd.2022.100759</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170">
@@ -15269,6 +16084,11 @@
           <t>Arsenic; Manganese; Lead; Privatewells; K-meansclustering; Geocoding</t>
         </is>
       </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>10.1016/j.scitotenv.2021.151479</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171">
@@ -15347,6 +16167,11 @@
           <t>Floods; Hurricanes; Interruptedtimeseriesanalysis; Gastrointestinalillness; Environmentalepidemiology; Disasterepidemiology</t>
         </is>
       </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>10.1016/j.scitotenv.2021.151108</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172">
@@ -15430,6 +16255,11 @@
           <t>Bayesiannetworks; Drinkingwater; Bloodleadlevels; Machinelearning; Riskassessment; Healthdisparity</t>
         </is>
       </c>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t>10.1016/j.envres.2021.112146</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173">
@@ -15523,6 +16353,11 @@
           <t>SARS-CoV-2; Wastewater; COVID-19; RT-qPCR; RT-ddPCR; Wastewater-basedepidemiology(WBE)</t>
         </is>
       </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>10.1016/j.scitotenv.2021.152503</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174">
@@ -15599,6 +16434,11 @@
       <c r="AB174" t="inlineStr">
         <is>
           <t>Privatewells; Householdwatertreatment; Healthbeliefmodel; Self-efficacy; Socialcognitivetheory; Drinkingwater</t>
+        </is>
+      </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>10.1016/j.scitotenv.2021.150448</t>
         </is>
       </c>
     </row>
